--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA0C34A-CFA4-422D-B04E-CAB52C4CD8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B7468A-ED5C-4EFE-8E61-2C9FEEB3AA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info Sim" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -165,9 +165,6 @@
     <t>0.0005</t>
   </si>
   <si>
-    <t>0,4; 0,6</t>
-  </si>
-  <si>
     <t>0,79; 0,21; 0,00; 0,00</t>
   </si>
   <si>
@@ -182,13 +179,19 @@
   <si>
     <t>N2; O2; CO2; H2O</t>
   </si>
+  <si>
+    <t>0,40; 0,60</t>
+  </si>
+  <si>
+    <t>1,00;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -470,6 +473,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -488,19 +503,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -812,36 +815,36 @@
       <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="15" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="15" t="s">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="14"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="18"/>
     </row>
     <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -968,7 +971,7 @@
       <c r="A4" s="5">
         <v>1002</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4874,36 +4877,36 @@
       <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="16" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="16" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="16" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="18"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="22"/>
     </row>
     <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -4969,16 +4972,16 @@
         <v>1001</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="23">
-        <v>1</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F3" s="7">
         <f>(0.0005)/2</f>
@@ -5008,17 +5011,17 @@
       <c r="N3" s="4">
         <v>20</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="21">
+      <c r="O3" s="4">
+        <v>1</v>
+      </c>
+      <c r="P3" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>29</v>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>1</v>
       </c>
       <c r="S3" s="4">
         <v>500</v>
@@ -5031,17 +5034,17 @@
       <c r="A4" s="5">
         <v>1002</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>47</v>
-      </c>
       <c r="E4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="7">
         <f>(0.000149)/2</f>
@@ -5071,17 +5074,17 @@
       <c r="N4" s="4">
         <v>10</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="21">
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+      <c r="P4" s="15">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>29</v>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>1</v>
       </c>
       <c r="S4" s="4">
         <v>600</v>

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B7468A-ED5C-4EFE-8E61-2C9FEEB3AA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68404FA-200D-4F6E-8A0E-241F08965470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,7 +191,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -441,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -479,9 +479,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -503,7 +500,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,33 +812,33 @@
       <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19" t="s">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="19" t="s">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="18"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="17"/>
     </row>
     <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -4852,7 +4849,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
     <col min="5" max="5" width="18" style="10" bestFit="1" customWidth="1"/>
@@ -4866,7 +4863,7 @@
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.44140625" bestFit="1" customWidth="1"/>
@@ -4877,33 +4874,33 @@
       <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="20" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="20" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="20" t="s">
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="22"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="21"/>
     </row>
     <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -4974,10 +4971,10 @@
       <c r="B3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>46</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -5014,8 +5011,8 @@
       <c r="O3" s="4">
         <v>1</v>
       </c>
-      <c r="P3" s="15">
-        <v>1E-3</v>
+      <c r="P3" s="22">
+        <v>1E-4</v>
       </c>
       <c r="Q3" s="7">
         <v>0</v>
@@ -5040,7 +5037,7 @@
       <c r="C4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5077,8 +5074,8 @@
       <c r="O4" s="4">
         <v>1</v>
       </c>
-      <c r="P4" s="15">
-        <v>5.0000000000000001E-4</v>
+      <c r="P4" s="22">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Q4" s="7">
         <v>0</v>

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68404FA-200D-4F6E-8A0E-241F08965470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B32E652-8911-4A0F-8471-A9643ABF538B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,16 +174,16 @@
     <t>Hexadecano</t>
   </si>
   <si>
-    <t>Octano; Hexadecano</t>
-  </si>
-  <si>
-    <t>N2; O2; CO2; H2O</t>
-  </si>
-  <si>
     <t>0,40; 0,60</t>
   </si>
   <si>
     <t>1,00;</t>
+  </si>
+  <si>
+    <t>N2;O2;CO2;H2O</t>
+  </si>
+  <si>
+    <t>Octano;Dodecano</t>
   </si>
 </sst>
 </file>
@@ -191,7 +191,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -482,6 +482,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -498,9 +501,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
     <col min="5" max="5" width="18" style="10" bestFit="1" customWidth="1"/>
@@ -812,33 +812,33 @@
       <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="18" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="18" t="s">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="18"/>
     </row>
     <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -4860,7 +4860,7 @@
     <col min="10" max="10" width="6.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
@@ -4874,33 +4874,33 @@
       <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="19" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="19" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="19" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="22"/>
     </row>
     <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -4972,10 +4972,10 @@
         <v>44</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -4988,7 +4988,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="4">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="I3" s="4">
         <v>300</v>
@@ -4997,21 +4997,21 @@
         <v>2000</v>
       </c>
       <c r="K3" s="7">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L3" s="4">
         <v>5</v>
       </c>
       <c r="M3" s="4">
-        <v>9.9999999999999995E-8</v>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="N3" s="4">
-        <v>20</v>
+        <v>0.02</v>
       </c>
       <c r="O3" s="4">
         <v>1</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="16">
         <v>1E-4</v>
       </c>
       <c r="Q3" s="7">
@@ -5024,7 +5024,7 @@
         <v>500</v>
       </c>
       <c r="T3" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -5032,13 +5032,13 @@
         <v>1002</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="15" t="s">
         <v>47</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>46</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>43</v>
@@ -5048,7 +5048,7 @@
         <v>7.4499999999999995E-5</v>
       </c>
       <c r="G4" s="4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="H4" s="4">
         <v>0.15</v>
@@ -5057,25 +5057,25 @@
         <v>305</v>
       </c>
       <c r="J4" s="8">
-        <v>1730</v>
+        <v>1500</v>
       </c>
       <c r="K4" s="7">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L4" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="4">
-        <v>1.9999999999999999E-7</v>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="N4" s="4">
-        <v>10</v>
+        <v>0.02</v>
       </c>
       <c r="O4" s="4">
         <v>1</v>
       </c>
-      <c r="P4" s="22">
-        <v>1.0000000000000001E-5</v>
+      <c r="P4" s="16">
+        <v>1E-4</v>
       </c>
       <c r="Q4" s="7">
         <v>0</v>
@@ -5087,7 +5087,7 @@
         <v>600</v>
       </c>
       <c r="T4" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C7D39A-E5C7-4EE6-9EC6-6DC74C006AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB11203A-03F4-4237-A17F-5CDC3167DF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="29">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -878,10 +878,10 @@
         <v>30</v>
       </c>
       <c r="L3" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N3" s="4">
         <v>10</v>
@@ -941,10 +941,10 @@
         <v>30</v>
       </c>
       <c r="L4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N4" s="4">
         <v>10</v>
@@ -1004,10 +1004,10 @@
         <v>30</v>
       </c>
       <c r="L5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N5" s="4">
         <v>10</v>
@@ -1067,10 +1067,10 @@
         <v>30</v>
       </c>
       <c r="L6" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N6" s="4">
         <v>10</v>
@@ -1130,10 +1130,10 @@
         <v>30</v>
       </c>
       <c r="L7" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N7" s="4">
         <v>10</v>
@@ -1193,10 +1193,10 @@
         <v>30</v>
       </c>
       <c r="L8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N8" s="4">
         <v>10</v>
@@ -1256,10 +1256,10 @@
         <v>30</v>
       </c>
       <c r="L9" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M9" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N9" s="4">
         <v>10</v>
@@ -1319,10 +1319,10 @@
         <v>30</v>
       </c>
       <c r="L10" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M10" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N10" s="4">
         <v>10</v>
@@ -1382,10 +1382,10 @@
         <v>30</v>
       </c>
       <c r="L11" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M11" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N11" s="4">
         <v>10</v>
@@ -5188,7 +5188,7 @@
         <v>28</v>
       </c>
       <c r="F3" s="7">
-        <f t="shared" ref="F3:F11" si="0">(0.0001451)/2</f>
+        <f t="shared" ref="F3:F5" si="0">(0.0001451)/2</f>
         <v>7.2550000000000002E-5</v>
       </c>
       <c r="G3" s="4">
@@ -5207,10 +5207,10 @@
         <v>30</v>
       </c>
       <c r="L3" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N3" s="4">
         <v>10</v>
@@ -5273,7 +5273,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N4" s="4">
         <v>10</v>
@@ -5333,10 +5333,10 @@
         <v>30</v>
       </c>
       <c r="L5" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M5" s="4">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="N5" s="4">
         <v>10</v>
@@ -5361,382 +5361,136 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>1004</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>7.2550000000000002E-5</v>
-      </c>
-      <c r="G6" s="4">
-        <v>150</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I6" s="4">
-        <v>300</v>
-      </c>
-      <c r="J6" s="8">
-        <v>1730</v>
-      </c>
-      <c r="K6" s="7">
-        <v>30</v>
-      </c>
-      <c r="L6" s="4">
-        <v>3</v>
-      </c>
-      <c r="M6" s="4">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N6" s="4">
-        <v>10</v>
-      </c>
-      <c r="O6" s="4">
-        <v>1</v>
-      </c>
-      <c r="P6" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <v>1</v>
-      </c>
-      <c r="S6" s="4">
-        <v>500</v>
-      </c>
-      <c r="T6" s="8">
-        <v>2</v>
-      </c>
+      <c r="A6" s="5"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="8"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>1005</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="7">
-        <f t="shared" si="0"/>
-        <v>7.2550000000000002E-5</v>
-      </c>
-      <c r="G7" s="4">
-        <v>150</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I7" s="4">
-        <v>300</v>
-      </c>
-      <c r="J7" s="8">
-        <v>1730</v>
-      </c>
-      <c r="K7" s="7">
-        <v>30</v>
-      </c>
-      <c r="L7" s="4">
-        <v>5</v>
-      </c>
-      <c r="M7" s="4">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N7" s="4">
-        <v>10</v>
-      </c>
-      <c r="O7" s="4">
-        <v>1</v>
-      </c>
-      <c r="P7" s="16">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <v>1</v>
-      </c>
-      <c r="S7" s="4">
-        <v>500</v>
-      </c>
-      <c r="T7" s="8">
-        <v>2</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="8"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>1006</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="0"/>
-        <v>7.2550000000000002E-5</v>
-      </c>
-      <c r="G8" s="4">
-        <v>150</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I8" s="4">
-        <v>300</v>
-      </c>
-      <c r="J8" s="8">
-        <v>1730</v>
-      </c>
-      <c r="K8" s="7">
-        <v>30</v>
-      </c>
-      <c r="L8" s="4">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N8" s="4">
-        <v>10</v>
-      </c>
-      <c r="O8" s="4">
-        <v>1</v>
-      </c>
-      <c r="P8" s="16">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4">
-        <v>500</v>
-      </c>
-      <c r="T8" s="8">
-        <v>2</v>
-      </c>
+      <c r="A8" s="5"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="8"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>1007</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="0"/>
-        <v>7.2550000000000002E-5</v>
-      </c>
-      <c r="G9" s="4">
-        <v>150</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I9" s="4">
-        <v>300</v>
-      </c>
-      <c r="J9" s="8">
-        <v>1730</v>
-      </c>
-      <c r="K9" s="7">
-        <v>30</v>
-      </c>
-      <c r="L9" s="4">
-        <v>5</v>
-      </c>
-      <c r="M9" s="4">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N9" s="4">
-        <v>10</v>
-      </c>
-      <c r="O9" s="4">
-        <v>1</v>
-      </c>
-      <c r="P9" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4">
-        <v>1</v>
-      </c>
-      <c r="S9" s="4">
-        <v>500</v>
-      </c>
-      <c r="T9" s="8">
-        <v>2</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="8"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
-        <v>1008</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="7">
-        <f t="shared" si="0"/>
-        <v>7.2550000000000002E-5</v>
-      </c>
-      <c r="G10" s="4">
-        <v>150</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I10" s="4">
-        <v>300</v>
-      </c>
-      <c r="J10" s="8">
-        <v>1730</v>
-      </c>
-      <c r="K10" s="7">
-        <v>30</v>
-      </c>
-      <c r="L10" s="4">
-        <v>1</v>
-      </c>
-      <c r="M10" s="4">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N10" s="4">
-        <v>10</v>
-      </c>
-      <c r="O10" s="4">
-        <v>1</v>
-      </c>
-      <c r="P10" s="16">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4">
-        <v>1</v>
-      </c>
-      <c r="S10" s="4">
-        <v>500</v>
-      </c>
-      <c r="T10" s="8">
-        <v>2</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="8"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
-        <v>1009</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" si="0"/>
-        <v>7.2550000000000002E-5</v>
-      </c>
-      <c r="G11" s="4">
-        <v>150</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I11" s="4">
-        <v>300</v>
-      </c>
-      <c r="J11" s="8">
-        <v>1730</v>
-      </c>
-      <c r="K11" s="7">
-        <v>30</v>
-      </c>
-      <c r="L11" s="4">
-        <v>3</v>
-      </c>
-      <c r="M11" s="4">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N11" s="4">
-        <v>10</v>
-      </c>
-      <c r="O11" s="4">
-        <v>1</v>
-      </c>
-      <c r="P11" s="16">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4">
-        <v>1</v>
-      </c>
-      <c r="S11" s="4">
-        <v>500</v>
-      </c>
-      <c r="T11" s="8">
-        <v>2</v>
-      </c>
+      <c r="A11" s="5"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="8"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB11203A-03F4-4237-A17F-5CDC3167DF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21984B77-D213-4B97-A456-B10FEF6EC83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="29">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -5188,7 +5188,7 @@
         <v>28</v>
       </c>
       <c r="F3" s="7">
-        <f t="shared" ref="F3:F5" si="0">(0.0001451)/2</f>
+        <f t="shared" ref="F3:F11" si="0">(0.0001451)/2</f>
         <v>7.2550000000000002E-5</v>
       </c>
       <c r="G3" s="4">
@@ -5231,7 +5231,7 @@
         <v>500</v>
       </c>
       <c r="T3" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -5294,7 +5294,7 @@
         <v>500</v>
       </c>
       <c r="T4" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -5357,140 +5357,386 @@
         <v>500</v>
       </c>
       <c r="T5" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="8"/>
+      <c r="A6" s="5">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>150</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I6" s="4">
+        <v>300</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K6" s="7">
+        <v>30</v>
+      </c>
+      <c r="L6" s="4">
+        <v>5</v>
+      </c>
+      <c r="M6" s="4">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="N6" s="4">
+        <v>10</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1</v>
+      </c>
+      <c r="P6" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>1</v>
+      </c>
+      <c r="S6" s="4">
+        <v>500</v>
+      </c>
+      <c r="T6" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="8"/>
+      <c r="A7" s="5">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G7" s="4">
+        <v>150</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I7" s="4">
+        <v>300</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K7" s="7">
+        <v>30</v>
+      </c>
+      <c r="L7" s="4">
+        <v>5</v>
+      </c>
+      <c r="M7" s="4">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="N7" s="4">
+        <v>10</v>
+      </c>
+      <c r="O7" s="4">
+        <v>1</v>
+      </c>
+      <c r="P7" s="16">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="S7" s="4">
+        <v>500</v>
+      </c>
+      <c r="T7" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="8"/>
+      <c r="A8" s="5">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G8" s="4">
+        <v>150</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I8" s="4">
+        <v>300</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K8" s="7">
+        <v>30</v>
+      </c>
+      <c r="L8" s="4">
+        <v>5</v>
+      </c>
+      <c r="M8" s="4">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="N8" s="4">
+        <v>10</v>
+      </c>
+      <c r="O8" s="4">
+        <v>1</v>
+      </c>
+      <c r="P8" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4">
+        <v>500</v>
+      </c>
+      <c r="T8" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="8"/>
+      <c r="A9" s="5">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G9" s="4">
+        <v>150</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I9" s="4">
+        <v>300</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K9" s="7">
+        <v>30</v>
+      </c>
+      <c r="L9" s="4">
+        <v>7</v>
+      </c>
+      <c r="M9" s="4">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="N9" s="4">
+        <v>10</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1</v>
+      </c>
+      <c r="P9" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
+        <v>1</v>
+      </c>
+      <c r="S9" s="4">
+        <v>500</v>
+      </c>
+      <c r="T9" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="8"/>
+      <c r="A10" s="5">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G10" s="4">
+        <v>150</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I10" s="4">
+        <v>300</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K10" s="7">
+        <v>30</v>
+      </c>
+      <c r="L10" s="4">
+        <v>7</v>
+      </c>
+      <c r="M10" s="4">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="N10" s="4">
+        <v>10</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1</v>
+      </c>
+      <c r="P10" s="16">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4">
+        <v>1</v>
+      </c>
+      <c r="S10" s="4">
+        <v>500</v>
+      </c>
+      <c r="T10" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="8"/>
+      <c r="A11" s="5">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G11" s="4">
+        <v>150</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I11" s="4">
+        <v>300</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K11" s="7">
+        <v>30</v>
+      </c>
+      <c r="L11" s="4">
+        <v>7</v>
+      </c>
+      <c r="M11" s="4">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="N11" s="4">
+        <v>10</v>
+      </c>
+      <c r="O11" s="4">
+        <v>1</v>
+      </c>
+      <c r="P11" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>1</v>
+      </c>
+      <c r="S11" s="4">
+        <v>500</v>
+      </c>
+      <c r="T11" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21984B77-D213-4B97-A456-B10FEF6EC83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F199B0D4-77EB-49BC-B73C-CCB9697E29D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="30">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -114,16 +114,19 @@
     <t>#SIMULATION</t>
   </si>
   <si>
-    <t>0,40; 0,60</t>
-  </si>
-  <si>
     <t>N2;O2;CO2;H2O</t>
   </si>
   <si>
-    <t>Hexano;Octano</t>
+    <t>0,708; 0,00; 0,097; 0,195</t>
   </si>
   <si>
-    <t>0,708; 0,00; 0,097; 0,195</t>
+    <t>Heptano;Hexadecano</t>
+  </si>
+  <si>
+    <t>0,70; 0,30</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -131,9 +134,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +160,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -172,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -377,11 +386,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -441,6 +463,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EF3E57-CE6A-4B11-A29F-455A2AA99755}">
-  <dimension ref="A1:T176"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
@@ -737,18 +762,19 @@
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
@@ -772,15 +798,16 @@
       <c r="M1" s="17"/>
       <c r="N1" s="17"/>
       <c r="O1" s="17"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="19" t="s">
+      <c r="P1" s="17"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="17"/>
       <c r="S1" s="17"/>
-      <c r="T1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T1" s="17"/>
+      <c r="U1" s="18"/>
+    </row>
+    <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -814,52 +841,55 @@
       <c r="K2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" s="7">
-        <f t="shared" ref="F3:F11" si="0">(0.0001451)/2</f>
+        <f t="shared" ref="F3:F13" si="0">(0.0001451)/2</f>
         <v>7.2550000000000002E-5</v>
       </c>
       <c r="G3" s="4">
@@ -869,7 +899,7 @@
         <v>0.15</v>
       </c>
       <c r="I3" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J3" s="8">
         <v>1730</v>
@@ -878,48 +908,51 @@
         <v>30</v>
       </c>
       <c r="L3" s="4">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
         <v>3</v>
       </c>
-      <c r="M3" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N3" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O3" s="4">
         <v>10</v>
       </c>
-      <c r="O3" s="4">
+      <c r="P3" s="4">
         <v>1</v>
       </c>
-      <c r="P3" s="16">
+      <c r="Q3" s="16">
         <v>1E-4</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="R3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <v>1</v>
       </c>
-      <c r="S3" s="4">
+      <c r="T3" s="4">
         <v>500</v>
       </c>
-      <c r="T3" s="8">
+      <c r="U3" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F4" s="7">
         <f t="shared" si="0"/>
@@ -932,7 +965,7 @@
         <v>0.15</v>
       </c>
       <c r="I4" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" s="8">
         <v>1730</v>
@@ -941,48 +974,51 @@
         <v>30</v>
       </c>
       <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
         <v>3</v>
       </c>
-      <c r="M4" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N4" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O4" s="4">
         <v>10</v>
       </c>
-      <c r="O4" s="4">
+      <c r="P4" s="4">
         <v>1</v>
       </c>
-      <c r="P4" s="16">
+      <c r="Q4" s="16">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="R4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="4">
+      <c r="S4" s="4">
         <v>1</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="4">
         <v>500</v>
       </c>
-      <c r="T4" s="8">
+      <c r="U4" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>1003</v>
+        <v>1103</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
@@ -995,7 +1031,7 @@
         <v>0.15</v>
       </c>
       <c r="I5" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J5" s="8">
         <v>1730</v>
@@ -1004,48 +1040,51 @@
         <v>30</v>
       </c>
       <c r="L5" s="4">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
         <v>3</v>
       </c>
-      <c r="M5" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N5" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O5" s="4">
         <v>10</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>1</v>
       </c>
-      <c r="P5" s="16">
+      <c r="Q5" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="R5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <v>1</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="4">
         <v>500</v>
       </c>
-      <c r="T5" s="8">
+      <c r="U5" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>1004</v>
+        <v>1104</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="0"/>
@@ -1058,7 +1097,7 @@
         <v>0.15</v>
       </c>
       <c r="I6" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J6" s="8">
         <v>1730</v>
@@ -1067,48 +1106,51 @@
         <v>30</v>
       </c>
       <c r="L6" s="4">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4">
         <v>5</v>
       </c>
-      <c r="M6" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N6" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O6" s="4">
         <v>10</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>1</v>
       </c>
-      <c r="P6" s="16">
+      <c r="Q6" s="16">
         <v>1E-4</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="R6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>1</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="4">
         <v>500</v>
       </c>
-      <c r="T6" s="8">
+      <c r="U6" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>1005</v>
+        <v>1105</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F7" s="7">
         <f t="shared" si="0"/>
@@ -1121,7 +1163,7 @@
         <v>0.15</v>
       </c>
       <c r="I7" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J7" s="8">
         <v>1730</v>
@@ -1130,48 +1172,51 @@
         <v>30</v>
       </c>
       <c r="L7" s="4">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4">
         <v>5</v>
       </c>
-      <c r="M7" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N7" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O7" s="4">
         <v>10</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>1</v>
       </c>
-      <c r="P7" s="16">
+      <c r="Q7" s="16">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="R7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>1</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="4">
         <v>500</v>
       </c>
-      <c r="T7" s="8">
+      <c r="U7" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>1006</v>
+        <v>1106</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="0"/>
@@ -1184,7 +1229,7 @@
         <v>0.15</v>
       </c>
       <c r="I8" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J8" s="8">
         <v>1730</v>
@@ -1193,48 +1238,51 @@
         <v>30</v>
       </c>
       <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
         <v>5</v>
       </c>
-      <c r="M8" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N8" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O8" s="4">
         <v>10</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>1</v>
       </c>
-      <c r="P8" s="16">
+      <c r="Q8" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="R8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>1</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="4">
         <v>500</v>
       </c>
-      <c r="T8" s="8">
+      <c r="U8" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>1007</v>
+        <v>1107</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
@@ -1247,7 +1295,7 @@
         <v>0.15</v>
       </c>
       <c r="I9" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J9" s="8">
         <v>1730</v>
@@ -1256,48 +1304,51 @@
         <v>30</v>
       </c>
       <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="4">
         <v>7</v>
       </c>
-      <c r="M9" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N9" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O9" s="4">
         <v>10</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>1</v>
       </c>
-      <c r="P9" s="16">
+      <c r="Q9" s="16">
         <v>1E-4</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="R9" s="7">
         <v>0</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <v>1</v>
       </c>
-      <c r="S9" s="4">
+      <c r="T9" s="4">
         <v>500</v>
       </c>
-      <c r="T9" s="8">
+      <c r="U9" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
-        <v>1008</v>
+        <v>1108</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F10" s="7">
         <f t="shared" si="0"/>
@@ -1310,7 +1361,7 @@
         <v>0.15</v>
       </c>
       <c r="I10" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J10" s="8">
         <v>1730</v>
@@ -1319,48 +1370,51 @@
         <v>30</v>
       </c>
       <c r="L10" s="4">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4">
         <v>7</v>
       </c>
-      <c r="M10" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N10" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O10" s="4">
         <v>10</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>1</v>
       </c>
-      <c r="P10" s="16">
+      <c r="Q10" s="16">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="R10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <v>1</v>
       </c>
-      <c r="S10" s="4">
+      <c r="T10" s="4">
         <v>500</v>
       </c>
-      <c r="T10" s="8">
+      <c r="U10" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>1009</v>
+        <v>1109</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="E11" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
@@ -1373,7 +1427,7 @@
         <v>0.15</v>
       </c>
       <c r="I11" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J11" s="8">
         <v>1730</v>
@@ -1382,34 +1436,37 @@
         <v>30</v>
       </c>
       <c r="L11" s="4">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4">
         <v>7</v>
       </c>
-      <c r="M11" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N11" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O11" s="4">
         <v>10</v>
       </c>
-      <c r="O11" s="4">
+      <c r="P11" s="4">
         <v>1</v>
       </c>
-      <c r="P11" s="16">
+      <c r="Q11" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="R11" s="7">
         <v>0</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <v>1</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="4">
         <v>500</v>
       </c>
-      <c r="T11" s="8">
+      <c r="U11" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="7"/>
       <c r="C12" s="4"/>
@@ -1425,35 +1482,80 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="7"/>
       <c r="S12" s="4"/>
-      <c r="T12" s="8"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="8"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T12" s="4"/>
+      <c r="U12" s="8"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>2101</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G13" s="4">
+        <v>150</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I13" s="4">
+        <v>303</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K13" s="7">
+        <v>30</v>
+      </c>
+      <c r="L13" s="4">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4">
+        <v>3</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O13" s="4">
+        <v>10</v>
+      </c>
+      <c r="P13" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4">
+        <v>500</v>
+      </c>
+      <c r="U13" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="7"/>
       <c r="C14" s="4"/>
@@ -1469,13 +1571,14 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="7"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="8"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T14" s="4"/>
+      <c r="U14" s="8"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="7"/>
       <c r="C15" s="4"/>
@@ -1491,13 +1594,14 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="7"/>
       <c r="S15" s="4"/>
-      <c r="T15" s="8"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T15" s="4"/>
+      <c r="U15" s="8"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>
@@ -1513,13 +1617,14 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="7"/>
       <c r="S16" s="4"/>
-      <c r="T16" s="8"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T16" s="4"/>
+      <c r="U16" s="8"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="7"/>
       <c r="C17" s="4"/>
@@ -1535,13 +1640,14 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="7"/>
       <c r="S17" s="4"/>
-      <c r="T17" s="8"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T17" s="4"/>
+      <c r="U17" s="8"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="7"/>
       <c r="C18" s="4"/>
@@ -1557,13 +1663,14 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="7"/>
       <c r="S18" s="4"/>
-      <c r="T18" s="8"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T18" s="4"/>
+      <c r="U18" s="8"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="7"/>
       <c r="C19" s="4"/>
@@ -1579,13 +1686,14 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="7"/>
       <c r="S19" s="4"/>
-      <c r="T19" s="8"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T19" s="4"/>
+      <c r="U19" s="8"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="7"/>
       <c r="C20" s="4"/>
@@ -1601,13 +1709,14 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="7"/>
       <c r="S20" s="4"/>
-      <c r="T20" s="8"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T20" s="4"/>
+      <c r="U20" s="8"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="7"/>
       <c r="C21" s="4"/>
@@ -1623,13 +1732,14 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="7"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="8"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T21" s="4"/>
+      <c r="U21" s="8"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="7"/>
       <c r="C22" s="4"/>
@@ -1645,13 +1755,14 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="7"/>
       <c r="S22" s="4"/>
-      <c r="T22" s="8"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T22" s="4"/>
+      <c r="U22" s="8"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="7"/>
       <c r="C23" s="4"/>
@@ -1667,13 +1778,14 @@
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="7"/>
       <c r="S23" s="4"/>
-      <c r="T23" s="8"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T23" s="4"/>
+      <c r="U23" s="8"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
@@ -1689,13 +1801,14 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="7"/>
       <c r="S24" s="4"/>
-      <c r="T24" s="8"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T24" s="4"/>
+      <c r="U24" s="8"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
@@ -1711,13 +1824,14 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="7"/>
       <c r="S25" s="4"/>
-      <c r="T25" s="8"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T25" s="4"/>
+      <c r="U25" s="8"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="7"/>
       <c r="C26" s="4"/>
@@ -1733,13 +1847,14 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="7"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="8"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T26" s="4"/>
+      <c r="U26" s="8"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="7"/>
       <c r="C27" s="4"/>
@@ -1755,13 +1870,14 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="7"/>
       <c r="S27" s="4"/>
-      <c r="T27" s="8"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T27" s="4"/>
+      <c r="U27" s="8"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="7"/>
       <c r="C28" s="4"/>
@@ -1777,13 +1893,14 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="7"/>
       <c r="S28" s="4"/>
-      <c r="T28" s="8"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T28" s="4"/>
+      <c r="U28" s="8"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
@@ -1799,13 +1916,14 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="7"/>
       <c r="S29" s="4"/>
-      <c r="T29" s="8"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T29" s="4"/>
+      <c r="U29" s="8"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
@@ -1821,13 +1939,14 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="7"/>
       <c r="S30" s="4"/>
-      <c r="T30" s="8"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T30" s="4"/>
+      <c r="U30" s="8"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="7"/>
       <c r="C31" s="4"/>
@@ -1843,13 +1962,14 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="7"/>
       <c r="S31" s="4"/>
-      <c r="T31" s="8"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T31" s="4"/>
+      <c r="U31" s="8"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="7"/>
       <c r="C32" s="4"/>
@@ -1865,13 +1985,14 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="7"/>
       <c r="S32" s="4"/>
-      <c r="T32" s="8"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T32" s="4"/>
+      <c r="U32" s="8"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="7"/>
       <c r="C33" s="4"/>
@@ -1887,13 +2008,14 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="7"/>
       <c r="S33" s="4"/>
-      <c r="T33" s="8"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T33" s="4"/>
+      <c r="U33" s="8"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="7"/>
       <c r="C34" s="4"/>
@@ -1909,13 +2031,14 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="7"/>
       <c r="S34" s="4"/>
-      <c r="T34" s="8"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T34" s="4"/>
+      <c r="U34" s="8"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="7"/>
       <c r="C35" s="4"/>
@@ -1931,13 +2054,14 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="7"/>
       <c r="S35" s="4"/>
-      <c r="T35" s="8"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T35" s="4"/>
+      <c r="U35" s="8"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="7"/>
       <c r="C36" s="4"/>
@@ -1953,13 +2077,14 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="7"/>
       <c r="S36" s="4"/>
-      <c r="T36" s="8"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T36" s="4"/>
+      <c r="U36" s="8"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="7"/>
       <c r="C37" s="4"/>
@@ -1975,13 +2100,14 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="7"/>
       <c r="S37" s="4"/>
-      <c r="T37" s="8"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T37" s="4"/>
+      <c r="U37" s="8"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="7"/>
       <c r="C38" s="4"/>
@@ -1997,13 +2123,14 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="7"/>
       <c r="S38" s="4"/>
-      <c r="T38" s="8"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T38" s="4"/>
+      <c r="U38" s="8"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="7"/>
       <c r="C39" s="4"/>
@@ -2019,13 +2146,14 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="7"/>
       <c r="S39" s="4"/>
-      <c r="T39" s="8"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T39" s="4"/>
+      <c r="U39" s="8"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="7"/>
       <c r="C40" s="4"/>
@@ -2041,13 +2169,14 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="7"/>
       <c r="S40" s="4"/>
-      <c r="T40" s="8"/>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T40" s="4"/>
+      <c r="U40" s="8"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="7"/>
       <c r="C41" s="4"/>
@@ -2063,13 +2192,14 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="7"/>
       <c r="S41" s="4"/>
-      <c r="T41" s="8"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T41" s="4"/>
+      <c r="U41" s="8"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="7"/>
       <c r="C42" s="4"/>
@@ -2085,13 +2215,14 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="7"/>
       <c r="S42" s="4"/>
-      <c r="T42" s="8"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T42" s="4"/>
+      <c r="U42" s="8"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="7"/>
       <c r="C43" s="4"/>
@@ -2107,13 +2238,14 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="7"/>
       <c r="S43" s="4"/>
-      <c r="T43" s="8"/>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T43" s="4"/>
+      <c r="U43" s="8"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="7"/>
       <c r="C44" s="4"/>
@@ -2129,13 +2261,14 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="7"/>
       <c r="S44" s="4"/>
-      <c r="T44" s="8"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T44" s="4"/>
+      <c r="U44" s="8"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="7"/>
       <c r="C45" s="4"/>
@@ -2151,13 +2284,14 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="7"/>
       <c r="S45" s="4"/>
-      <c r="T45" s="8"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T45" s="4"/>
+      <c r="U45" s="8"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="7"/>
       <c r="C46" s="4"/>
@@ -2173,13 +2307,14 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="7"/>
       <c r="S46" s="4"/>
-      <c r="T46" s="8"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T46" s="4"/>
+      <c r="U46" s="8"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="7"/>
       <c r="C47" s="4"/>
@@ -2195,13 +2330,14 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="7"/>
       <c r="S47" s="4"/>
-      <c r="T47" s="8"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T47" s="4"/>
+      <c r="U47" s="8"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="7"/>
       <c r="C48" s="4"/>
@@ -2217,13 +2353,14 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="7"/>
       <c r="S48" s="4"/>
-      <c r="T48" s="8"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T48" s="4"/>
+      <c r="U48" s="8"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="7"/>
       <c r="C49" s="4"/>
@@ -2239,13 +2376,14 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="8"/>
+      <c r="R49" s="7"/>
       <c r="S49" s="4"/>
-      <c r="T49" s="8"/>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T49" s="4"/>
+      <c r="U49" s="8"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="7"/>
       <c r="C50" s="4"/>
@@ -2261,13 +2399,14 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="7"/>
       <c r="S50" s="4"/>
-      <c r="T50" s="8"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T50" s="4"/>
+      <c r="U50" s="8"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="7"/>
       <c r="C51" s="4"/>
@@ -2283,13 +2422,14 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="7"/>
       <c r="S51" s="4"/>
-      <c r="T51" s="8"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T51" s="4"/>
+      <c r="U51" s="8"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="7"/>
       <c r="C52" s="4"/>
@@ -2305,13 +2445,14 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="7"/>
       <c r="S52" s="4"/>
-      <c r="T52" s="8"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T52" s="4"/>
+      <c r="U52" s="8"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="7"/>
       <c r="C53" s="4"/>
@@ -2327,13 +2468,14 @@
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="8"/>
+      <c r="R53" s="7"/>
       <c r="S53" s="4"/>
-      <c r="T53" s="8"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T53" s="4"/>
+      <c r="U53" s="8"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="7"/>
       <c r="C54" s="4"/>
@@ -2349,13 +2491,14 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="7"/>
       <c r="S54" s="4"/>
-      <c r="T54" s="8"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T54" s="4"/>
+      <c r="U54" s="8"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="7"/>
       <c r="C55" s="4"/>
@@ -2371,13 +2514,14 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="7"/>
       <c r="S55" s="4"/>
-      <c r="T55" s="8"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T55" s="4"/>
+      <c r="U55" s="8"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="7"/>
       <c r="C56" s="4"/>
@@ -2393,13 +2537,14 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="7"/>
-      <c r="R56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="7"/>
       <c r="S56" s="4"/>
-      <c r="T56" s="8"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T56" s="4"/>
+      <c r="U56" s="8"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="7"/>
       <c r="C57" s="4"/>
@@ -2415,13 +2560,14 @@
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="7"/>
-      <c r="R57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="7"/>
       <c r="S57" s="4"/>
-      <c r="T57" s="8"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T57" s="4"/>
+      <c r="U57" s="8"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="7"/>
       <c r="C58" s="4"/>
@@ -2437,13 +2583,14 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="7"/>
       <c r="S58" s="4"/>
-      <c r="T58" s="8"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T58" s="4"/>
+      <c r="U58" s="8"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="7"/>
       <c r="C59" s="4"/>
@@ -2459,13 +2606,14 @@
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="8"/>
+      <c r="R59" s="7"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="8"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T59" s="4"/>
+      <c r="U59" s="8"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="7"/>
       <c r="C60" s="4"/>
@@ -2481,13 +2629,14 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="7"/>
-      <c r="R60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="8"/>
+      <c r="R60" s="7"/>
       <c r="S60" s="4"/>
-      <c r="T60" s="8"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T60" s="4"/>
+      <c r="U60" s="8"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="7"/>
       <c r="C61" s="4"/>
@@ -2503,13 +2652,14 @@
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="8"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="7"/>
       <c r="S61" s="4"/>
-      <c r="T61" s="8"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T61" s="4"/>
+      <c r="U61" s="8"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="7"/>
       <c r="C62" s="4"/>
@@ -2525,13 +2675,14 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="7"/>
       <c r="S62" s="4"/>
-      <c r="T62" s="8"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T62" s="4"/>
+      <c r="U62" s="8"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="7"/>
       <c r="C63" s="4"/>
@@ -2547,13 +2698,14 @@
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
-      <c r="P63" s="8"/>
-      <c r="Q63" s="7"/>
-      <c r="R63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="8"/>
+      <c r="R63" s="7"/>
       <c r="S63" s="4"/>
-      <c r="T63" s="8"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T63" s="4"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="7"/>
       <c r="C64" s="4"/>
@@ -2569,13 +2721,14 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="8"/>
+      <c r="R64" s="7"/>
       <c r="S64" s="4"/>
-      <c r="T64" s="8"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T64" s="4"/>
+      <c r="U64" s="8"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="7"/>
       <c r="C65" s="4"/>
@@ -2591,13 +2744,14 @@
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
-      <c r="P65" s="8"/>
-      <c r="Q65" s="7"/>
-      <c r="R65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="8"/>
+      <c r="R65" s="7"/>
       <c r="S65" s="4"/>
-      <c r="T65" s="8"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T65" s="4"/>
+      <c r="U65" s="8"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="7"/>
       <c r="C66" s="4"/>
@@ -2613,13 +2767,14 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="7"/>
-      <c r="R66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="8"/>
+      <c r="R66" s="7"/>
       <c r="S66" s="4"/>
-      <c r="T66" s="8"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T66" s="4"/>
+      <c r="U66" s="8"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="7"/>
       <c r="C67" s="4"/>
@@ -2635,13 +2790,14 @@
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
-      <c r="P67" s="8"/>
-      <c r="Q67" s="7"/>
-      <c r="R67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="7"/>
       <c r="S67" s="4"/>
-      <c r="T67" s="8"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T67" s="4"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="7"/>
       <c r="C68" s="4"/>
@@ -2657,13 +2813,14 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="7"/>
-      <c r="R68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="8"/>
+      <c r="R68" s="7"/>
       <c r="S68" s="4"/>
-      <c r="T68" s="8"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T68" s="4"/>
+      <c r="U68" s="8"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="7"/>
       <c r="C69" s="4"/>
@@ -2679,13 +2836,14 @@
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
-      <c r="P69" s="8"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="8"/>
+      <c r="R69" s="7"/>
       <c r="S69" s="4"/>
-      <c r="T69" s="8"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T69" s="4"/>
+      <c r="U69" s="8"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="7"/>
       <c r="C70" s="4"/>
@@ -2701,13 +2859,14 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="8"/>
+      <c r="R70" s="7"/>
       <c r="S70" s="4"/>
-      <c r="T70" s="8"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T70" s="4"/>
+      <c r="U70" s="8"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="7"/>
       <c r="C71" s="4"/>
@@ -2723,13 +2882,14 @@
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="7"/>
-      <c r="R71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="8"/>
+      <c r="R71" s="7"/>
       <c r="S71" s="4"/>
-      <c r="T71" s="8"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T71" s="4"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="7"/>
       <c r="C72" s="4"/>
@@ -2745,13 +2905,14 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="7"/>
-      <c r="R72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="8"/>
+      <c r="R72" s="7"/>
       <c r="S72" s="4"/>
-      <c r="T72" s="8"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T72" s="4"/>
+      <c r="U72" s="8"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="7"/>
       <c r="C73" s="4"/>
@@ -2767,13 +2928,14 @@
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="7"/>
-      <c r="R73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="8"/>
+      <c r="R73" s="7"/>
       <c r="S73" s="4"/>
-      <c r="T73" s="8"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T73" s="4"/>
+      <c r="U73" s="8"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="7"/>
       <c r="C74" s="4"/>
@@ -2789,13 +2951,14 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="8"/>
+      <c r="R74" s="7"/>
       <c r="S74" s="4"/>
-      <c r="T74" s="8"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T74" s="4"/>
+      <c r="U74" s="8"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="7"/>
       <c r="C75" s="4"/>
@@ -2811,13 +2974,14 @@
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
-      <c r="P75" s="8"/>
-      <c r="Q75" s="7"/>
-      <c r="R75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="8"/>
+      <c r="R75" s="7"/>
       <c r="S75" s="4"/>
-      <c r="T75" s="8"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T75" s="4"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="7"/>
       <c r="C76" s="4"/>
@@ -2833,13 +2997,14 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="7"/>
-      <c r="R76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="8"/>
+      <c r="R76" s="7"/>
       <c r="S76" s="4"/>
-      <c r="T76" s="8"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T76" s="4"/>
+      <c r="U76" s="8"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="7"/>
       <c r="C77" s="4"/>
@@ -2855,13 +3020,14 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
-      <c r="P77" s="8"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="8"/>
+      <c r="R77" s="7"/>
       <c r="S77" s="4"/>
-      <c r="T77" s="8"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T77" s="4"/>
+      <c r="U77" s="8"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="7"/>
       <c r="C78" s="4"/>
@@ -2877,13 +3043,14 @@
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
-      <c r="P78" s="8"/>
-      <c r="Q78" s="7"/>
-      <c r="R78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="7"/>
       <c r="S78" s="4"/>
-      <c r="T78" s="8"/>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T78" s="4"/>
+      <c r="U78" s="8"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="7"/>
       <c r="C79" s="4"/>
@@ -2899,13 +3066,14 @@
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="7"/>
-      <c r="R79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="8"/>
+      <c r="R79" s="7"/>
       <c r="S79" s="4"/>
-      <c r="T79" s="8"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T79" s="4"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="7"/>
       <c r="C80" s="4"/>
@@ -2921,13 +3089,14 @@
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="8"/>
+      <c r="R80" s="7"/>
       <c r="S80" s="4"/>
-      <c r="T80" s="8"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T80" s="4"/>
+      <c r="U80" s="8"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="7"/>
       <c r="C81" s="4"/>
@@ -2943,13 +3112,14 @@
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="8"/>
+      <c r="R81" s="7"/>
       <c r="S81" s="4"/>
-      <c r="T81" s="8"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T81" s="4"/>
+      <c r="U81" s="8"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="7"/>
       <c r="C82" s="4"/>
@@ -2965,13 +3135,14 @@
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="7"/>
-      <c r="R82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="8"/>
+      <c r="R82" s="7"/>
       <c r="S82" s="4"/>
-      <c r="T82" s="8"/>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T82" s="4"/>
+      <c r="U82" s="8"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
       <c r="B83" s="7"/>
       <c r="C83" s="4"/>
@@ -2987,13 +3158,14 @@
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="7"/>
-      <c r="R83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="8"/>
+      <c r="R83" s="7"/>
       <c r="S83" s="4"/>
-      <c r="T83" s="8"/>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T83" s="4"/>
+      <c r="U83" s="8"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="7"/>
       <c r="C84" s="4"/>
@@ -3009,13 +3181,14 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="7"/>
-      <c r="R84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="8"/>
+      <c r="R84" s="7"/>
       <c r="S84" s="4"/>
-      <c r="T84" s="8"/>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T84" s="4"/>
+      <c r="U84" s="8"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="7"/>
       <c r="C85" s="4"/>
@@ -3031,13 +3204,14 @@
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="7"/>
-      <c r="R85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="8"/>
+      <c r="R85" s="7"/>
       <c r="S85" s="4"/>
-      <c r="T85" s="8"/>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T85" s="4"/>
+      <c r="U85" s="8"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="7"/>
       <c r="C86" s="4"/>
@@ -3053,13 +3227,14 @@
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
-      <c r="P86" s="8"/>
-      <c r="Q86" s="7"/>
-      <c r="R86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="8"/>
+      <c r="R86" s="7"/>
       <c r="S86" s="4"/>
-      <c r="T86" s="8"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T86" s="4"/>
+      <c r="U86" s="8"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="7"/>
       <c r="C87" s="4"/>
@@ -3075,13 +3250,14 @@
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="7"/>
-      <c r="R87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="8"/>
+      <c r="R87" s="7"/>
       <c r="S87" s="4"/>
-      <c r="T87" s="8"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T87" s="4"/>
+      <c r="U87" s="8"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
       <c r="B88" s="7"/>
       <c r="C88" s="4"/>
@@ -3097,13 +3273,14 @@
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
-      <c r="P88" s="8"/>
-      <c r="Q88" s="7"/>
-      <c r="R88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="8"/>
+      <c r="R88" s="7"/>
       <c r="S88" s="4"/>
-      <c r="T88" s="8"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T88" s="4"/>
+      <c r="U88" s="8"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="7"/>
       <c r="C89" s="4"/>
@@ -3119,13 +3296,14 @@
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
-      <c r="P89" s="8"/>
-      <c r="Q89" s="7"/>
-      <c r="R89" s="4"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="8"/>
+      <c r="R89" s="7"/>
       <c r="S89" s="4"/>
-      <c r="T89" s="8"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T89" s="4"/>
+      <c r="U89" s="8"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
       <c r="B90" s="7"/>
       <c r="C90" s="4"/>
@@ -3141,13 +3319,14 @@
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
-      <c r="P90" s="8"/>
-      <c r="Q90" s="7"/>
-      <c r="R90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="8"/>
+      <c r="R90" s="7"/>
       <c r="S90" s="4"/>
-      <c r="T90" s="8"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T90" s="4"/>
+      <c r="U90" s="8"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="7"/>
       <c r="C91" s="4"/>
@@ -3163,13 +3342,14 @@
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
-      <c r="P91" s="8"/>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="8"/>
+      <c r="R91" s="7"/>
       <c r="S91" s="4"/>
-      <c r="T91" s="8"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T91" s="4"/>
+      <c r="U91" s="8"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
       <c r="B92" s="7"/>
       <c r="C92" s="4"/>
@@ -3185,13 +3365,14 @@
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
-      <c r="P92" s="8"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="8"/>
+      <c r="R92" s="7"/>
       <c r="S92" s="4"/>
-      <c r="T92" s="8"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T92" s="4"/>
+      <c r="U92" s="8"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="7"/>
       <c r="C93" s="4"/>
@@ -3207,13 +3388,14 @@
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
-      <c r="P93" s="8"/>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="8"/>
+      <c r="R93" s="7"/>
       <c r="S93" s="4"/>
-      <c r="T93" s="8"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T93" s="4"/>
+      <c r="U93" s="8"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="7"/>
       <c r="C94" s="4"/>
@@ -3229,13 +3411,14 @@
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
-      <c r="P94" s="8"/>
-      <c r="Q94" s="7"/>
-      <c r="R94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="8"/>
+      <c r="R94" s="7"/>
       <c r="S94" s="4"/>
-      <c r="T94" s="8"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T94" s="4"/>
+      <c r="U94" s="8"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
       <c r="B95" s="7"/>
       <c r="C95" s="4"/>
@@ -3251,13 +3434,14 @@
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
-      <c r="P95" s="8"/>
-      <c r="Q95" s="7"/>
-      <c r="R95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="8"/>
+      <c r="R95" s="7"/>
       <c r="S95" s="4"/>
-      <c r="T95" s="8"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T95" s="4"/>
+      <c r="U95" s="8"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
       <c r="B96" s="7"/>
       <c r="C96" s="4"/>
@@ -3273,13 +3457,14 @@
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
-      <c r="P96" s="8"/>
-      <c r="Q96" s="7"/>
-      <c r="R96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="8"/>
+      <c r="R96" s="7"/>
       <c r="S96" s="4"/>
-      <c r="T96" s="8"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T96" s="4"/>
+      <c r="U96" s="8"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
       <c r="B97" s="7"/>
       <c r="C97" s="4"/>
@@ -3295,13 +3480,14 @@
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
-      <c r="P97" s="8"/>
-      <c r="Q97" s="7"/>
-      <c r="R97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="8"/>
+      <c r="R97" s="7"/>
       <c r="S97" s="4"/>
-      <c r="T97" s="8"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T97" s="4"/>
+      <c r="U97" s="8"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="7"/>
       <c r="C98" s="4"/>
@@ -3317,13 +3503,14 @@
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
-      <c r="P98" s="8"/>
-      <c r="Q98" s="7"/>
-      <c r="R98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="8"/>
+      <c r="R98" s="7"/>
       <c r="S98" s="4"/>
-      <c r="T98" s="8"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T98" s="4"/>
+      <c r="U98" s="8"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="7"/>
       <c r="C99" s="4"/>
@@ -3339,13 +3526,14 @@
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
-      <c r="P99" s="8"/>
-      <c r="Q99" s="7"/>
-      <c r="R99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="8"/>
+      <c r="R99" s="7"/>
       <c r="S99" s="4"/>
-      <c r="T99" s="8"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T99" s="4"/>
+      <c r="U99" s="8"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
       <c r="B100" s="7"/>
       <c r="C100" s="4"/>
@@ -3361,13 +3549,14 @@
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
-      <c r="P100" s="8"/>
-      <c r="Q100" s="7"/>
-      <c r="R100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="8"/>
+      <c r="R100" s="7"/>
       <c r="S100" s="4"/>
-      <c r="T100" s="8"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T100" s="4"/>
+      <c r="U100" s="8"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
       <c r="B101" s="7"/>
       <c r="C101" s="4"/>
@@ -3383,13 +3572,14 @@
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
-      <c r="P101" s="8"/>
-      <c r="Q101" s="7"/>
-      <c r="R101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="8"/>
+      <c r="R101" s="7"/>
       <c r="S101" s="4"/>
-      <c r="T101" s="8"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T101" s="4"/>
+      <c r="U101" s="8"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
       <c r="B102" s="7"/>
       <c r="C102" s="4"/>
@@ -3405,13 +3595,14 @@
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
-      <c r="P102" s="8"/>
-      <c r="Q102" s="7"/>
-      <c r="R102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="8"/>
+      <c r="R102" s="7"/>
       <c r="S102" s="4"/>
-      <c r="T102" s="8"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T102" s="4"/>
+      <c r="U102" s="8"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
       <c r="B103" s="7"/>
       <c r="C103" s="4"/>
@@ -3427,13 +3618,14 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
-      <c r="P103" s="8"/>
-      <c r="Q103" s="7"/>
-      <c r="R103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="8"/>
+      <c r="R103" s="7"/>
       <c r="S103" s="4"/>
-      <c r="T103" s="8"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T103" s="4"/>
+      <c r="U103" s="8"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
       <c r="B104" s="7"/>
       <c r="C104" s="4"/>
@@ -3449,13 +3641,14 @@
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
-      <c r="P104" s="8"/>
-      <c r="Q104" s="7"/>
-      <c r="R104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="8"/>
+      <c r="R104" s="7"/>
       <c r="S104" s="4"/>
-      <c r="T104" s="8"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T104" s="4"/>
+      <c r="U104" s="8"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
       <c r="B105" s="7"/>
       <c r="C105" s="4"/>
@@ -3471,13 +3664,14 @@
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
-      <c r="P105" s="8"/>
-      <c r="Q105" s="7"/>
-      <c r="R105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="8"/>
+      <c r="R105" s="7"/>
       <c r="S105" s="4"/>
-      <c r="T105" s="8"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T105" s="4"/>
+      <c r="U105" s="8"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
       <c r="B106" s="7"/>
       <c r="C106" s="4"/>
@@ -3493,13 +3687,14 @@
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
-      <c r="P106" s="8"/>
-      <c r="Q106" s="7"/>
-      <c r="R106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="8"/>
+      <c r="R106" s="7"/>
       <c r="S106" s="4"/>
-      <c r="T106" s="8"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T106" s="4"/>
+      <c r="U106" s="8"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
       <c r="B107" s="7"/>
       <c r="C107" s="4"/>
@@ -3515,13 +3710,14 @@
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
-      <c r="P107" s="8"/>
-      <c r="Q107" s="7"/>
-      <c r="R107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="8"/>
+      <c r="R107" s="7"/>
       <c r="S107" s="4"/>
-      <c r="T107" s="8"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T107" s="4"/>
+      <c r="U107" s="8"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="7"/>
       <c r="C108" s="4"/>
@@ -3537,13 +3733,14 @@
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
-      <c r="P108" s="8"/>
-      <c r="Q108" s="7"/>
-      <c r="R108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="8"/>
+      <c r="R108" s="7"/>
       <c r="S108" s="4"/>
-      <c r="T108" s="8"/>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T108" s="4"/>
+      <c r="U108" s="8"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
       <c r="B109" s="7"/>
       <c r="C109" s="4"/>
@@ -3559,13 +3756,14 @@
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
-      <c r="P109" s="8"/>
-      <c r="Q109" s="7"/>
-      <c r="R109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="8"/>
+      <c r="R109" s="7"/>
       <c r="S109" s="4"/>
-      <c r="T109" s="8"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T109" s="4"/>
+      <c r="U109" s="8"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
       <c r="B110" s="7"/>
       <c r="C110" s="4"/>
@@ -3581,13 +3779,14 @@
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
-      <c r="P110" s="8"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="8"/>
+      <c r="R110" s="7"/>
       <c r="S110" s="4"/>
-      <c r="T110" s="8"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T110" s="4"/>
+      <c r="U110" s="8"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
       <c r="B111" s="7"/>
       <c r="C111" s="4"/>
@@ -3603,13 +3802,14 @@
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
-      <c r="P111" s="8"/>
-      <c r="Q111" s="7"/>
-      <c r="R111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="8"/>
+      <c r="R111" s="7"/>
       <c r="S111" s="4"/>
-      <c r="T111" s="8"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T111" s="4"/>
+      <c r="U111" s="8"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="7"/>
       <c r="C112" s="4"/>
@@ -3625,13 +3825,14 @@
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
-      <c r="P112" s="8"/>
-      <c r="Q112" s="7"/>
-      <c r="R112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="8"/>
+      <c r="R112" s="7"/>
       <c r="S112" s="4"/>
-      <c r="T112" s="8"/>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T112" s="4"/>
+      <c r="U112" s="8"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
       <c r="B113" s="7"/>
       <c r="C113" s="4"/>
@@ -3647,13 +3848,14 @@
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
-      <c r="P113" s="8"/>
-      <c r="Q113" s="7"/>
-      <c r="R113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="8"/>
+      <c r="R113" s="7"/>
       <c r="S113" s="4"/>
-      <c r="T113" s="8"/>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T113" s="4"/>
+      <c r="U113" s="8"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
       <c r="B114" s="7"/>
       <c r="C114" s="4"/>
@@ -3669,13 +3871,14 @@
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
-      <c r="P114" s="8"/>
-      <c r="Q114" s="7"/>
-      <c r="R114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="8"/>
+      <c r="R114" s="7"/>
       <c r="S114" s="4"/>
-      <c r="T114" s="8"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T114" s="4"/>
+      <c r="U114" s="8"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
       <c r="B115" s="7"/>
       <c r="C115" s="4"/>
@@ -3691,13 +3894,14 @@
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
-      <c r="P115" s="8"/>
-      <c r="Q115" s="7"/>
-      <c r="R115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="7"/>
       <c r="S115" s="4"/>
-      <c r="T115" s="8"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T115" s="4"/>
+      <c r="U115" s="8"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
       <c r="B116" s="7"/>
       <c r="C116" s="4"/>
@@ -3713,13 +3917,14 @@
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
-      <c r="P116" s="8"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="8"/>
+      <c r="R116" s="7"/>
       <c r="S116" s="4"/>
-      <c r="T116" s="8"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T116" s="4"/>
+      <c r="U116" s="8"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
       <c r="B117" s="7"/>
       <c r="C117" s="4"/>
@@ -3735,13 +3940,14 @@
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
-      <c r="P117" s="8"/>
-      <c r="Q117" s="7"/>
-      <c r="R117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="8"/>
+      <c r="R117" s="7"/>
       <c r="S117" s="4"/>
-      <c r="T117" s="8"/>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T117" s="4"/>
+      <c r="U117" s="8"/>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
       <c r="B118" s="7"/>
       <c r="C118" s="4"/>
@@ -3757,13 +3963,14 @@
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
-      <c r="P118" s="8"/>
-      <c r="Q118" s="7"/>
-      <c r="R118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="8"/>
+      <c r="R118" s="7"/>
       <c r="S118" s="4"/>
-      <c r="T118" s="8"/>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T118" s="4"/>
+      <c r="U118" s="8"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
       <c r="B119" s="7"/>
       <c r="C119" s="4"/>
@@ -3779,13 +3986,14 @@
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
-      <c r="P119" s="8"/>
-      <c r="Q119" s="7"/>
-      <c r="R119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="8"/>
+      <c r="R119" s="7"/>
       <c r="S119" s="4"/>
-      <c r="T119" s="8"/>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T119" s="4"/>
+      <c r="U119" s="8"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="7"/>
       <c r="C120" s="4"/>
@@ -3801,13 +4009,14 @@
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
-      <c r="P120" s="8"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="8"/>
+      <c r="R120" s="7"/>
       <c r="S120" s="4"/>
-      <c r="T120" s="8"/>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T120" s="4"/>
+      <c r="U120" s="8"/>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="7"/>
       <c r="C121" s="4"/>
@@ -3823,13 +4032,14 @@
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
-      <c r="P121" s="8"/>
-      <c r="Q121" s="7"/>
-      <c r="R121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="8"/>
+      <c r="R121" s="7"/>
       <c r="S121" s="4"/>
-      <c r="T121" s="8"/>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T121" s="4"/>
+      <c r="U121" s="8"/>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="7"/>
       <c r="C122" s="4"/>
@@ -3845,13 +4055,14 @@
       <c r="M122" s="4"/>
       <c r="N122" s="4"/>
       <c r="O122" s="4"/>
-      <c r="P122" s="8"/>
-      <c r="Q122" s="7"/>
-      <c r="R122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="8"/>
+      <c r="R122" s="7"/>
       <c r="S122" s="4"/>
-      <c r="T122" s="8"/>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T122" s="4"/>
+      <c r="U122" s="8"/>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="7"/>
       <c r="C123" s="4"/>
@@ -3867,13 +4078,14 @@
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
       <c r="O123" s="4"/>
-      <c r="P123" s="8"/>
-      <c r="Q123" s="7"/>
-      <c r="R123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="8"/>
+      <c r="R123" s="7"/>
       <c r="S123" s="4"/>
-      <c r="T123" s="8"/>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T123" s="4"/>
+      <c r="U123" s="8"/>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
       <c r="B124" s="7"/>
       <c r="C124" s="4"/>
@@ -3889,13 +4101,14 @@
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
       <c r="O124" s="4"/>
-      <c r="P124" s="8"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="8"/>
+      <c r="R124" s="7"/>
       <c r="S124" s="4"/>
-      <c r="T124" s="8"/>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T124" s="4"/>
+      <c r="U124" s="8"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
       <c r="B125" s="7"/>
       <c r="C125" s="4"/>
@@ -3911,13 +4124,14 @@
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
       <c r="O125" s="4"/>
-      <c r="P125" s="8"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="4"/>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="8"/>
+      <c r="R125" s="7"/>
       <c r="S125" s="4"/>
-      <c r="T125" s="8"/>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T125" s="4"/>
+      <c r="U125" s="8"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="7"/>
       <c r="C126" s="4"/>
@@ -3933,13 +4147,14 @@
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
       <c r="O126" s="4"/>
-      <c r="P126" s="8"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="4"/>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="8"/>
+      <c r="R126" s="7"/>
       <c r="S126" s="4"/>
-      <c r="T126" s="8"/>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T126" s="4"/>
+      <c r="U126" s="8"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="7"/>
       <c r="C127" s="4"/>
@@ -3955,13 +4170,14 @@
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
       <c r="O127" s="4"/>
-      <c r="P127" s="8"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="4"/>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="8"/>
+      <c r="R127" s="7"/>
       <c r="S127" s="4"/>
-      <c r="T127" s="8"/>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T127" s="4"/>
+      <c r="U127" s="8"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="7"/>
       <c r="C128" s="4"/>
@@ -3977,13 +4193,14 @@
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
       <c r="O128" s="4"/>
-      <c r="P128" s="8"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="4"/>
+      <c r="P128" s="4"/>
+      <c r="Q128" s="8"/>
+      <c r="R128" s="7"/>
       <c r="S128" s="4"/>
-      <c r="T128" s="8"/>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T128" s="4"/>
+      <c r="U128" s="8"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
       <c r="B129" s="7"/>
       <c r="C129" s="4"/>
@@ -3999,13 +4216,14 @@
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
       <c r="O129" s="4"/>
-      <c r="P129" s="8"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="8"/>
+      <c r="R129" s="7"/>
       <c r="S129" s="4"/>
-      <c r="T129" s="8"/>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T129" s="4"/>
+      <c r="U129" s="8"/>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="7"/>
       <c r="C130" s="4"/>
@@ -4021,13 +4239,14 @@
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
       <c r="O130" s="4"/>
-      <c r="P130" s="8"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="4"/>
+      <c r="P130" s="4"/>
+      <c r="Q130" s="8"/>
+      <c r="R130" s="7"/>
       <c r="S130" s="4"/>
-      <c r="T130" s="8"/>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T130" s="4"/>
+      <c r="U130" s="8"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
       <c r="B131" s="7"/>
       <c r="C131" s="4"/>
@@ -4043,13 +4262,14 @@
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
       <c r="O131" s="4"/>
-      <c r="P131" s="8"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="4"/>
+      <c r="P131" s="4"/>
+      <c r="Q131" s="8"/>
+      <c r="R131" s="7"/>
       <c r="S131" s="4"/>
-      <c r="T131" s="8"/>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T131" s="4"/>
+      <c r="U131" s="8"/>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
       <c r="B132" s="7"/>
       <c r="C132" s="4"/>
@@ -4065,13 +4285,14 @@
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
       <c r="O132" s="4"/>
-      <c r="P132" s="8"/>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="4"/>
+      <c r="P132" s="4"/>
+      <c r="Q132" s="8"/>
+      <c r="R132" s="7"/>
       <c r="S132" s="4"/>
-      <c r="T132" s="8"/>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T132" s="4"/>
+      <c r="U132" s="8"/>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
       <c r="B133" s="7"/>
       <c r="C133" s="4"/>
@@ -4087,13 +4308,14 @@
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
       <c r="O133" s="4"/>
-      <c r="P133" s="8"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="4"/>
+      <c r="P133" s="4"/>
+      <c r="Q133" s="8"/>
+      <c r="R133" s="7"/>
       <c r="S133" s="4"/>
-      <c r="T133" s="8"/>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T133" s="4"/>
+      <c r="U133" s="8"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
       <c r="B134" s="7"/>
       <c r="C134" s="4"/>
@@ -4109,13 +4331,14 @@
       <c r="M134" s="4"/>
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
-      <c r="P134" s="8"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="4"/>
+      <c r="P134" s="4"/>
+      <c r="Q134" s="8"/>
+      <c r="R134" s="7"/>
       <c r="S134" s="4"/>
-      <c r="T134" s="8"/>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T134" s="4"/>
+      <c r="U134" s="8"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="7"/>
       <c r="C135" s="4"/>
@@ -4131,13 +4354,14 @@
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
       <c r="O135" s="4"/>
-      <c r="P135" s="8"/>
-      <c r="Q135" s="7"/>
-      <c r="R135" s="4"/>
+      <c r="P135" s="4"/>
+      <c r="Q135" s="8"/>
+      <c r="R135" s="7"/>
       <c r="S135" s="4"/>
-      <c r="T135" s="8"/>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T135" s="4"/>
+      <c r="U135" s="8"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="7"/>
       <c r="C136" s="4"/>
@@ -4153,13 +4377,14 @@
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
       <c r="O136" s="4"/>
-      <c r="P136" s="8"/>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="4"/>
+      <c r="P136" s="4"/>
+      <c r="Q136" s="8"/>
+      <c r="R136" s="7"/>
       <c r="S136" s="4"/>
-      <c r="T136" s="8"/>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T136" s="4"/>
+      <c r="U136" s="8"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="7"/>
       <c r="C137" s="4"/>
@@ -4175,13 +4400,14 @@
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
       <c r="O137" s="4"/>
-      <c r="P137" s="8"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="4"/>
+      <c r="P137" s="4"/>
+      <c r="Q137" s="8"/>
+      <c r="R137" s="7"/>
       <c r="S137" s="4"/>
-      <c r="T137" s="8"/>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T137" s="4"/>
+      <c r="U137" s="8"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="7"/>
       <c r="C138" s="4"/>
@@ -4197,13 +4423,14 @@
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
-      <c r="P138" s="8"/>
-      <c r="Q138" s="7"/>
-      <c r="R138" s="4"/>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="8"/>
+      <c r="R138" s="7"/>
       <c r="S138" s="4"/>
-      <c r="T138" s="8"/>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T138" s="4"/>
+      <c r="U138" s="8"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="7"/>
       <c r="C139" s="4"/>
@@ -4219,13 +4446,14 @@
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
-      <c r="P139" s="8"/>
-      <c r="Q139" s="7"/>
-      <c r="R139" s="4"/>
+      <c r="P139" s="4"/>
+      <c r="Q139" s="8"/>
+      <c r="R139" s="7"/>
       <c r="S139" s="4"/>
-      <c r="T139" s="8"/>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T139" s="4"/>
+      <c r="U139" s="8"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="7"/>
       <c r="C140" s="4"/>
@@ -4241,13 +4469,14 @@
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
       <c r="O140" s="4"/>
-      <c r="P140" s="8"/>
-      <c r="Q140" s="7"/>
-      <c r="R140" s="4"/>
+      <c r="P140" s="4"/>
+      <c r="Q140" s="8"/>
+      <c r="R140" s="7"/>
       <c r="S140" s="4"/>
-      <c r="T140" s="8"/>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T140" s="4"/>
+      <c r="U140" s="8"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="7"/>
       <c r="C141" s="4"/>
@@ -4263,13 +4492,14 @@
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
       <c r="O141" s="4"/>
-      <c r="P141" s="8"/>
-      <c r="Q141" s="7"/>
-      <c r="R141" s="4"/>
+      <c r="P141" s="4"/>
+      <c r="Q141" s="8"/>
+      <c r="R141" s="7"/>
       <c r="S141" s="4"/>
-      <c r="T141" s="8"/>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T141" s="4"/>
+      <c r="U141" s="8"/>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
       <c r="B142" s="7"/>
       <c r="C142" s="4"/>
@@ -4285,13 +4515,14 @@
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
       <c r="O142" s="4"/>
-      <c r="P142" s="8"/>
-      <c r="Q142" s="7"/>
-      <c r="R142" s="4"/>
+      <c r="P142" s="4"/>
+      <c r="Q142" s="8"/>
+      <c r="R142" s="7"/>
       <c r="S142" s="4"/>
-      <c r="T142" s="8"/>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T142" s="4"/>
+      <c r="U142" s="8"/>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="7"/>
       <c r="C143" s="4"/>
@@ -4307,13 +4538,14 @@
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
       <c r="O143" s="4"/>
-      <c r="P143" s="8"/>
-      <c r="Q143" s="7"/>
-      <c r="R143" s="4"/>
+      <c r="P143" s="4"/>
+      <c r="Q143" s="8"/>
+      <c r="R143" s="7"/>
       <c r="S143" s="4"/>
-      <c r="T143" s="8"/>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T143" s="4"/>
+      <c r="U143" s="8"/>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="7"/>
       <c r="C144" s="4"/>
@@ -4329,13 +4561,14 @@
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
       <c r="O144" s="4"/>
-      <c r="P144" s="8"/>
-      <c r="Q144" s="7"/>
-      <c r="R144" s="4"/>
+      <c r="P144" s="4"/>
+      <c r="Q144" s="8"/>
+      <c r="R144" s="7"/>
       <c r="S144" s="4"/>
-      <c r="T144" s="8"/>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T144" s="4"/>
+      <c r="U144" s="8"/>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="7"/>
       <c r="C145" s="4"/>
@@ -4351,13 +4584,14 @@
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
       <c r="O145" s="4"/>
-      <c r="P145" s="8"/>
-      <c r="Q145" s="7"/>
-      <c r="R145" s="4"/>
+      <c r="P145" s="4"/>
+      <c r="Q145" s="8"/>
+      <c r="R145" s="7"/>
       <c r="S145" s="4"/>
-      <c r="T145" s="8"/>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T145" s="4"/>
+      <c r="U145" s="8"/>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="7"/>
       <c r="C146" s="4"/>
@@ -4373,13 +4607,14 @@
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
       <c r="O146" s="4"/>
-      <c r="P146" s="8"/>
-      <c r="Q146" s="7"/>
-      <c r="R146" s="4"/>
+      <c r="P146" s="4"/>
+      <c r="Q146" s="8"/>
+      <c r="R146" s="7"/>
       <c r="S146" s="4"/>
-      <c r="T146" s="8"/>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T146" s="4"/>
+      <c r="U146" s="8"/>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="7"/>
       <c r="C147" s="4"/>
@@ -4395,13 +4630,14 @@
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
       <c r="O147" s="4"/>
-      <c r="P147" s="8"/>
-      <c r="Q147" s="7"/>
-      <c r="R147" s="4"/>
+      <c r="P147" s="4"/>
+      <c r="Q147" s="8"/>
+      <c r="R147" s="7"/>
       <c r="S147" s="4"/>
-      <c r="T147" s="8"/>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T147" s="4"/>
+      <c r="U147" s="8"/>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="7"/>
       <c r="C148" s="4"/>
@@ -4417,13 +4653,14 @@
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
       <c r="O148" s="4"/>
-      <c r="P148" s="8"/>
-      <c r="Q148" s="7"/>
-      <c r="R148" s="4"/>
+      <c r="P148" s="4"/>
+      <c r="Q148" s="8"/>
+      <c r="R148" s="7"/>
       <c r="S148" s="4"/>
-      <c r="T148" s="8"/>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T148" s="4"/>
+      <c r="U148" s="8"/>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="7"/>
       <c r="C149" s="4"/>
@@ -4439,13 +4676,14 @@
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
       <c r="O149" s="4"/>
-      <c r="P149" s="8"/>
-      <c r="Q149" s="7"/>
-      <c r="R149" s="4"/>
+      <c r="P149" s="4"/>
+      <c r="Q149" s="8"/>
+      <c r="R149" s="7"/>
       <c r="S149" s="4"/>
-      <c r="T149" s="8"/>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T149" s="4"/>
+      <c r="U149" s="8"/>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="7"/>
       <c r="C150" s="4"/>
@@ -4461,13 +4699,14 @@
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
       <c r="O150" s="4"/>
-      <c r="P150" s="8"/>
-      <c r="Q150" s="7"/>
-      <c r="R150" s="4"/>
+      <c r="P150" s="4"/>
+      <c r="Q150" s="8"/>
+      <c r="R150" s="7"/>
       <c r="S150" s="4"/>
-      <c r="T150" s="8"/>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T150" s="4"/>
+      <c r="U150" s="8"/>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="7"/>
       <c r="C151" s="4"/>
@@ -4483,13 +4722,14 @@
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
       <c r="O151" s="4"/>
-      <c r="P151" s="8"/>
-      <c r="Q151" s="7"/>
-      <c r="R151" s="4"/>
+      <c r="P151" s="4"/>
+      <c r="Q151" s="8"/>
+      <c r="R151" s="7"/>
       <c r="S151" s="4"/>
-      <c r="T151" s="8"/>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T151" s="4"/>
+      <c r="U151" s="8"/>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="7"/>
       <c r="C152" s="4"/>
@@ -4505,13 +4745,14 @@
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
       <c r="O152" s="4"/>
-      <c r="P152" s="8"/>
-      <c r="Q152" s="7"/>
-      <c r="R152" s="4"/>
+      <c r="P152" s="4"/>
+      <c r="Q152" s="8"/>
+      <c r="R152" s="7"/>
       <c r="S152" s="4"/>
-      <c r="T152" s="8"/>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T152" s="4"/>
+      <c r="U152" s="8"/>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="7"/>
       <c r="C153" s="4"/>
@@ -4527,13 +4768,14 @@
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
       <c r="O153" s="4"/>
-      <c r="P153" s="8"/>
-      <c r="Q153" s="7"/>
-      <c r="R153" s="4"/>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="8"/>
+      <c r="R153" s="7"/>
       <c r="S153" s="4"/>
-      <c r="T153" s="8"/>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T153" s="4"/>
+      <c r="U153" s="8"/>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="7"/>
       <c r="C154" s="4"/>
@@ -4549,13 +4791,14 @@
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
       <c r="O154" s="4"/>
-      <c r="P154" s="8"/>
-      <c r="Q154" s="7"/>
-      <c r="R154" s="4"/>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="8"/>
+      <c r="R154" s="7"/>
       <c r="S154" s="4"/>
-      <c r="T154" s="8"/>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T154" s="4"/>
+      <c r="U154" s="8"/>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="7"/>
       <c r="C155" s="4"/>
@@ -4571,13 +4814,14 @@
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
       <c r="O155" s="4"/>
-      <c r="P155" s="8"/>
-      <c r="Q155" s="7"/>
-      <c r="R155" s="4"/>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="8"/>
+      <c r="R155" s="7"/>
       <c r="S155" s="4"/>
-      <c r="T155" s="8"/>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T155" s="4"/>
+      <c r="U155" s="8"/>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="7"/>
       <c r="C156" s="4"/>
@@ -4593,13 +4837,14 @@
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
       <c r="O156" s="4"/>
-      <c r="P156" s="8"/>
-      <c r="Q156" s="7"/>
-      <c r="R156" s="4"/>
+      <c r="P156" s="4"/>
+      <c r="Q156" s="8"/>
+      <c r="R156" s="7"/>
       <c r="S156" s="4"/>
-      <c r="T156" s="8"/>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T156" s="4"/>
+      <c r="U156" s="8"/>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="7"/>
       <c r="C157" s="4"/>
@@ -4615,13 +4860,14 @@
       <c r="M157" s="4"/>
       <c r="N157" s="4"/>
       <c r="O157" s="4"/>
-      <c r="P157" s="8"/>
-      <c r="Q157" s="7"/>
-      <c r="R157" s="4"/>
+      <c r="P157" s="4"/>
+      <c r="Q157" s="8"/>
+      <c r="R157" s="7"/>
       <c r="S157" s="4"/>
-      <c r="T157" s="8"/>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T157" s="4"/>
+      <c r="U157" s="8"/>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="7"/>
       <c r="C158" s="4"/>
@@ -4637,13 +4883,14 @@
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
       <c r="O158" s="4"/>
-      <c r="P158" s="8"/>
-      <c r="Q158" s="7"/>
-      <c r="R158" s="4"/>
+      <c r="P158" s="4"/>
+      <c r="Q158" s="8"/>
+      <c r="R158" s="7"/>
       <c r="S158" s="4"/>
-      <c r="T158" s="8"/>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T158" s="4"/>
+      <c r="U158" s="8"/>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="7"/>
       <c r="C159" s="4"/>
@@ -4659,13 +4906,14 @@
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
       <c r="O159" s="4"/>
-      <c r="P159" s="8"/>
-      <c r="Q159" s="7"/>
-      <c r="R159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="8"/>
+      <c r="R159" s="7"/>
       <c r="S159" s="4"/>
-      <c r="T159" s="8"/>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T159" s="4"/>
+      <c r="U159" s="8"/>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="7"/>
       <c r="C160" s="4"/>
@@ -4681,13 +4929,14 @@
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
       <c r="O160" s="4"/>
-      <c r="P160" s="8"/>
-      <c r="Q160" s="7"/>
-      <c r="R160" s="4"/>
+      <c r="P160" s="4"/>
+      <c r="Q160" s="8"/>
+      <c r="R160" s="7"/>
       <c r="S160" s="4"/>
-      <c r="T160" s="8"/>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T160" s="4"/>
+      <c r="U160" s="8"/>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="7"/>
       <c r="C161" s="4"/>
@@ -4703,13 +4952,14 @@
       <c r="M161" s="4"/>
       <c r="N161" s="4"/>
       <c r="O161" s="4"/>
-      <c r="P161" s="8"/>
-      <c r="Q161" s="7"/>
-      <c r="R161" s="4"/>
+      <c r="P161" s="4"/>
+      <c r="Q161" s="8"/>
+      <c r="R161" s="7"/>
       <c r="S161" s="4"/>
-      <c r="T161" s="8"/>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T161" s="4"/>
+      <c r="U161" s="8"/>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="7"/>
       <c r="C162" s="4"/>
@@ -4725,13 +4975,14 @@
       <c r="M162" s="4"/>
       <c r="N162" s="4"/>
       <c r="O162" s="4"/>
-      <c r="P162" s="8"/>
-      <c r="Q162" s="7"/>
-      <c r="R162" s="4"/>
+      <c r="P162" s="4"/>
+      <c r="Q162" s="8"/>
+      <c r="R162" s="7"/>
       <c r="S162" s="4"/>
-      <c r="T162" s="8"/>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T162" s="4"/>
+      <c r="U162" s="8"/>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="7"/>
       <c r="C163" s="4"/>
@@ -4747,13 +4998,14 @@
       <c r="M163" s="4"/>
       <c r="N163" s="4"/>
       <c r="O163" s="4"/>
-      <c r="P163" s="8"/>
-      <c r="Q163" s="7"/>
-      <c r="R163" s="4"/>
+      <c r="P163" s="4"/>
+      <c r="Q163" s="8"/>
+      <c r="R163" s="7"/>
       <c r="S163" s="4"/>
-      <c r="T163" s="8"/>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T163" s="4"/>
+      <c r="U163" s="8"/>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="7"/>
       <c r="C164" s="4"/>
@@ -4769,13 +5021,14 @@
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
       <c r="O164" s="4"/>
-      <c r="P164" s="8"/>
-      <c r="Q164" s="7"/>
-      <c r="R164" s="4"/>
+      <c r="P164" s="4"/>
+      <c r="Q164" s="8"/>
+      <c r="R164" s="7"/>
       <c r="S164" s="4"/>
-      <c r="T164" s="8"/>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T164" s="4"/>
+      <c r="U164" s="8"/>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="7"/>
       <c r="C165" s="4"/>
@@ -4791,13 +5044,14 @@
       <c r="M165" s="4"/>
       <c r="N165" s="4"/>
       <c r="O165" s="4"/>
-      <c r="P165" s="8"/>
-      <c r="Q165" s="7"/>
-      <c r="R165" s="4"/>
+      <c r="P165" s="4"/>
+      <c r="Q165" s="8"/>
+      <c r="R165" s="7"/>
       <c r="S165" s="4"/>
-      <c r="T165" s="8"/>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T165" s="4"/>
+      <c r="U165" s="8"/>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="7"/>
       <c r="C166" s="4"/>
@@ -4813,13 +5067,14 @@
       <c r="M166" s="4"/>
       <c r="N166" s="4"/>
       <c r="O166" s="4"/>
-      <c r="P166" s="8"/>
-      <c r="Q166" s="7"/>
-      <c r="R166" s="4"/>
+      <c r="P166" s="4"/>
+      <c r="Q166" s="8"/>
+      <c r="R166" s="7"/>
       <c r="S166" s="4"/>
-      <c r="T166" s="8"/>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T166" s="4"/>
+      <c r="U166" s="8"/>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="7"/>
       <c r="C167" s="4"/>
@@ -4835,13 +5090,14 @@
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
       <c r="O167" s="4"/>
-      <c r="P167" s="8"/>
-      <c r="Q167" s="7"/>
-      <c r="R167" s="4"/>
+      <c r="P167" s="4"/>
+      <c r="Q167" s="8"/>
+      <c r="R167" s="7"/>
       <c r="S167" s="4"/>
-      <c r="T167" s="8"/>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T167" s="4"/>
+      <c r="U167" s="8"/>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="7"/>
       <c r="C168" s="4"/>
@@ -4857,13 +5113,14 @@
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
       <c r="O168" s="4"/>
-      <c r="P168" s="8"/>
-      <c r="Q168" s="7"/>
-      <c r="R168" s="4"/>
+      <c r="P168" s="4"/>
+      <c r="Q168" s="8"/>
+      <c r="R168" s="7"/>
       <c r="S168" s="4"/>
-      <c r="T168" s="8"/>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T168" s="4"/>
+      <c r="U168" s="8"/>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="7"/>
       <c r="C169" s="4"/>
@@ -4879,13 +5136,14 @@
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
       <c r="O169" s="4"/>
-      <c r="P169" s="8"/>
-      <c r="Q169" s="7"/>
-      <c r="R169" s="4"/>
+      <c r="P169" s="4"/>
+      <c r="Q169" s="8"/>
+      <c r="R169" s="7"/>
       <c r="S169" s="4"/>
-      <c r="T169" s="8"/>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T169" s="4"/>
+      <c r="U169" s="8"/>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="7"/>
       <c r="C170" s="4"/>
@@ -4901,13 +5159,14 @@
       <c r="M170" s="4"/>
       <c r="N170" s="4"/>
       <c r="O170" s="4"/>
-      <c r="P170" s="8"/>
-      <c r="Q170" s="7"/>
-      <c r="R170" s="4"/>
+      <c r="P170" s="4"/>
+      <c r="Q170" s="8"/>
+      <c r="R170" s="7"/>
       <c r="S170" s="4"/>
-      <c r="T170" s="8"/>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T170" s="4"/>
+      <c r="U170" s="8"/>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="7"/>
       <c r="C171" s="4"/>
@@ -4923,13 +5182,14 @@
       <c r="M171" s="4"/>
       <c r="N171" s="4"/>
       <c r="O171" s="4"/>
-      <c r="P171" s="8"/>
-      <c r="Q171" s="7"/>
-      <c r="R171" s="4"/>
+      <c r="P171" s="4"/>
+      <c r="Q171" s="8"/>
+      <c r="R171" s="7"/>
       <c r="S171" s="4"/>
-      <c r="T171" s="8"/>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T171" s="4"/>
+      <c r="U171" s="8"/>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="7"/>
       <c r="C172" s="4"/>
@@ -4945,13 +5205,14 @@
       <c r="M172" s="4"/>
       <c r="N172" s="4"/>
       <c r="O172" s="4"/>
-      <c r="P172" s="8"/>
-      <c r="Q172" s="7"/>
-      <c r="R172" s="4"/>
+      <c r="P172" s="4"/>
+      <c r="Q172" s="8"/>
+      <c r="R172" s="7"/>
       <c r="S172" s="4"/>
-      <c r="T172" s="8"/>
-    </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T172" s="4"/>
+      <c r="U172" s="8"/>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="7"/>
       <c r="C173" s="4"/>
@@ -4967,13 +5228,14 @@
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
       <c r="O173" s="4"/>
-      <c r="P173" s="8"/>
-      <c r="Q173" s="7"/>
-      <c r="R173" s="4"/>
+      <c r="P173" s="4"/>
+      <c r="Q173" s="8"/>
+      <c r="R173" s="7"/>
       <c r="S173" s="4"/>
-      <c r="T173" s="8"/>
-    </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T173" s="4"/>
+      <c r="U173" s="8"/>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="7"/>
       <c r="C174" s="4"/>
@@ -4989,13 +5251,14 @@
       <c r="M174" s="4"/>
       <c r="N174" s="4"/>
       <c r="O174" s="4"/>
-      <c r="P174" s="8"/>
-      <c r="Q174" s="7"/>
-      <c r="R174" s="4"/>
+      <c r="P174" s="4"/>
+      <c r="Q174" s="8"/>
+      <c r="R174" s="7"/>
       <c r="S174" s="4"/>
-      <c r="T174" s="8"/>
-    </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T174" s="4"/>
+      <c r="U174" s="8"/>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="7"/>
       <c r="C175" s="4"/>
@@ -5011,13 +5274,14 @@
       <c r="M175" s="4"/>
       <c r="N175" s="4"/>
       <c r="O175" s="4"/>
-      <c r="P175" s="8"/>
-      <c r="Q175" s="7"/>
-      <c r="R175" s="4"/>
+      <c r="P175" s="4"/>
+      <c r="Q175" s="8"/>
+      <c r="R175" s="7"/>
       <c r="S175" s="4"/>
-      <c r="T175" s="8"/>
-    </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T175" s="4"/>
+      <c r="U175" s="8"/>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="7"/>
       <c r="C176" s="4"/>
@@ -5033,18 +5297,19 @@
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
       <c r="O176" s="4"/>
-      <c r="P176" s="8"/>
-      <c r="Q176" s="7"/>
-      <c r="R176" s="4"/>
+      <c r="P176" s="4"/>
+      <c r="Q176" s="8"/>
+      <c r="R176" s="7"/>
       <c r="S176" s="4"/>
-      <c r="T176" s="8"/>
+      <c r="T176" s="4"/>
+      <c r="U176" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="R1:U1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5052,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2F00BA-95B2-42FB-9A66-5FDDA7DC61DE}">
-  <dimension ref="A1:T177"/>
+  <dimension ref="A1:U177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
@@ -5066,18 +5331,19 @@
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
@@ -5097,19 +5363,20 @@
       <c r="K1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="21"/>
+      <c r="L1" s="23"/>
       <c r="M1" s="21"/>
       <c r="N1" s="21"/>
       <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="20" t="s">
+      <c r="P1" s="21"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="21"/>
       <c r="S1" s="21"/>
-      <c r="T1" s="22"/>
-    </row>
-    <row r="2" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T1" s="21"/>
+      <c r="U1" s="22"/>
+    </row>
+    <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -5143,49 +5410,52 @@
       <c r="K2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F3" s="7">
         <f t="shared" ref="F3:F11" si="0">(0.0001451)/2</f>
@@ -5198,7 +5468,7 @@
         <v>0.15</v>
       </c>
       <c r="I3" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J3" s="8">
         <v>1730</v>
@@ -5207,48 +5477,51 @@
         <v>30</v>
       </c>
       <c r="L3" s="4">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
         <v>3</v>
       </c>
-      <c r="M3" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N3" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O3" s="4">
         <v>10</v>
       </c>
-      <c r="O3" s="4">
+      <c r="P3" s="4">
         <v>1</v>
       </c>
-      <c r="P3" s="16">
+      <c r="Q3" s="16">
         <v>1E-4</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="R3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <v>1</v>
       </c>
-      <c r="S3" s="4">
+      <c r="T3" s="4">
         <v>500</v>
       </c>
-      <c r="T3" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F4" s="7">
         <f t="shared" si="0"/>
@@ -5261,7 +5534,7 @@
         <v>0.15</v>
       </c>
       <c r="I4" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" s="8">
         <v>1730</v>
@@ -5270,48 +5543,51 @@
         <v>30</v>
       </c>
       <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
         <v>3</v>
       </c>
-      <c r="M4" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N4" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O4" s="4">
         <v>10</v>
       </c>
-      <c r="O4" s="4">
+      <c r="P4" s="4">
         <v>1</v>
       </c>
-      <c r="P4" s="16">
+      <c r="Q4" s="16">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="R4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="4">
+      <c r="S4" s="4">
         <v>1</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="4">
         <v>500</v>
       </c>
-      <c r="T4" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>1003</v>
+        <v>1103</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
@@ -5324,7 +5600,7 @@
         <v>0.15</v>
       </c>
       <c r="I5" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J5" s="8">
         <v>1730</v>
@@ -5333,48 +5609,51 @@
         <v>30</v>
       </c>
       <c r="L5" s="4">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
         <v>3</v>
       </c>
-      <c r="M5" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N5" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O5" s="4">
         <v>10</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>1</v>
       </c>
-      <c r="P5" s="16">
+      <c r="Q5" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="R5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <v>1</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="4">
         <v>500</v>
       </c>
-      <c r="T5" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>1004</v>
+        <v>1104</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="0"/>
@@ -5387,7 +5666,7 @@
         <v>0.15</v>
       </c>
       <c r="I6" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J6" s="8">
         <v>1730</v>
@@ -5396,48 +5675,51 @@
         <v>30</v>
       </c>
       <c r="L6" s="4">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4">
         <v>5</v>
       </c>
-      <c r="M6" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N6" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O6" s="4">
         <v>10</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>1</v>
       </c>
-      <c r="P6" s="16">
+      <c r="Q6" s="16">
         <v>1E-4</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="R6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>1</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="4">
         <v>500</v>
       </c>
-      <c r="T6" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U6" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>1005</v>
+        <v>1105</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F7" s="7">
         <f t="shared" si="0"/>
@@ -5450,7 +5732,7 @@
         <v>0.15</v>
       </c>
       <c r="I7" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J7" s="8">
         <v>1730</v>
@@ -5459,48 +5741,51 @@
         <v>30</v>
       </c>
       <c r="L7" s="4">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4">
         <v>5</v>
       </c>
-      <c r="M7" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N7" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O7" s="4">
         <v>10</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>1</v>
       </c>
-      <c r="P7" s="16">
+      <c r="Q7" s="16">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="R7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>1</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="4">
         <v>500</v>
       </c>
-      <c r="T7" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>1006</v>
+        <v>1106</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="0"/>
@@ -5513,7 +5798,7 @@
         <v>0.15</v>
       </c>
       <c r="I8" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J8" s="8">
         <v>1730</v>
@@ -5522,48 +5807,51 @@
         <v>30</v>
       </c>
       <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
         <v>5</v>
       </c>
-      <c r="M8" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N8" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O8" s="4">
         <v>10</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>1</v>
       </c>
-      <c r="P8" s="16">
+      <c r="Q8" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="R8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>1</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="4">
         <v>500</v>
       </c>
-      <c r="T8" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U8" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>1007</v>
+        <v>1107</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
@@ -5576,7 +5864,7 @@
         <v>0.15</v>
       </c>
       <c r="I9" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J9" s="8">
         <v>1730</v>
@@ -5585,48 +5873,51 @@
         <v>30</v>
       </c>
       <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="4">
         <v>7</v>
       </c>
-      <c r="M9" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N9" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O9" s="4">
         <v>10</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>1</v>
       </c>
-      <c r="P9" s="16">
+      <c r="Q9" s="16">
         <v>1E-4</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="R9" s="7">
         <v>0</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <v>1</v>
       </c>
-      <c r="S9" s="4">
+      <c r="T9" s="4">
         <v>500</v>
       </c>
-      <c r="T9" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U9" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
-        <v>1008</v>
+        <v>1108</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F10" s="7">
         <f t="shared" si="0"/>
@@ -5639,7 +5930,7 @@
         <v>0.15</v>
       </c>
       <c r="I10" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J10" s="8">
         <v>1730</v>
@@ -5648,48 +5939,51 @@
         <v>30</v>
       </c>
       <c r="L10" s="4">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4">
         <v>7</v>
       </c>
-      <c r="M10" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N10" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O10" s="4">
         <v>10</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>1</v>
       </c>
-      <c r="P10" s="16">
+      <c r="Q10" s="16">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="R10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <v>1</v>
       </c>
-      <c r="S10" s="4">
+      <c r="T10" s="4">
         <v>500</v>
       </c>
-      <c r="T10" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>1009</v>
+        <v>1109</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="E11" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
@@ -5702,7 +5996,7 @@
         <v>0.15</v>
       </c>
       <c r="I11" s="4">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J11" s="8">
         <v>1730</v>
@@ -5711,34 +6005,37 @@
         <v>30</v>
       </c>
       <c r="L11" s="4">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4">
         <v>7</v>
       </c>
-      <c r="M11" s="4">
-        <v>9.9999999999999995E-8</v>
-      </c>
       <c r="N11" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O11" s="4">
         <v>10</v>
       </c>
-      <c r="O11" s="4">
+      <c r="P11" s="4">
         <v>1</v>
       </c>
-      <c r="P11" s="16">
+      <c r="Q11" s="16">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="R11" s="7">
         <v>0</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <v>1</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="4">
         <v>500</v>
       </c>
-      <c r="T11" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U11" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="7"/>
       <c r="C12" s="4"/>
@@ -5754,35 +6051,14 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="7"/>
       <c r="S12" s="4"/>
-      <c r="T12" s="8"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="8"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T12" s="4"/>
+      <c r="U12" s="8"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="7"/>
       <c r="C14" s="4"/>
@@ -5798,13 +6074,14 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="7"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="8"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T14" s="4"/>
+      <c r="U14" s="8"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="7"/>
       <c r="C15" s="4"/>
@@ -5820,13 +6097,14 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="7"/>
       <c r="S15" s="4"/>
-      <c r="T15" s="8"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T15" s="4"/>
+      <c r="U15" s="8"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>
@@ -5842,13 +6120,14 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="7"/>
       <c r="S16" s="4"/>
-      <c r="T16" s="8"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T16" s="4"/>
+      <c r="U16" s="8"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="7"/>
       <c r="C17" s="4"/>
@@ -5864,13 +6143,14 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="7"/>
       <c r="S17" s="4"/>
-      <c r="T17" s="8"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T17" s="4"/>
+      <c r="U17" s="8"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="7"/>
       <c r="C18" s="4"/>
@@ -5886,13 +6166,14 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="7"/>
       <c r="S18" s="4"/>
-      <c r="T18" s="8"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T18" s="4"/>
+      <c r="U18" s="8"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="7"/>
       <c r="C19" s="4"/>
@@ -5908,13 +6189,14 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="7"/>
       <c r="S19" s="4"/>
-      <c r="T19" s="8"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T19" s="4"/>
+      <c r="U19" s="8"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="7"/>
       <c r="C20" s="4"/>
@@ -5930,13 +6212,14 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="7"/>
       <c r="S20" s="4"/>
-      <c r="T20" s="8"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T20" s="4"/>
+      <c r="U20" s="8"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="7"/>
       <c r="C21" s="4"/>
@@ -5952,13 +6235,14 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="7"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="8"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T21" s="4"/>
+      <c r="U21" s="8"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="7"/>
       <c r="C22" s="4"/>
@@ -5974,13 +6258,14 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="7"/>
       <c r="S22" s="4"/>
-      <c r="T22" s="8"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T22" s="4"/>
+      <c r="U22" s="8"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="7"/>
       <c r="C23" s="4"/>
@@ -5996,13 +6281,14 @@
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="7"/>
       <c r="S23" s="4"/>
-      <c r="T23" s="8"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T23" s="4"/>
+      <c r="U23" s="8"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
@@ -6018,13 +6304,14 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="7"/>
       <c r="S24" s="4"/>
-      <c r="T24" s="8"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T24" s="4"/>
+      <c r="U24" s="8"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
@@ -6040,13 +6327,14 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="7"/>
       <c r="S25" s="4"/>
-      <c r="T25" s="8"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T25" s="4"/>
+      <c r="U25" s="8"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="7"/>
       <c r="C26" s="4"/>
@@ -6062,13 +6350,14 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="7"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="8"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T26" s="4"/>
+      <c r="U26" s="8"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="7"/>
       <c r="C27" s="4"/>
@@ -6084,13 +6373,14 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="7"/>
       <c r="S27" s="4"/>
-      <c r="T27" s="8"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T27" s="4"/>
+      <c r="U27" s="8"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="7"/>
       <c r="C28" s="4"/>
@@ -6106,13 +6396,14 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="7"/>
       <c r="S28" s="4"/>
-      <c r="T28" s="8"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T28" s="4"/>
+      <c r="U28" s="8"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
@@ -6128,13 +6419,14 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="7"/>
       <c r="S29" s="4"/>
-      <c r="T29" s="8"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T29" s="4"/>
+      <c r="U29" s="8"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
@@ -6150,13 +6442,14 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="7"/>
       <c r="S30" s="4"/>
-      <c r="T30" s="8"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T30" s="4"/>
+      <c r="U30" s="8"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="7"/>
       <c r="C31" s="4"/>
@@ -6172,13 +6465,14 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="7"/>
       <c r="S31" s="4"/>
-      <c r="T31" s="8"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T31" s="4"/>
+      <c r="U31" s="8"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="7"/>
       <c r="C32" s="4"/>
@@ -6194,13 +6488,14 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="7"/>
       <c r="S32" s="4"/>
-      <c r="T32" s="8"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T32" s="4"/>
+      <c r="U32" s="8"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="7"/>
       <c r="C33" s="4"/>
@@ -6216,13 +6511,14 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="7"/>
       <c r="S33" s="4"/>
-      <c r="T33" s="8"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T33" s="4"/>
+      <c r="U33" s="8"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="7"/>
       <c r="C34" s="4"/>
@@ -6238,13 +6534,14 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="7"/>
       <c r="S34" s="4"/>
-      <c r="T34" s="8"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T34" s="4"/>
+      <c r="U34" s="8"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="7"/>
       <c r="C35" s="4"/>
@@ -6260,13 +6557,14 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="7"/>
       <c r="S35" s="4"/>
-      <c r="T35" s="8"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T35" s="4"/>
+      <c r="U35" s="8"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="7"/>
       <c r="C36" s="4"/>
@@ -6282,13 +6580,14 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="7"/>
       <c r="S36" s="4"/>
-      <c r="T36" s="8"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T36" s="4"/>
+      <c r="U36" s="8"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="7"/>
       <c r="C37" s="4"/>
@@ -6304,13 +6603,14 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="7"/>
       <c r="S37" s="4"/>
-      <c r="T37" s="8"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T37" s="4"/>
+      <c r="U37" s="8"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="7"/>
       <c r="C38" s="4"/>
@@ -6326,13 +6626,14 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="7"/>
       <c r="S38" s="4"/>
-      <c r="T38" s="8"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T38" s="4"/>
+      <c r="U38" s="8"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="7"/>
       <c r="C39" s="4"/>
@@ -6348,13 +6649,14 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="7"/>
       <c r="S39" s="4"/>
-      <c r="T39" s="8"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T39" s="4"/>
+      <c r="U39" s="8"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="7"/>
       <c r="C40" s="4"/>
@@ -6370,13 +6672,14 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="7"/>
       <c r="S40" s="4"/>
-      <c r="T40" s="8"/>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T40" s="4"/>
+      <c r="U40" s="8"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="7"/>
       <c r="C41" s="4"/>
@@ -6392,13 +6695,14 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="7"/>
       <c r="S41" s="4"/>
-      <c r="T41" s="8"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T41" s="4"/>
+      <c r="U41" s="8"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="7"/>
       <c r="C42" s="4"/>
@@ -6414,13 +6718,14 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="7"/>
       <c r="S42" s="4"/>
-      <c r="T42" s="8"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T42" s="4"/>
+      <c r="U42" s="8"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="7"/>
       <c r="C43" s="4"/>
@@ -6436,13 +6741,14 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="7"/>
       <c r="S43" s="4"/>
-      <c r="T43" s="8"/>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T43" s="4"/>
+      <c r="U43" s="8"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="7"/>
       <c r="C44" s="4"/>
@@ -6458,13 +6764,14 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="7"/>
       <c r="S44" s="4"/>
-      <c r="T44" s="8"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T44" s="4"/>
+      <c r="U44" s="8"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="7"/>
       <c r="C45" s="4"/>
@@ -6480,13 +6787,14 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="7"/>
       <c r="S45" s="4"/>
-      <c r="T45" s="8"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T45" s="4"/>
+      <c r="U45" s="8"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="7"/>
       <c r="C46" s="4"/>
@@ -6502,13 +6810,14 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="7"/>
       <c r="S46" s="4"/>
-      <c r="T46" s="8"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T46" s="4"/>
+      <c r="U46" s="8"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="7"/>
       <c r="C47" s="4"/>
@@ -6524,13 +6833,14 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="7"/>
       <c r="S47" s="4"/>
-      <c r="T47" s="8"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T47" s="4"/>
+      <c r="U47" s="8"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="7"/>
       <c r="C48" s="4"/>
@@ -6546,13 +6856,14 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="7"/>
       <c r="S48" s="4"/>
-      <c r="T48" s="8"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T48" s="4"/>
+      <c r="U48" s="8"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="7"/>
       <c r="C49" s="4"/>
@@ -6568,13 +6879,14 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="8"/>
+      <c r="R49" s="7"/>
       <c r="S49" s="4"/>
-      <c r="T49" s="8"/>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T49" s="4"/>
+      <c r="U49" s="8"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="7"/>
       <c r="C50" s="4"/>
@@ -6590,13 +6902,14 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="7"/>
       <c r="S50" s="4"/>
-      <c r="T50" s="8"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T50" s="4"/>
+      <c r="U50" s="8"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="7"/>
       <c r="C51" s="4"/>
@@ -6612,13 +6925,14 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="7"/>
       <c r="S51" s="4"/>
-      <c r="T51" s="8"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T51" s="4"/>
+      <c r="U51" s="8"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="7"/>
       <c r="C52" s="4"/>
@@ -6634,13 +6948,14 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="7"/>
       <c r="S52" s="4"/>
-      <c r="T52" s="8"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T52" s="4"/>
+      <c r="U52" s="8"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="7"/>
       <c r="C53" s="4"/>
@@ -6656,13 +6971,14 @@
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="8"/>
+      <c r="R53" s="7"/>
       <c r="S53" s="4"/>
-      <c r="T53" s="8"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T53" s="4"/>
+      <c r="U53" s="8"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="7"/>
       <c r="C54" s="4"/>
@@ -6678,13 +6994,14 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="7"/>
       <c r="S54" s="4"/>
-      <c r="T54" s="8"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T54" s="4"/>
+      <c r="U54" s="8"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="7"/>
       <c r="C55" s="4"/>
@@ -6700,13 +7017,14 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="7"/>
       <c r="S55" s="4"/>
-      <c r="T55" s="8"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T55" s="4"/>
+      <c r="U55" s="8"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="7"/>
       <c r="C56" s="4"/>
@@ -6722,13 +7040,14 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="7"/>
-      <c r="R56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="7"/>
       <c r="S56" s="4"/>
-      <c r="T56" s="8"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T56" s="4"/>
+      <c r="U56" s="8"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="7"/>
       <c r="C57" s="4"/>
@@ -6744,13 +7063,14 @@
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="7"/>
-      <c r="R57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="7"/>
       <c r="S57" s="4"/>
-      <c r="T57" s="8"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T57" s="4"/>
+      <c r="U57" s="8"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="7"/>
       <c r="C58" s="4"/>
@@ -6766,13 +7086,14 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="7"/>
       <c r="S58" s="4"/>
-      <c r="T58" s="8"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T58" s="4"/>
+      <c r="U58" s="8"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="7"/>
       <c r="C59" s="4"/>
@@ -6788,13 +7109,14 @@
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="8"/>
+      <c r="R59" s="7"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="8"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T59" s="4"/>
+      <c r="U59" s="8"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="7"/>
       <c r="C60" s="4"/>
@@ -6810,13 +7132,14 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="7"/>
-      <c r="R60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="8"/>
+      <c r="R60" s="7"/>
       <c r="S60" s="4"/>
-      <c r="T60" s="8"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T60" s="4"/>
+      <c r="U60" s="8"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="7"/>
       <c r="C61" s="4"/>
@@ -6832,13 +7155,14 @@
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="8"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="7"/>
       <c r="S61" s="4"/>
-      <c r="T61" s="8"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T61" s="4"/>
+      <c r="U61" s="8"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="7"/>
       <c r="C62" s="4"/>
@@ -6854,13 +7178,14 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="7"/>
       <c r="S62" s="4"/>
-      <c r="T62" s="8"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T62" s="4"/>
+      <c r="U62" s="8"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="7"/>
       <c r="C63" s="4"/>
@@ -6876,13 +7201,14 @@
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
-      <c r="P63" s="8"/>
-      <c r="Q63" s="7"/>
-      <c r="R63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="8"/>
+      <c r="R63" s="7"/>
       <c r="S63" s="4"/>
-      <c r="T63" s="8"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T63" s="4"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="7"/>
       <c r="C64" s="4"/>
@@ -6898,13 +7224,14 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="8"/>
+      <c r="R64" s="7"/>
       <c r="S64" s="4"/>
-      <c r="T64" s="8"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T64" s="4"/>
+      <c r="U64" s="8"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="7"/>
       <c r="C65" s="4"/>
@@ -6920,13 +7247,14 @@
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
-      <c r="P65" s="8"/>
-      <c r="Q65" s="7"/>
-      <c r="R65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="8"/>
+      <c r="R65" s="7"/>
       <c r="S65" s="4"/>
-      <c r="T65" s="8"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T65" s="4"/>
+      <c r="U65" s="8"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="7"/>
       <c r="C66" s="4"/>
@@ -6942,13 +7270,14 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="7"/>
-      <c r="R66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="8"/>
+      <c r="R66" s="7"/>
       <c r="S66" s="4"/>
-      <c r="T66" s="8"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T66" s="4"/>
+      <c r="U66" s="8"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="7"/>
       <c r="C67" s="4"/>
@@ -6964,13 +7293,14 @@
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
-      <c r="P67" s="8"/>
-      <c r="Q67" s="7"/>
-      <c r="R67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="7"/>
       <c r="S67" s="4"/>
-      <c r="T67" s="8"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T67" s="4"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="7"/>
       <c r="C68" s="4"/>
@@ -6986,13 +7316,14 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="7"/>
-      <c r="R68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="8"/>
+      <c r="R68" s="7"/>
       <c r="S68" s="4"/>
-      <c r="T68" s="8"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T68" s="4"/>
+      <c r="U68" s="8"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="7"/>
       <c r="C69" s="4"/>
@@ -7008,13 +7339,14 @@
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
-      <c r="P69" s="8"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="8"/>
+      <c r="R69" s="7"/>
       <c r="S69" s="4"/>
-      <c r="T69" s="8"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T69" s="4"/>
+      <c r="U69" s="8"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="7"/>
       <c r="C70" s="4"/>
@@ -7030,13 +7362,14 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="8"/>
+      <c r="R70" s="7"/>
       <c r="S70" s="4"/>
-      <c r="T70" s="8"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T70" s="4"/>
+      <c r="U70" s="8"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="7"/>
       <c r="C71" s="4"/>
@@ -7052,13 +7385,14 @@
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="7"/>
-      <c r="R71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="8"/>
+      <c r="R71" s="7"/>
       <c r="S71" s="4"/>
-      <c r="T71" s="8"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T71" s="4"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="7"/>
       <c r="C72" s="4"/>
@@ -7074,13 +7408,14 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="7"/>
-      <c r="R72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="8"/>
+      <c r="R72" s="7"/>
       <c r="S72" s="4"/>
-      <c r="T72" s="8"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T72" s="4"/>
+      <c r="U72" s="8"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="7"/>
       <c r="C73" s="4"/>
@@ -7096,13 +7431,14 @@
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="7"/>
-      <c r="R73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="8"/>
+      <c r="R73" s="7"/>
       <c r="S73" s="4"/>
-      <c r="T73" s="8"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T73" s="4"/>
+      <c r="U73" s="8"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="7"/>
       <c r="C74" s="4"/>
@@ -7118,13 +7454,14 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="8"/>
+      <c r="R74" s="7"/>
       <c r="S74" s="4"/>
-      <c r="T74" s="8"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T74" s="4"/>
+      <c r="U74" s="8"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="7"/>
       <c r="C75" s="4"/>
@@ -7140,13 +7477,14 @@
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
-      <c r="P75" s="8"/>
-      <c r="Q75" s="7"/>
-      <c r="R75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="8"/>
+      <c r="R75" s="7"/>
       <c r="S75" s="4"/>
-      <c r="T75" s="8"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T75" s="4"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="7"/>
       <c r="C76" s="4"/>
@@ -7162,13 +7500,14 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="7"/>
-      <c r="R76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="8"/>
+      <c r="R76" s="7"/>
       <c r="S76" s="4"/>
-      <c r="T76" s="8"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T76" s="4"/>
+      <c r="U76" s="8"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="7"/>
       <c r="C77" s="4"/>
@@ -7184,13 +7523,14 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
-      <c r="P77" s="8"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="8"/>
+      <c r="R77" s="7"/>
       <c r="S77" s="4"/>
-      <c r="T77" s="8"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T77" s="4"/>
+      <c r="U77" s="8"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="7"/>
       <c r="C78" s="4"/>
@@ -7206,13 +7546,14 @@
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
-      <c r="P78" s="8"/>
-      <c r="Q78" s="7"/>
-      <c r="R78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="7"/>
       <c r="S78" s="4"/>
-      <c r="T78" s="8"/>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T78" s="4"/>
+      <c r="U78" s="8"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="7"/>
       <c r="C79" s="4"/>
@@ -7228,13 +7569,14 @@
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="7"/>
-      <c r="R79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="8"/>
+      <c r="R79" s="7"/>
       <c r="S79" s="4"/>
-      <c r="T79" s="8"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T79" s="4"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="7"/>
       <c r="C80" s="4"/>
@@ -7250,13 +7592,14 @@
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="8"/>
+      <c r="R80" s="7"/>
       <c r="S80" s="4"/>
-      <c r="T80" s="8"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T80" s="4"/>
+      <c r="U80" s="8"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="7"/>
       <c r="C81" s="4"/>
@@ -7272,13 +7615,14 @@
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="8"/>
+      <c r="R81" s="7"/>
       <c r="S81" s="4"/>
-      <c r="T81" s="8"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T81" s="4"/>
+      <c r="U81" s="8"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="7"/>
       <c r="C82" s="4"/>
@@ -7294,13 +7638,14 @@
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="7"/>
-      <c r="R82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="8"/>
+      <c r="R82" s="7"/>
       <c r="S82" s="4"/>
-      <c r="T82" s="8"/>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T82" s="4"/>
+      <c r="U82" s="8"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
       <c r="B83" s="7"/>
       <c r="C83" s="4"/>
@@ -7316,13 +7661,14 @@
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="7"/>
-      <c r="R83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="8"/>
+      <c r="R83" s="7"/>
       <c r="S83" s="4"/>
-      <c r="T83" s="8"/>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T83" s="4"/>
+      <c r="U83" s="8"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="7"/>
       <c r="C84" s="4"/>
@@ -7338,13 +7684,14 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="7"/>
-      <c r="R84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="8"/>
+      <c r="R84" s="7"/>
       <c r="S84" s="4"/>
-      <c r="T84" s="8"/>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T84" s="4"/>
+      <c r="U84" s="8"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="7"/>
       <c r="C85" s="4"/>
@@ -7360,13 +7707,14 @@
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="7"/>
-      <c r="R85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="8"/>
+      <c r="R85" s="7"/>
       <c r="S85" s="4"/>
-      <c r="T85" s="8"/>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T85" s="4"/>
+      <c r="U85" s="8"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="7"/>
       <c r="C86" s="4"/>
@@ -7382,13 +7730,14 @@
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
-      <c r="P86" s="8"/>
-      <c r="Q86" s="7"/>
-      <c r="R86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="8"/>
+      <c r="R86" s="7"/>
       <c r="S86" s="4"/>
-      <c r="T86" s="8"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T86" s="4"/>
+      <c r="U86" s="8"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="7"/>
       <c r="C87" s="4"/>
@@ -7404,13 +7753,14 @@
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="7"/>
-      <c r="R87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="8"/>
+      <c r="R87" s="7"/>
       <c r="S87" s="4"/>
-      <c r="T87" s="8"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T87" s="4"/>
+      <c r="U87" s="8"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
       <c r="B88" s="7"/>
       <c r="C88" s="4"/>
@@ -7426,13 +7776,14 @@
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
-      <c r="P88" s="8"/>
-      <c r="Q88" s="7"/>
-      <c r="R88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="8"/>
+      <c r="R88" s="7"/>
       <c r="S88" s="4"/>
-      <c r="T88" s="8"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T88" s="4"/>
+      <c r="U88" s="8"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="7"/>
       <c r="C89" s="4"/>
@@ -7448,13 +7799,14 @@
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
-      <c r="P89" s="8"/>
-      <c r="Q89" s="7"/>
-      <c r="R89" s="4"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="8"/>
+      <c r="R89" s="7"/>
       <c r="S89" s="4"/>
-      <c r="T89" s="8"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T89" s="4"/>
+      <c r="U89" s="8"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
       <c r="B90" s="7"/>
       <c r="C90" s="4"/>
@@ -7470,13 +7822,14 @@
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
-      <c r="P90" s="8"/>
-      <c r="Q90" s="7"/>
-      <c r="R90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="8"/>
+      <c r="R90" s="7"/>
       <c r="S90" s="4"/>
-      <c r="T90" s="8"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T90" s="4"/>
+      <c r="U90" s="8"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="7"/>
       <c r="C91" s="4"/>
@@ -7492,13 +7845,14 @@
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
-      <c r="P91" s="8"/>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="8"/>
+      <c r="R91" s="7"/>
       <c r="S91" s="4"/>
-      <c r="T91" s="8"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T91" s="4"/>
+      <c r="U91" s="8"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
       <c r="B92" s="7"/>
       <c r="C92" s="4"/>
@@ -7514,13 +7868,14 @@
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
-      <c r="P92" s="8"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="8"/>
+      <c r="R92" s="7"/>
       <c r="S92" s="4"/>
-      <c r="T92" s="8"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T92" s="4"/>
+      <c r="U92" s="8"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="7"/>
       <c r="C93" s="4"/>
@@ -7536,13 +7891,14 @@
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
-      <c r="P93" s="8"/>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="8"/>
+      <c r="R93" s="7"/>
       <c r="S93" s="4"/>
-      <c r="T93" s="8"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T93" s="4"/>
+      <c r="U93" s="8"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="7"/>
       <c r="C94" s="4"/>
@@ -7558,13 +7914,14 @@
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
-      <c r="P94" s="8"/>
-      <c r="Q94" s="7"/>
-      <c r="R94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="8"/>
+      <c r="R94" s="7"/>
       <c r="S94" s="4"/>
-      <c r="T94" s="8"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T94" s="4"/>
+      <c r="U94" s="8"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
       <c r="B95" s="7"/>
       <c r="C95" s="4"/>
@@ -7580,13 +7937,14 @@
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
-      <c r="P95" s="8"/>
-      <c r="Q95" s="7"/>
-      <c r="R95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="8"/>
+      <c r="R95" s="7"/>
       <c r="S95" s="4"/>
-      <c r="T95" s="8"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T95" s="4"/>
+      <c r="U95" s="8"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
       <c r="B96" s="7"/>
       <c r="C96" s="4"/>
@@ -7602,13 +7960,14 @@
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
-      <c r="P96" s="8"/>
-      <c r="Q96" s="7"/>
-      <c r="R96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="8"/>
+      <c r="R96" s="7"/>
       <c r="S96" s="4"/>
-      <c r="T96" s="8"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T96" s="4"/>
+      <c r="U96" s="8"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
       <c r="B97" s="7"/>
       <c r="C97" s="4"/>
@@ -7624,13 +7983,14 @@
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
-      <c r="P97" s="8"/>
-      <c r="Q97" s="7"/>
-      <c r="R97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="8"/>
+      <c r="R97" s="7"/>
       <c r="S97" s="4"/>
-      <c r="T97" s="8"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T97" s="4"/>
+      <c r="U97" s="8"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="7"/>
       <c r="C98" s="4"/>
@@ -7646,13 +8006,14 @@
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
-      <c r="P98" s="8"/>
-      <c r="Q98" s="7"/>
-      <c r="R98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="8"/>
+      <c r="R98" s="7"/>
       <c r="S98" s="4"/>
-      <c r="T98" s="8"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T98" s="4"/>
+      <c r="U98" s="8"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="7"/>
       <c r="C99" s="4"/>
@@ -7668,13 +8029,14 @@
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
-      <c r="P99" s="8"/>
-      <c r="Q99" s="7"/>
-      <c r="R99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="8"/>
+      <c r="R99" s="7"/>
       <c r="S99" s="4"/>
-      <c r="T99" s="8"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T99" s="4"/>
+      <c r="U99" s="8"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
       <c r="B100" s="7"/>
       <c r="C100" s="4"/>
@@ -7690,13 +8052,14 @@
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
-      <c r="P100" s="8"/>
-      <c r="Q100" s="7"/>
-      <c r="R100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="8"/>
+      <c r="R100" s="7"/>
       <c r="S100" s="4"/>
-      <c r="T100" s="8"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T100" s="4"/>
+      <c r="U100" s="8"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
       <c r="B101" s="7"/>
       <c r="C101" s="4"/>
@@ -7712,13 +8075,14 @@
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
-      <c r="P101" s="8"/>
-      <c r="Q101" s="7"/>
-      <c r="R101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="8"/>
+      <c r="R101" s="7"/>
       <c r="S101" s="4"/>
-      <c r="T101" s="8"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T101" s="4"/>
+      <c r="U101" s="8"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
       <c r="B102" s="7"/>
       <c r="C102" s="4"/>
@@ -7734,13 +8098,14 @@
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
-      <c r="P102" s="8"/>
-      <c r="Q102" s="7"/>
-      <c r="R102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="8"/>
+      <c r="R102" s="7"/>
       <c r="S102" s="4"/>
-      <c r="T102" s="8"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T102" s="4"/>
+      <c r="U102" s="8"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
       <c r="B103" s="7"/>
       <c r="C103" s="4"/>
@@ -7756,13 +8121,14 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
-      <c r="P103" s="8"/>
-      <c r="Q103" s="7"/>
-      <c r="R103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="8"/>
+      <c r="R103" s="7"/>
       <c r="S103" s="4"/>
-      <c r="T103" s="8"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T103" s="4"/>
+      <c r="U103" s="8"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
       <c r="B104" s="7"/>
       <c r="C104" s="4"/>
@@ -7778,13 +8144,14 @@
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
-      <c r="P104" s="8"/>
-      <c r="Q104" s="7"/>
-      <c r="R104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="8"/>
+      <c r="R104" s="7"/>
       <c r="S104" s="4"/>
-      <c r="T104" s="8"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T104" s="4"/>
+      <c r="U104" s="8"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
       <c r="B105" s="7"/>
       <c r="C105" s="4"/>
@@ -7800,13 +8167,14 @@
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
-      <c r="P105" s="8"/>
-      <c r="Q105" s="7"/>
-      <c r="R105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="8"/>
+      <c r="R105" s="7"/>
       <c r="S105" s="4"/>
-      <c r="T105" s="8"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T105" s="4"/>
+      <c r="U105" s="8"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
       <c r="B106" s="7"/>
       <c r="C106" s="4"/>
@@ -7822,13 +8190,14 @@
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
-      <c r="P106" s="8"/>
-      <c r="Q106" s="7"/>
-      <c r="R106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="8"/>
+      <c r="R106" s="7"/>
       <c r="S106" s="4"/>
-      <c r="T106" s="8"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T106" s="4"/>
+      <c r="U106" s="8"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
       <c r="B107" s="7"/>
       <c r="C107" s="4"/>
@@ -7844,13 +8213,14 @@
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
-      <c r="P107" s="8"/>
-      <c r="Q107" s="7"/>
-      <c r="R107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="8"/>
+      <c r="R107" s="7"/>
       <c r="S107" s="4"/>
-      <c r="T107" s="8"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T107" s="4"/>
+      <c r="U107" s="8"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="7"/>
       <c r="C108" s="4"/>
@@ -7866,13 +8236,14 @@
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
-      <c r="P108" s="8"/>
-      <c r="Q108" s="7"/>
-      <c r="R108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="8"/>
+      <c r="R108" s="7"/>
       <c r="S108" s="4"/>
-      <c r="T108" s="8"/>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T108" s="4"/>
+      <c r="U108" s="8"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
       <c r="B109" s="7"/>
       <c r="C109" s="4"/>
@@ -7888,13 +8259,14 @@
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
-      <c r="P109" s="8"/>
-      <c r="Q109" s="7"/>
-      <c r="R109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="8"/>
+      <c r="R109" s="7"/>
       <c r="S109" s="4"/>
-      <c r="T109" s="8"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T109" s="4"/>
+      <c r="U109" s="8"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
       <c r="B110" s="7"/>
       <c r="C110" s="4"/>
@@ -7910,13 +8282,14 @@
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
-      <c r="P110" s="8"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="8"/>
+      <c r="R110" s="7"/>
       <c r="S110" s="4"/>
-      <c r="T110" s="8"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T110" s="4"/>
+      <c r="U110" s="8"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
       <c r="B111" s="7"/>
       <c r="C111" s="4"/>
@@ -7932,13 +8305,14 @@
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
-      <c r="P111" s="8"/>
-      <c r="Q111" s="7"/>
-      <c r="R111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="8"/>
+      <c r="R111" s="7"/>
       <c r="S111" s="4"/>
-      <c r="T111" s="8"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T111" s="4"/>
+      <c r="U111" s="8"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="7"/>
       <c r="C112" s="4"/>
@@ -7954,13 +8328,14 @@
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
-      <c r="P112" s="8"/>
-      <c r="Q112" s="7"/>
-      <c r="R112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="8"/>
+      <c r="R112" s="7"/>
       <c r="S112" s="4"/>
-      <c r="T112" s="8"/>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T112" s="4"/>
+      <c r="U112" s="8"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
       <c r="B113" s="7"/>
       <c r="C113" s="4"/>
@@ -7976,13 +8351,14 @@
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
-      <c r="P113" s="8"/>
-      <c r="Q113" s="7"/>
-      <c r="R113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="8"/>
+      <c r="R113" s="7"/>
       <c r="S113" s="4"/>
-      <c r="T113" s="8"/>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T113" s="4"/>
+      <c r="U113" s="8"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
       <c r="B114" s="7"/>
       <c r="C114" s="4"/>
@@ -7998,13 +8374,14 @@
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
-      <c r="P114" s="8"/>
-      <c r="Q114" s="7"/>
-      <c r="R114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="8"/>
+      <c r="R114" s="7"/>
       <c r="S114" s="4"/>
-      <c r="T114" s="8"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T114" s="4"/>
+      <c r="U114" s="8"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
       <c r="B115" s="7"/>
       <c r="C115" s="4"/>
@@ -8020,13 +8397,14 @@
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
-      <c r="P115" s="8"/>
-      <c r="Q115" s="7"/>
-      <c r="R115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="7"/>
       <c r="S115" s="4"/>
-      <c r="T115" s="8"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T115" s="4"/>
+      <c r="U115" s="8"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
       <c r="B116" s="7"/>
       <c r="C116" s="4"/>
@@ -8042,13 +8420,14 @@
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
-      <c r="P116" s="8"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="8"/>
+      <c r="R116" s="7"/>
       <c r="S116" s="4"/>
-      <c r="T116" s="8"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T116" s="4"/>
+      <c r="U116" s="8"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
       <c r="B117" s="7"/>
       <c r="C117" s="4"/>
@@ -8064,13 +8443,14 @@
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
-      <c r="P117" s="8"/>
-      <c r="Q117" s="7"/>
-      <c r="R117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="8"/>
+      <c r="R117" s="7"/>
       <c r="S117" s="4"/>
-      <c r="T117" s="8"/>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T117" s="4"/>
+      <c r="U117" s="8"/>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
       <c r="B118" s="7"/>
       <c r="C118" s="4"/>
@@ -8086,13 +8466,14 @@
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
-      <c r="P118" s="8"/>
-      <c r="Q118" s="7"/>
-      <c r="R118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="8"/>
+      <c r="R118" s="7"/>
       <c r="S118" s="4"/>
-      <c r="T118" s="8"/>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T118" s="4"/>
+      <c r="U118" s="8"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
       <c r="B119" s="7"/>
       <c r="C119" s="4"/>
@@ -8108,13 +8489,14 @@
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
-      <c r="P119" s="8"/>
-      <c r="Q119" s="7"/>
-      <c r="R119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="8"/>
+      <c r="R119" s="7"/>
       <c r="S119" s="4"/>
-      <c r="T119" s="8"/>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T119" s="4"/>
+      <c r="U119" s="8"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="7"/>
       <c r="C120" s="4"/>
@@ -8130,13 +8512,14 @@
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
-      <c r="P120" s="8"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="8"/>
+      <c r="R120" s="7"/>
       <c r="S120" s="4"/>
-      <c r="T120" s="8"/>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T120" s="4"/>
+      <c r="U120" s="8"/>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="7"/>
       <c r="C121" s="4"/>
@@ -8152,13 +8535,14 @@
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
-      <c r="P121" s="8"/>
-      <c r="Q121" s="7"/>
-      <c r="R121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="8"/>
+      <c r="R121" s="7"/>
       <c r="S121" s="4"/>
-      <c r="T121" s="8"/>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T121" s="4"/>
+      <c r="U121" s="8"/>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="7"/>
       <c r="C122" s="4"/>
@@ -8174,13 +8558,14 @@
       <c r="M122" s="4"/>
       <c r="N122" s="4"/>
       <c r="O122" s="4"/>
-      <c r="P122" s="8"/>
-      <c r="Q122" s="7"/>
-      <c r="R122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="8"/>
+      <c r="R122" s="7"/>
       <c r="S122" s="4"/>
-      <c r="T122" s="8"/>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T122" s="4"/>
+      <c r="U122" s="8"/>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="7"/>
       <c r="C123" s="4"/>
@@ -8196,13 +8581,14 @@
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
       <c r="O123" s="4"/>
-      <c r="P123" s="8"/>
-      <c r="Q123" s="7"/>
-      <c r="R123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="8"/>
+      <c r="R123" s="7"/>
       <c r="S123" s="4"/>
-      <c r="T123" s="8"/>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T123" s="4"/>
+      <c r="U123" s="8"/>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
       <c r="B124" s="7"/>
       <c r="C124" s="4"/>
@@ -8218,13 +8604,14 @@
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
       <c r="O124" s="4"/>
-      <c r="P124" s="8"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="8"/>
+      <c r="R124" s="7"/>
       <c r="S124" s="4"/>
-      <c r="T124" s="8"/>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T124" s="4"/>
+      <c r="U124" s="8"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
       <c r="B125" s="7"/>
       <c r="C125" s="4"/>
@@ -8240,13 +8627,14 @@
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
       <c r="O125" s="4"/>
-      <c r="P125" s="8"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="4"/>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="8"/>
+      <c r="R125" s="7"/>
       <c r="S125" s="4"/>
-      <c r="T125" s="8"/>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T125" s="4"/>
+      <c r="U125" s="8"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="7"/>
       <c r="C126" s="4"/>
@@ -8262,13 +8650,14 @@
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
       <c r="O126" s="4"/>
-      <c r="P126" s="8"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="4"/>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="8"/>
+      <c r="R126" s="7"/>
       <c r="S126" s="4"/>
-      <c r="T126" s="8"/>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T126" s="4"/>
+      <c r="U126" s="8"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="7"/>
       <c r="C127" s="4"/>
@@ -8284,13 +8673,14 @@
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
       <c r="O127" s="4"/>
-      <c r="P127" s="8"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="4"/>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="8"/>
+      <c r="R127" s="7"/>
       <c r="S127" s="4"/>
-      <c r="T127" s="8"/>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T127" s="4"/>
+      <c r="U127" s="8"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="7"/>
       <c r="C128" s="4"/>
@@ -8306,13 +8696,14 @@
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
       <c r="O128" s="4"/>
-      <c r="P128" s="8"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="4"/>
+      <c r="P128" s="4"/>
+      <c r="Q128" s="8"/>
+      <c r="R128" s="7"/>
       <c r="S128" s="4"/>
-      <c r="T128" s="8"/>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T128" s="4"/>
+      <c r="U128" s="8"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
       <c r="B129" s="7"/>
       <c r="C129" s="4"/>
@@ -8328,13 +8719,14 @@
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
       <c r="O129" s="4"/>
-      <c r="P129" s="8"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="8"/>
+      <c r="R129" s="7"/>
       <c r="S129" s="4"/>
-      <c r="T129" s="8"/>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T129" s="4"/>
+      <c r="U129" s="8"/>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="7"/>
       <c r="C130" s="4"/>
@@ -8350,13 +8742,14 @@
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
       <c r="O130" s="4"/>
-      <c r="P130" s="8"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="4"/>
+      <c r="P130" s="4"/>
+      <c r="Q130" s="8"/>
+      <c r="R130" s="7"/>
       <c r="S130" s="4"/>
-      <c r="T130" s="8"/>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T130" s="4"/>
+      <c r="U130" s="8"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
       <c r="B131" s="7"/>
       <c r="C131" s="4"/>
@@ -8372,13 +8765,14 @@
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
       <c r="O131" s="4"/>
-      <c r="P131" s="8"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="4"/>
+      <c r="P131" s="4"/>
+      <c r="Q131" s="8"/>
+      <c r="R131" s="7"/>
       <c r="S131" s="4"/>
-      <c r="T131" s="8"/>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T131" s="4"/>
+      <c r="U131" s="8"/>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
       <c r="B132" s="7"/>
       <c r="C132" s="4"/>
@@ -8394,13 +8788,14 @@
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
       <c r="O132" s="4"/>
-      <c r="P132" s="8"/>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="4"/>
+      <c r="P132" s="4"/>
+      <c r="Q132" s="8"/>
+      <c r="R132" s="7"/>
       <c r="S132" s="4"/>
-      <c r="T132" s="8"/>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T132" s="4"/>
+      <c r="U132" s="8"/>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
       <c r="B133" s="7"/>
       <c r="C133" s="4"/>
@@ -8416,13 +8811,14 @@
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
       <c r="O133" s="4"/>
-      <c r="P133" s="8"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="4"/>
+      <c r="P133" s="4"/>
+      <c r="Q133" s="8"/>
+      <c r="R133" s="7"/>
       <c r="S133" s="4"/>
-      <c r="T133" s="8"/>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T133" s="4"/>
+      <c r="U133" s="8"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
       <c r="B134" s="7"/>
       <c r="C134" s="4"/>
@@ -8438,13 +8834,14 @@
       <c r="M134" s="4"/>
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
-      <c r="P134" s="8"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="4"/>
+      <c r="P134" s="4"/>
+      <c r="Q134" s="8"/>
+      <c r="R134" s="7"/>
       <c r="S134" s="4"/>
-      <c r="T134" s="8"/>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T134" s="4"/>
+      <c r="U134" s="8"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="7"/>
       <c r="C135" s="4"/>
@@ -8460,13 +8857,14 @@
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
       <c r="O135" s="4"/>
-      <c r="P135" s="8"/>
-      <c r="Q135" s="7"/>
-      <c r="R135" s="4"/>
+      <c r="P135" s="4"/>
+      <c r="Q135" s="8"/>
+      <c r="R135" s="7"/>
       <c r="S135" s="4"/>
-      <c r="T135" s="8"/>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T135" s="4"/>
+      <c r="U135" s="8"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="7"/>
       <c r="C136" s="4"/>
@@ -8482,13 +8880,14 @@
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
       <c r="O136" s="4"/>
-      <c r="P136" s="8"/>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="4"/>
+      <c r="P136" s="4"/>
+      <c r="Q136" s="8"/>
+      <c r="R136" s="7"/>
       <c r="S136" s="4"/>
-      <c r="T136" s="8"/>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T136" s="4"/>
+      <c r="U136" s="8"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="7"/>
       <c r="C137" s="4"/>
@@ -8504,13 +8903,14 @@
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
       <c r="O137" s="4"/>
-      <c r="P137" s="8"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="4"/>
+      <c r="P137" s="4"/>
+      <c r="Q137" s="8"/>
+      <c r="R137" s="7"/>
       <c r="S137" s="4"/>
-      <c r="T137" s="8"/>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T137" s="4"/>
+      <c r="U137" s="8"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="7"/>
       <c r="C138" s="4"/>
@@ -8526,13 +8926,14 @@
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
-      <c r="P138" s="8"/>
-      <c r="Q138" s="7"/>
-      <c r="R138" s="4"/>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="8"/>
+      <c r="R138" s="7"/>
       <c r="S138" s="4"/>
-      <c r="T138" s="8"/>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T138" s="4"/>
+      <c r="U138" s="8"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="7"/>
       <c r="C139" s="4"/>
@@ -8548,13 +8949,14 @@
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
-      <c r="P139" s="8"/>
-      <c r="Q139" s="7"/>
-      <c r="R139" s="4"/>
+      <c r="P139" s="4"/>
+      <c r="Q139" s="8"/>
+      <c r="R139" s="7"/>
       <c r="S139" s="4"/>
-      <c r="T139" s="8"/>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T139" s="4"/>
+      <c r="U139" s="8"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="7"/>
       <c r="C140" s="4"/>
@@ -8570,13 +8972,14 @@
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
       <c r="O140" s="4"/>
-      <c r="P140" s="8"/>
-      <c r="Q140" s="7"/>
-      <c r="R140" s="4"/>
+      <c r="P140" s="4"/>
+      <c r="Q140" s="8"/>
+      <c r="R140" s="7"/>
       <c r="S140" s="4"/>
-      <c r="T140" s="8"/>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T140" s="4"/>
+      <c r="U140" s="8"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="7"/>
       <c r="C141" s="4"/>
@@ -8592,13 +8995,14 @@
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
       <c r="O141" s="4"/>
-      <c r="P141" s="8"/>
-      <c r="Q141" s="7"/>
-      <c r="R141" s="4"/>
+      <c r="P141" s="4"/>
+      <c r="Q141" s="8"/>
+      <c r="R141" s="7"/>
       <c r="S141" s="4"/>
-      <c r="T141" s="8"/>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T141" s="4"/>
+      <c r="U141" s="8"/>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
       <c r="B142" s="7"/>
       <c r="C142" s="4"/>
@@ -8614,13 +9018,14 @@
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
       <c r="O142" s="4"/>
-      <c r="P142" s="8"/>
-      <c r="Q142" s="7"/>
-      <c r="R142" s="4"/>
+      <c r="P142" s="4"/>
+      <c r="Q142" s="8"/>
+      <c r="R142" s="7"/>
       <c r="S142" s="4"/>
-      <c r="T142" s="8"/>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T142" s="4"/>
+      <c r="U142" s="8"/>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="7"/>
       <c r="C143" s="4"/>
@@ -8636,13 +9041,14 @@
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
       <c r="O143" s="4"/>
-      <c r="P143" s="8"/>
-      <c r="Q143" s="7"/>
-      <c r="R143" s="4"/>
+      <c r="P143" s="4"/>
+      <c r="Q143" s="8"/>
+      <c r="R143" s="7"/>
       <c r="S143" s="4"/>
-      <c r="T143" s="8"/>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T143" s="4"/>
+      <c r="U143" s="8"/>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="7"/>
       <c r="C144" s="4"/>
@@ -8658,13 +9064,14 @@
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
       <c r="O144" s="4"/>
-      <c r="P144" s="8"/>
-      <c r="Q144" s="7"/>
-      <c r="R144" s="4"/>
+      <c r="P144" s="4"/>
+      <c r="Q144" s="8"/>
+      <c r="R144" s="7"/>
       <c r="S144" s="4"/>
-      <c r="T144" s="8"/>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T144" s="4"/>
+      <c r="U144" s="8"/>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="7"/>
       <c r="C145" s="4"/>
@@ -8680,13 +9087,14 @@
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
       <c r="O145" s="4"/>
-      <c r="P145" s="8"/>
-      <c r="Q145" s="7"/>
-      <c r="R145" s="4"/>
+      <c r="P145" s="4"/>
+      <c r="Q145" s="8"/>
+      <c r="R145" s="7"/>
       <c r="S145" s="4"/>
-      <c r="T145" s="8"/>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T145" s="4"/>
+      <c r="U145" s="8"/>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="7"/>
       <c r="C146" s="4"/>
@@ -8702,13 +9110,14 @@
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
       <c r="O146" s="4"/>
-      <c r="P146" s="8"/>
-      <c r="Q146" s="7"/>
-      <c r="R146" s="4"/>
+      <c r="P146" s="4"/>
+      <c r="Q146" s="8"/>
+      <c r="R146" s="7"/>
       <c r="S146" s="4"/>
-      <c r="T146" s="8"/>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T146" s="4"/>
+      <c r="U146" s="8"/>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="7"/>
       <c r="C147" s="4"/>
@@ -8724,13 +9133,14 @@
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
       <c r="O147" s="4"/>
-      <c r="P147" s="8"/>
-      <c r="Q147" s="7"/>
-      <c r="R147" s="4"/>
+      <c r="P147" s="4"/>
+      <c r="Q147" s="8"/>
+      <c r="R147" s="7"/>
       <c r="S147" s="4"/>
-      <c r="T147" s="8"/>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T147" s="4"/>
+      <c r="U147" s="8"/>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="7"/>
       <c r="C148" s="4"/>
@@ -8746,13 +9156,14 @@
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
       <c r="O148" s="4"/>
-      <c r="P148" s="8"/>
-      <c r="Q148" s="7"/>
-      <c r="R148" s="4"/>
+      <c r="P148" s="4"/>
+      <c r="Q148" s="8"/>
+      <c r="R148" s="7"/>
       <c r="S148" s="4"/>
-      <c r="T148" s="8"/>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T148" s="4"/>
+      <c r="U148" s="8"/>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="7"/>
       <c r="C149" s="4"/>
@@ -8768,13 +9179,14 @@
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
       <c r="O149" s="4"/>
-      <c r="P149" s="8"/>
-      <c r="Q149" s="7"/>
-      <c r="R149" s="4"/>
+      <c r="P149" s="4"/>
+      <c r="Q149" s="8"/>
+      <c r="R149" s="7"/>
       <c r="S149" s="4"/>
-      <c r="T149" s="8"/>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T149" s="4"/>
+      <c r="U149" s="8"/>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="7"/>
       <c r="C150" s="4"/>
@@ -8790,13 +9202,14 @@
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
       <c r="O150" s="4"/>
-      <c r="P150" s="8"/>
-      <c r="Q150" s="7"/>
-      <c r="R150" s="4"/>
+      <c r="P150" s="4"/>
+      <c r="Q150" s="8"/>
+      <c r="R150" s="7"/>
       <c r="S150" s="4"/>
-      <c r="T150" s="8"/>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T150" s="4"/>
+      <c r="U150" s="8"/>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="7"/>
       <c r="C151" s="4"/>
@@ -8812,13 +9225,14 @@
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
       <c r="O151" s="4"/>
-      <c r="P151" s="8"/>
-      <c r="Q151" s="7"/>
-      <c r="R151" s="4"/>
+      <c r="P151" s="4"/>
+      <c r="Q151" s="8"/>
+      <c r="R151" s="7"/>
       <c r="S151" s="4"/>
-      <c r="T151" s="8"/>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T151" s="4"/>
+      <c r="U151" s="8"/>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="7"/>
       <c r="C152" s="4"/>
@@ -8834,13 +9248,14 @@
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
       <c r="O152" s="4"/>
-      <c r="P152" s="8"/>
-      <c r="Q152" s="7"/>
-      <c r="R152" s="4"/>
+      <c r="P152" s="4"/>
+      <c r="Q152" s="8"/>
+      <c r="R152" s="7"/>
       <c r="S152" s="4"/>
-      <c r="T152" s="8"/>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T152" s="4"/>
+      <c r="U152" s="8"/>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="7"/>
       <c r="C153" s="4"/>
@@ -8856,13 +9271,14 @@
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
       <c r="O153" s="4"/>
-      <c r="P153" s="8"/>
-      <c r="Q153" s="7"/>
-      <c r="R153" s="4"/>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="8"/>
+      <c r="R153" s="7"/>
       <c r="S153" s="4"/>
-      <c r="T153" s="8"/>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T153" s="4"/>
+      <c r="U153" s="8"/>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="7"/>
       <c r="C154" s="4"/>
@@ -8878,13 +9294,14 @@
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
       <c r="O154" s="4"/>
-      <c r="P154" s="8"/>
-      <c r="Q154" s="7"/>
-      <c r="R154" s="4"/>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="8"/>
+      <c r="R154" s="7"/>
       <c r="S154" s="4"/>
-      <c r="T154" s="8"/>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T154" s="4"/>
+      <c r="U154" s="8"/>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="7"/>
       <c r="C155" s="4"/>
@@ -8900,13 +9317,14 @@
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
       <c r="O155" s="4"/>
-      <c r="P155" s="8"/>
-      <c r="Q155" s="7"/>
-      <c r="R155" s="4"/>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="8"/>
+      <c r="R155" s="7"/>
       <c r="S155" s="4"/>
-      <c r="T155" s="8"/>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T155" s="4"/>
+      <c r="U155" s="8"/>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="7"/>
       <c r="C156" s="4"/>
@@ -8922,13 +9340,14 @@
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
       <c r="O156" s="4"/>
-      <c r="P156" s="8"/>
-      <c r="Q156" s="7"/>
-      <c r="R156" s="4"/>
+      <c r="P156" s="4"/>
+      <c r="Q156" s="8"/>
+      <c r="R156" s="7"/>
       <c r="S156" s="4"/>
-      <c r="T156" s="8"/>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T156" s="4"/>
+      <c r="U156" s="8"/>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="7"/>
       <c r="C157" s="4"/>
@@ -8944,13 +9363,14 @@
       <c r="M157" s="4"/>
       <c r="N157" s="4"/>
       <c r="O157" s="4"/>
-      <c r="P157" s="8"/>
-      <c r="Q157" s="7"/>
-      <c r="R157" s="4"/>
+      <c r="P157" s="4"/>
+      <c r="Q157" s="8"/>
+      <c r="R157" s="7"/>
       <c r="S157" s="4"/>
-      <c r="T157" s="8"/>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T157" s="4"/>
+      <c r="U157" s="8"/>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="7"/>
       <c r="C158" s="4"/>
@@ -8966,13 +9386,14 @@
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
       <c r="O158" s="4"/>
-      <c r="P158" s="8"/>
-      <c r="Q158" s="7"/>
-      <c r="R158" s="4"/>
+      <c r="P158" s="4"/>
+      <c r="Q158" s="8"/>
+      <c r="R158" s="7"/>
       <c r="S158" s="4"/>
-      <c r="T158" s="8"/>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T158" s="4"/>
+      <c r="U158" s="8"/>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="7"/>
       <c r="C159" s="4"/>
@@ -8988,13 +9409,14 @@
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
       <c r="O159" s="4"/>
-      <c r="P159" s="8"/>
-      <c r="Q159" s="7"/>
-      <c r="R159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="8"/>
+      <c r="R159" s="7"/>
       <c r="S159" s="4"/>
-      <c r="T159" s="8"/>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T159" s="4"/>
+      <c r="U159" s="8"/>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="7"/>
       <c r="C160" s="4"/>
@@ -9010,13 +9432,14 @@
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
       <c r="O160" s="4"/>
-      <c r="P160" s="8"/>
-      <c r="Q160" s="7"/>
-      <c r="R160" s="4"/>
+      <c r="P160" s="4"/>
+      <c r="Q160" s="8"/>
+      <c r="R160" s="7"/>
       <c r="S160" s="4"/>
-      <c r="T160" s="8"/>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T160" s="4"/>
+      <c r="U160" s="8"/>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="7"/>
       <c r="C161" s="4"/>
@@ -9032,13 +9455,14 @@
       <c r="M161" s="4"/>
       <c r="N161" s="4"/>
       <c r="O161" s="4"/>
-      <c r="P161" s="8"/>
-      <c r="Q161" s="7"/>
-      <c r="R161" s="4"/>
+      <c r="P161" s="4"/>
+      <c r="Q161" s="8"/>
+      <c r="R161" s="7"/>
       <c r="S161" s="4"/>
-      <c r="T161" s="8"/>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T161" s="4"/>
+      <c r="U161" s="8"/>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="7"/>
       <c r="C162" s="4"/>
@@ -9054,13 +9478,14 @@
       <c r="M162" s="4"/>
       <c r="N162" s="4"/>
       <c r="O162" s="4"/>
-      <c r="P162" s="8"/>
-      <c r="Q162" s="7"/>
-      <c r="R162" s="4"/>
+      <c r="P162" s="4"/>
+      <c r="Q162" s="8"/>
+      <c r="R162" s="7"/>
       <c r="S162" s="4"/>
-      <c r="T162" s="8"/>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T162" s="4"/>
+      <c r="U162" s="8"/>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="7"/>
       <c r="C163" s="4"/>
@@ -9076,13 +9501,14 @@
       <c r="M163" s="4"/>
       <c r="N163" s="4"/>
       <c r="O163" s="4"/>
-      <c r="P163" s="8"/>
-      <c r="Q163" s="7"/>
-      <c r="R163" s="4"/>
+      <c r="P163" s="4"/>
+      <c r="Q163" s="8"/>
+      <c r="R163" s="7"/>
       <c r="S163" s="4"/>
-      <c r="T163" s="8"/>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T163" s="4"/>
+      <c r="U163" s="8"/>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="7"/>
       <c r="C164" s="4"/>
@@ -9098,13 +9524,14 @@
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
       <c r="O164" s="4"/>
-      <c r="P164" s="8"/>
-      <c r="Q164" s="7"/>
-      <c r="R164" s="4"/>
+      <c r="P164" s="4"/>
+      <c r="Q164" s="8"/>
+      <c r="R164" s="7"/>
       <c r="S164" s="4"/>
-      <c r="T164" s="8"/>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T164" s="4"/>
+      <c r="U164" s="8"/>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="7"/>
       <c r="C165" s="4"/>
@@ -9120,13 +9547,14 @@
       <c r="M165" s="4"/>
       <c r="N165" s="4"/>
       <c r="O165" s="4"/>
-      <c r="P165" s="8"/>
-      <c r="Q165" s="7"/>
-      <c r="R165" s="4"/>
+      <c r="P165" s="4"/>
+      <c r="Q165" s="8"/>
+      <c r="R165" s="7"/>
       <c r="S165" s="4"/>
-      <c r="T165" s="8"/>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T165" s="4"/>
+      <c r="U165" s="8"/>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="7"/>
       <c r="C166" s="4"/>
@@ -9142,13 +9570,14 @@
       <c r="M166" s="4"/>
       <c r="N166" s="4"/>
       <c r="O166" s="4"/>
-      <c r="P166" s="8"/>
-      <c r="Q166" s="7"/>
-      <c r="R166" s="4"/>
+      <c r="P166" s="4"/>
+      <c r="Q166" s="8"/>
+      <c r="R166" s="7"/>
       <c r="S166" s="4"/>
-      <c r="T166" s="8"/>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T166" s="4"/>
+      <c r="U166" s="8"/>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="7"/>
       <c r="C167" s="4"/>
@@ -9164,13 +9593,14 @@
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
       <c r="O167" s="4"/>
-      <c r="P167" s="8"/>
-      <c r="Q167" s="7"/>
-      <c r="R167" s="4"/>
+      <c r="P167" s="4"/>
+      <c r="Q167" s="8"/>
+      <c r="R167" s="7"/>
       <c r="S167" s="4"/>
-      <c r="T167" s="8"/>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T167" s="4"/>
+      <c r="U167" s="8"/>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="7"/>
       <c r="C168" s="4"/>
@@ -9186,13 +9616,14 @@
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
       <c r="O168" s="4"/>
-      <c r="P168" s="8"/>
-      <c r="Q168" s="7"/>
-      <c r="R168" s="4"/>
+      <c r="P168" s="4"/>
+      <c r="Q168" s="8"/>
+      <c r="R168" s="7"/>
       <c r="S168" s="4"/>
-      <c r="T168" s="8"/>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T168" s="4"/>
+      <c r="U168" s="8"/>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="7"/>
       <c r="C169" s="4"/>
@@ -9208,13 +9639,14 @@
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
       <c r="O169" s="4"/>
-      <c r="P169" s="8"/>
-      <c r="Q169" s="7"/>
-      <c r="R169" s="4"/>
+      <c r="P169" s="4"/>
+      <c r="Q169" s="8"/>
+      <c r="R169" s="7"/>
       <c r="S169" s="4"/>
-      <c r="T169" s="8"/>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T169" s="4"/>
+      <c r="U169" s="8"/>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="7"/>
       <c r="C170" s="4"/>
@@ -9230,13 +9662,14 @@
       <c r="M170" s="4"/>
       <c r="N170" s="4"/>
       <c r="O170" s="4"/>
-      <c r="P170" s="8"/>
-      <c r="Q170" s="7"/>
-      <c r="R170" s="4"/>
+      <c r="P170" s="4"/>
+      <c r="Q170" s="8"/>
+      <c r="R170" s="7"/>
       <c r="S170" s="4"/>
-      <c r="T170" s="8"/>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T170" s="4"/>
+      <c r="U170" s="8"/>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="7"/>
       <c r="C171" s="4"/>
@@ -9252,13 +9685,14 @@
       <c r="M171" s="4"/>
       <c r="N171" s="4"/>
       <c r="O171" s="4"/>
-      <c r="P171" s="8"/>
-      <c r="Q171" s="7"/>
-      <c r="R171" s="4"/>
+      <c r="P171" s="4"/>
+      <c r="Q171" s="8"/>
+      <c r="R171" s="7"/>
       <c r="S171" s="4"/>
-      <c r="T171" s="8"/>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T171" s="4"/>
+      <c r="U171" s="8"/>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="7"/>
       <c r="C172" s="4"/>
@@ -9274,13 +9708,14 @@
       <c r="M172" s="4"/>
       <c r="N172" s="4"/>
       <c r="O172" s="4"/>
-      <c r="P172" s="8"/>
-      <c r="Q172" s="7"/>
-      <c r="R172" s="4"/>
+      <c r="P172" s="4"/>
+      <c r="Q172" s="8"/>
+      <c r="R172" s="7"/>
       <c r="S172" s="4"/>
-      <c r="T172" s="8"/>
-    </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T172" s="4"/>
+      <c r="U172" s="8"/>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="7"/>
       <c r="C173" s="4"/>
@@ -9296,13 +9731,14 @@
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
       <c r="O173" s="4"/>
-      <c r="P173" s="8"/>
-      <c r="Q173" s="7"/>
-      <c r="R173" s="4"/>
+      <c r="P173" s="4"/>
+      <c r="Q173" s="8"/>
+      <c r="R173" s="7"/>
       <c r="S173" s="4"/>
-      <c r="T173" s="8"/>
-    </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T173" s="4"/>
+      <c r="U173" s="8"/>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="7"/>
       <c r="C174" s="4"/>
@@ -9318,13 +9754,14 @@
       <c r="M174" s="4"/>
       <c r="N174" s="4"/>
       <c r="O174" s="4"/>
-      <c r="P174" s="8"/>
-      <c r="Q174" s="7"/>
-      <c r="R174" s="4"/>
+      <c r="P174" s="4"/>
+      <c r="Q174" s="8"/>
+      <c r="R174" s="7"/>
       <c r="S174" s="4"/>
-      <c r="T174" s="8"/>
-    </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T174" s="4"/>
+      <c r="U174" s="8"/>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="7"/>
       <c r="C175" s="4"/>
@@ -9340,13 +9777,14 @@
       <c r="M175" s="4"/>
       <c r="N175" s="4"/>
       <c r="O175" s="4"/>
-      <c r="P175" s="8"/>
-      <c r="Q175" s="7"/>
-      <c r="R175" s="4"/>
+      <c r="P175" s="4"/>
+      <c r="Q175" s="8"/>
+      <c r="R175" s="7"/>
       <c r="S175" s="4"/>
-      <c r="T175" s="8"/>
-    </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T175" s="4"/>
+      <c r="U175" s="8"/>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="7"/>
       <c r="C176" s="4"/>
@@ -9362,13 +9800,14 @@
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
       <c r="O176" s="4"/>
-      <c r="P176" s="8"/>
-      <c r="Q176" s="7"/>
-      <c r="R176" s="4"/>
+      <c r="P176" s="4"/>
+      <c r="Q176" s="8"/>
+      <c r="R176" s="7"/>
       <c r="S176" s="4"/>
-      <c r="T176" s="8"/>
-    </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T176" s="4"/>
+      <c r="U176" s="8"/>
+    </row>
+    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="7"/>
       <c r="C177" s="4"/>
@@ -9384,19 +9823,21 @@
       <c r="M177" s="4"/>
       <c r="N177" s="4"/>
       <c r="O177" s="4"/>
-      <c r="P177" s="8"/>
-      <c r="Q177" s="7"/>
-      <c r="R177" s="4"/>
+      <c r="P177" s="4"/>
+      <c r="Q177" s="8"/>
+      <c r="R177" s="7"/>
       <c r="S177" s="4"/>
-      <c r="T177" s="8"/>
+      <c r="T177" s="4"/>
+      <c r="U177" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="R1:U1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F7FF4F-F875-4841-888C-3E8F752B138F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F12DA77-79F2-4C9B-BB69-473D80C6E1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info Sim" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="33">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -129,24 +129,25 @@
     <t>N</t>
   </si>
   <si>
-    <t>0,718; 0,00; 0,155; 0,127</t>
+    <t>Delta_t</t>
   </si>
   <si>
-    <t>Butanol</t>
+    <t>Heptano;Eicosano</t>
   </si>
   <si>
-    <t>1,0;</t>
+    <t>0,7248;0,00;0,1513;0,1239</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000000000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +173,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -431,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -484,6 +492,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -505,7 +519,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -788,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EF3E57-CE6A-4B11-A29F-455A2AA99755}">
-  <dimension ref="A1:U167"/>
+  <dimension ref="A1:V167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
@@ -818,34 +847,34 @@
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22" t="s">
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="22" t="s">
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="21"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="23"/>
     </row>
     <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -1530,7 +1559,7 @@
       <c r="U12" s="8"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="27">
+      <c r="A13" s="19">
         <v>2101</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -1596,7 +1625,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="27">
+      <c r="A14" s="19">
         <v>2102</v>
       </c>
       <c r="B14" s="14" t="s">
@@ -1662,7 +1691,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="27">
+      <c r="A15" s="19">
         <v>2103</v>
       </c>
       <c r="B15" s="14" t="s">
@@ -1728,7 +1757,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="27">
+      <c r="A16" s="19">
         <v>2104</v>
       </c>
       <c r="B16" s="14" t="s">
@@ -1794,7 +1823,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="27">
+      <c r="A17" s="19">
         <v>2105</v>
       </c>
       <c r="B17" s="14" t="s">
@@ -1860,7 +1889,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="27">
+      <c r="A18" s="19">
         <v>2106</v>
       </c>
       <c r="B18" s="14" t="s">
@@ -1926,7 +1955,7 @@
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="27">
+      <c r="A19" s="19">
         <v>2107</v>
       </c>
       <c r="B19" s="14" t="s">
@@ -1992,7 +2021,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="27">
+      <c r="A20" s="19">
         <v>2108</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -2058,7 +2087,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A21" s="27">
+      <c r="A21" s="20">
         <v>2109</v>
       </c>
       <c r="B21" s="14" t="s">
@@ -2140,7 +2169,7 @@
         <v>26</v>
       </c>
       <c r="F23" s="7">
-        <f t="shared" ref="F23:F35" si="2">(0.0001451)/2</f>
+        <f t="shared" ref="F23:F48" si="2">(0.0001451)/2</f>
         <v>7.2550000000000002E-5</v>
       </c>
       <c r="G23" s="4">
@@ -2256,7 +2285,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A25" s="27">
+      <c r="A25" s="19">
         <v>3103</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -2322,7 +2351,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="27">
+      <c r="A26" s="19">
         <v>3104</v>
       </c>
       <c r="B26" s="14" t="s">
@@ -2388,7 +2417,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="27">
+      <c r="A27" s="19">
         <v>3105</v>
       </c>
       <c r="B27" s="14" t="s">
@@ -2717,8 +2746,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A33" s="27">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="19">
         <v>4103</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -2783,8 +2812,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A34" s="27">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="19">
         <v>4104</v>
       </c>
       <c r="B34" s="14" t="s">
@@ -2849,8 +2878,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A35" s="27">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="19">
         <v>4105</v>
       </c>
       <c r="B35" s="14" t="s">
@@ -2915,7 +2944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="7"/>
       <c r="C36" s="4"/>
@@ -2938,281 +2967,752 @@
       <c r="T36" s="4"/>
       <c r="U36" s="8"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="8"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="5"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="8"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="8"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="8"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="8"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="5"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="8"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="8"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="8"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="5"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="8"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="5"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="8"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="8"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="8"/>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>5101</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G37" s="4">
+        <v>150</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I37" s="4">
+        <v>303</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K37" s="7">
+        <v>15</v>
+      </c>
+      <c r="L37" s="4">
+        <v>4</v>
+      </c>
+      <c r="M37" s="4">
+        <v>3</v>
+      </c>
+      <c r="N37" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O37" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R37" s="7">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4">
+        <v>1</v>
+      </c>
+      <c r="T37" s="4">
+        <v>500</v>
+      </c>
+      <c r="U37" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>5102</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G38" s="4">
+        <v>150</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I38" s="4">
+        <v>303</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K38" s="7">
+        <v>30</v>
+      </c>
+      <c r="L38" s="4">
+        <v>2</v>
+      </c>
+      <c r="M38" s="4">
+        <v>3</v>
+      </c>
+      <c r="N38" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="P38" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R38" s="7">
+        <v>0</v>
+      </c>
+      <c r="S38" s="4">
+        <v>1</v>
+      </c>
+      <c r="T38" s="4">
+        <v>500</v>
+      </c>
+      <c r="U38" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>5103</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G39" s="4">
+        <v>150</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I39" s="4">
+        <v>303</v>
+      </c>
+      <c r="J39" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K39" s="7">
+        <v>60</v>
+      </c>
+      <c r="L39" s="4">
+        <v>1</v>
+      </c>
+      <c r="M39" s="4">
+        <v>3</v>
+      </c>
+      <c r="N39" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O39" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="P39" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="4">
+        <v>1</v>
+      </c>
+      <c r="T39" s="4">
+        <v>500</v>
+      </c>
+      <c r="U39" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
+        <v>5104</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G40" s="4">
+        <v>150</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I40" s="4">
+        <v>303</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K40" s="7">
+        <v>25</v>
+      </c>
+      <c r="L40" s="4">
+        <v>4</v>
+      </c>
+      <c r="M40" s="4">
+        <v>3</v>
+      </c>
+      <c r="N40" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O40" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="P40" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R40" s="7">
+        <v>0</v>
+      </c>
+      <c r="S40" s="4">
+        <v>1</v>
+      </c>
+      <c r="T40" s="4">
+        <v>500</v>
+      </c>
+      <c r="U40" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
+        <v>5105</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G41" s="4">
+        <v>150</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I41" s="4">
+        <v>303</v>
+      </c>
+      <c r="J41" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K41" s="7">
+        <v>50</v>
+      </c>
+      <c r="L41" s="4">
+        <v>2</v>
+      </c>
+      <c r="M41" s="4">
+        <v>3</v>
+      </c>
+      <c r="N41" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="P41" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R41" s="7">
+        <v>0</v>
+      </c>
+      <c r="S41" s="4">
+        <v>1</v>
+      </c>
+      <c r="T41" s="4">
+        <v>500</v>
+      </c>
+      <c r="U41" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
+        <v>5106</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F42" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G42" s="4">
+        <v>150</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I42" s="4">
+        <v>303</v>
+      </c>
+      <c r="J42" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K42" s="7">
+        <v>100</v>
+      </c>
+      <c r="L42" s="4">
+        <v>1</v>
+      </c>
+      <c r="M42" s="4">
+        <v>3</v>
+      </c>
+      <c r="N42" s="4">
+        <v>1E-8</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="P42" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R42" s="7">
+        <v>0</v>
+      </c>
+      <c r="S42" s="4">
+        <v>1</v>
+      </c>
+      <c r="T42" s="4">
+        <v>500</v>
+      </c>
+      <c r="U42" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
+        <v>6101</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G44" s="4">
+        <v>150</v>
+      </c>
+      <c r="H44" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I44" s="4">
+        <v>303</v>
+      </c>
+      <c r="J44" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K44" s="7">
+        <v>50</v>
+      </c>
+      <c r="L44" s="4">
+        <v>1</v>
+      </c>
+      <c r="M44" s="4">
+        <v>8</v>
+      </c>
+      <c r="N44" s="4">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="O44" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P44" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="21">
+        <v>1E-4</v>
+      </c>
+      <c r="R44" s="7">
+        <v>0</v>
+      </c>
+      <c r="S44" s="4">
+        <v>1</v>
+      </c>
+      <c r="T44" s="4">
+        <v>500</v>
+      </c>
+      <c r="U44" s="8">
+        <v>2</v>
+      </c>
+      <c r="V44" s="4">
+        <v>2.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
+        <v>6102</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G45" s="4">
+        <v>150</v>
+      </c>
+      <c r="H45" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I45" s="4">
+        <v>303</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K45" s="7">
+        <v>50</v>
+      </c>
+      <c r="L45" s="4">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4">
+        <v>8</v>
+      </c>
+      <c r="N45" s="4">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="O45" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P45" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="21">
+        <v>1E-4</v>
+      </c>
+      <c r="R45" s="7">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4">
+        <v>1</v>
+      </c>
+      <c r="T45" s="4">
+        <v>500</v>
+      </c>
+      <c r="U45" s="8">
+        <v>2</v>
+      </c>
+      <c r="V45" s="4">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>6103</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G46" s="4">
+        <v>150</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I46" s="4">
+        <v>303</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K46" s="7">
+        <v>50</v>
+      </c>
+      <c r="L46" s="4">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4">
+        <v>8</v>
+      </c>
+      <c r="N46" s="4">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="O46" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P46" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="21">
+        <v>1E-4</v>
+      </c>
+      <c r="R46" s="7">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4">
+        <v>1</v>
+      </c>
+      <c r="T46" s="4">
+        <v>500</v>
+      </c>
+      <c r="U46" s="8">
+        <v>2</v>
+      </c>
+      <c r="V46" s="4">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
+        <v>6104</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G47" s="4">
+        <v>150</v>
+      </c>
+      <c r="H47" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I47" s="4">
+        <v>303</v>
+      </c>
+      <c r="J47" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K47" s="7">
+        <v>50</v>
+      </c>
+      <c r="L47" s="4">
+        <v>1</v>
+      </c>
+      <c r="M47" s="4">
+        <v>8</v>
+      </c>
+      <c r="N47" s="4">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="O47" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P47" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="21">
+        <v>1E-4</v>
+      </c>
+      <c r="R47" s="7">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4">
+        <v>1</v>
+      </c>
+      <c r="T47" s="4">
+        <v>500</v>
+      </c>
+      <c r="U47" s="8">
+        <v>2</v>
+      </c>
+      <c r="V47" s="4">
+        <v>2.5000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
+        <v>6105</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" s="7">
+        <f t="shared" si="2"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G48" s="4">
+        <v>150</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I48" s="4">
+        <v>303</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K48" s="7">
+        <v>50</v>
+      </c>
+      <c r="L48" s="4">
+        <v>1</v>
+      </c>
+      <c r="M48" s="4">
+        <v>8</v>
+      </c>
+      <c r="N48" s="4">
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="O48" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P48" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="21">
+        <v>1E-4</v>
+      </c>
+      <c r="R48" s="7">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4">
+        <v>1</v>
+      </c>
+      <c r="T48" s="4">
+        <v>500</v>
+      </c>
+      <c r="U48" s="8">
+        <v>2</v>
+      </c>
+      <c r="V48" s="4">
+        <f>V47/2</f>
+        <v>1.2500000000000001E-6</v>
+      </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
@@ -3238,119 +3738,329 @@
       <c r="U49" s="8"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A50" s="5"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="8"/>
+      <c r="A50" s="29">
+        <v>1301</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" s="32">
+        <v>3.6275000000000001E-5</v>
+      </c>
+      <c r="G50" s="30">
+        <v>150</v>
+      </c>
+      <c r="H50" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I50" s="30">
+        <v>340</v>
+      </c>
+      <c r="J50" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K50" s="32">
+        <v>30</v>
+      </c>
+      <c r="L50" s="30">
+        <v>1</v>
+      </c>
+      <c r="M50" s="30">
+        <v>7</v>
+      </c>
+      <c r="N50" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O50" s="30">
+        <v>10</v>
+      </c>
+      <c r="P50" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R50" s="32">
+        <v>0</v>
+      </c>
+      <c r="S50" s="30">
+        <v>1</v>
+      </c>
+      <c r="T50" s="30">
+        <v>500</v>
+      </c>
+      <c r="U50" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="8"/>
+      <c r="A51" s="29">
+        <v>1302</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="32">
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G51" s="30">
+        <v>150</v>
+      </c>
+      <c r="H51" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I51" s="30">
+        <v>340</v>
+      </c>
+      <c r="J51" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K51" s="32">
+        <v>30</v>
+      </c>
+      <c r="L51" s="30">
+        <v>1</v>
+      </c>
+      <c r="M51" s="30">
+        <v>7</v>
+      </c>
+      <c r="N51" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O51" s="30">
+        <v>10</v>
+      </c>
+      <c r="P51" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R51" s="32">
+        <v>0</v>
+      </c>
+      <c r="S51" s="30">
+        <v>1</v>
+      </c>
+      <c r="T51" s="30">
+        <v>500</v>
+      </c>
+      <c r="U51" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="8"/>
+      <c r="A52" s="29">
+        <v>1303</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" s="32">
+        <v>1.451E-4</v>
+      </c>
+      <c r="G52" s="30">
+        <v>150</v>
+      </c>
+      <c r="H52" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I52" s="30">
+        <v>340</v>
+      </c>
+      <c r="J52" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K52" s="32">
+        <v>30</v>
+      </c>
+      <c r="L52" s="30">
+        <v>1</v>
+      </c>
+      <c r="M52" s="30">
+        <v>7</v>
+      </c>
+      <c r="N52" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O52" s="30">
+        <v>10</v>
+      </c>
+      <c r="P52" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R52" s="32">
+        <v>0</v>
+      </c>
+      <c r="S52" s="30">
+        <v>1</v>
+      </c>
+      <c r="T52" s="30">
+        <v>500</v>
+      </c>
+      <c r="U52" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="8"/>
+      <c r="A53" s="29">
+        <v>1304</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" s="32">
+        <v>2.1765E-4</v>
+      </c>
+      <c r="G53" s="30">
+        <v>150</v>
+      </c>
+      <c r="H53" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I53" s="30">
+        <v>340</v>
+      </c>
+      <c r="J53" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K53" s="32">
+        <v>30</v>
+      </c>
+      <c r="L53" s="30">
+        <v>1</v>
+      </c>
+      <c r="M53" s="30">
+        <v>7</v>
+      </c>
+      <c r="N53" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O53" s="30">
+        <v>10</v>
+      </c>
+      <c r="P53" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R53" s="32">
+        <v>0</v>
+      </c>
+      <c r="S53" s="30">
+        <v>1</v>
+      </c>
+      <c r="T53" s="30">
+        <v>500</v>
+      </c>
+      <c r="U53" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="5"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="8"/>
+      <c r="A54" s="29">
+        <v>1305</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" s="32">
+        <v>2.9020000000000001E-4</v>
+      </c>
+      <c r="G54" s="30">
+        <v>150</v>
+      </c>
+      <c r="H54" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I54" s="30">
+        <v>340</v>
+      </c>
+      <c r="J54" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K54" s="32">
+        <v>30</v>
+      </c>
+      <c r="L54" s="30">
+        <v>1</v>
+      </c>
+      <c r="M54" s="30">
+        <v>7</v>
+      </c>
+      <c r="N54" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O54" s="30">
+        <v>10</v>
+      </c>
+      <c r="P54" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R54" s="32">
+        <v>0</v>
+      </c>
+      <c r="S54" s="30">
+        <v>1</v>
+      </c>
+      <c r="T54" s="30">
+        <v>500</v>
+      </c>
+      <c r="U54" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
@@ -5964,7 +6674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2F00BA-95B2-42FB-9A66-5FDDA7DC61DE}">
-  <dimension ref="A1:U166"/>
+  <dimension ref="A1:U163"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
@@ -5994,34 +6704,34 @@
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="23" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="23" t="s">
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="23" t="s">
+      <c r="L1" s="28"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="25"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="27"/>
     </row>
     <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -6089,162 +6799,329 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>5101</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="29">
+        <v>1301</v>
+      </c>
+      <c r="B3" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="F3" s="32">
+        <v>3.6275000000000001E-5</v>
+      </c>
+      <c r="G3" s="30">
+        <v>150</v>
+      </c>
+      <c r="H3" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="30">
+        <v>340</v>
+      </c>
+      <c r="J3" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K3" s="32">
+        <v>30</v>
+      </c>
+      <c r="L3" s="30">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30">
+        <v>7</v>
+      </c>
+      <c r="N3" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O3" s="30">
+        <v>10</v>
+      </c>
+      <c r="P3" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R3" s="32">
+        <v>0</v>
+      </c>
+      <c r="S3" s="30">
+        <v>1</v>
+      </c>
+      <c r="T3" s="30">
+        <v>500</v>
+      </c>
+      <c r="U3" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="29">
+        <v>1302</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E4" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="32">
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G4" s="30">
+        <v>150</v>
+      </c>
+      <c r="H4" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="30">
+        <v>340</v>
+      </c>
+      <c r="J4" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K4" s="32">
         <v>30</v>
       </c>
-      <c r="F3" s="7">
-        <f>(0.0005012)/2</f>
-        <v>2.5060000000000002E-4</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="L4" s="30">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30">
+        <v>7</v>
+      </c>
+      <c r="N4" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O4" s="30">
+        <v>10</v>
+      </c>
+      <c r="P4" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R4" s="32">
+        <v>0</v>
+      </c>
+      <c r="S4" s="30">
+        <v>1</v>
+      </c>
+      <c r="T4" s="30">
+        <v>500</v>
+      </c>
+      <c r="U4" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="29">
+        <v>1303</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="32">
+        <v>1.451E-4</v>
+      </c>
+      <c r="G5" s="30">
         <v>150</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H5" s="30">
         <v>0.15</v>
       </c>
-      <c r="I3" s="4">
-        <v>328</v>
-      </c>
-      <c r="J3" s="8">
-        <v>1368</v>
-      </c>
-      <c r="K3" s="7">
+      <c r="I5" s="30">
+        <v>340</v>
+      </c>
+      <c r="J5" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K5" s="32">
         <v>30</v>
       </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>5</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1E-8</v>
-      </c>
-      <c r="O3" s="4">
+      <c r="L5" s="30">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30">
+        <v>7</v>
+      </c>
+      <c r="N5" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O5" s="30">
         <v>10</v>
       </c>
-      <c r="P3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="16">
+      <c r="P5" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="31">
         <v>1E-4</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R5" s="32">
         <v>0</v>
       </c>
-      <c r="S3" s="4">
-        <v>1</v>
-      </c>
-      <c r="T3" s="4">
+      <c r="S5" s="30">
+        <v>1</v>
+      </c>
+      <c r="T5" s="30">
         <v>500</v>
       </c>
-      <c r="U3" s="8">
+      <c r="U5" s="31">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="8"/>
-    </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="8"/>
+      <c r="A6" s="29">
+        <v>1304</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="32">
+        <v>2.1765E-4</v>
+      </c>
+      <c r="G6" s="30">
+        <v>150</v>
+      </c>
+      <c r="H6" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I6" s="30">
+        <v>340</v>
+      </c>
+      <c r="J6" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K6" s="32">
+        <v>30</v>
+      </c>
+      <c r="L6" s="30">
+        <v>1</v>
+      </c>
+      <c r="M6" s="30">
+        <v>7</v>
+      </c>
+      <c r="N6" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O6" s="30">
+        <v>10</v>
+      </c>
+      <c r="P6" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R6" s="32">
+        <v>0</v>
+      </c>
+      <c r="S6" s="30">
+        <v>1</v>
+      </c>
+      <c r="T6" s="30">
+        <v>500</v>
+      </c>
+      <c r="U6" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="8"/>
+      <c r="A7" s="29">
+        <v>1305</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="32">
+        <v>2.9020000000000001E-4</v>
+      </c>
+      <c r="G7" s="30">
+        <v>150</v>
+      </c>
+      <c r="H7" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="I7" s="30">
+        <v>340</v>
+      </c>
+      <c r="J7" s="31">
+        <v>1730</v>
+      </c>
+      <c r="K7" s="32">
+        <v>30</v>
+      </c>
+      <c r="L7" s="30">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30">
+        <v>7</v>
+      </c>
+      <c r="N7" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O7" s="30">
+        <v>10</v>
+      </c>
+      <c r="P7" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="R7" s="32">
+        <v>0</v>
+      </c>
+      <c r="S7" s="30">
+        <v>1</v>
+      </c>
+      <c r="T7" s="30">
+        <v>500</v>
+      </c>
+      <c r="U7" s="31">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -6398,7 +7275,7 @@
       <c r="K14" s="7"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="N14" s="17"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="16"/>
@@ -6421,7 +7298,7 @@
       <c r="K15" s="7"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
+      <c r="N15" s="17"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="16"/>
@@ -6444,7 +7321,7 @@
       <c r="K16" s="7"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="N16" s="17"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="16"/>
@@ -6455,9 +7332,9 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="14"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="15"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="8"/>
       <c r="F17" s="7"/>
       <c r="G17" s="4"/>
@@ -6467,10 +7344,10 @@
       <c r="K17" s="7"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="16"/>
+      <c r="Q17" s="8"/>
       <c r="R17" s="7"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -6478,9 +7355,9 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="14"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="15"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="8"/>
       <c r="F18" s="7"/>
       <c r="G18" s="4"/>
@@ -6490,10 +7367,10 @@
       <c r="K18" s="7"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="16"/>
+      <c r="Q18" s="8"/>
       <c r="R18" s="7"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -6501,9 +7378,9 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="14"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="15"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="8"/>
       <c r="F19" s="7"/>
       <c r="G19" s="4"/>
@@ -6513,10 +7390,10 @@
       <c r="K19" s="7"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="17"/>
+      <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
-      <c r="Q19" s="16"/>
+      <c r="Q19" s="8"/>
       <c r="R19" s="7"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
@@ -9834,75 +10711,6 @@
       <c r="T163" s="4"/>
       <c r="U163" s="8"/>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A164" s="5"/>
-      <c r="B164" s="7"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="8"/>
-      <c r="F164" s="7"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-      <c r="I164" s="4"/>
-      <c r="J164" s="8"/>
-      <c r="K164" s="7"/>
-      <c r="L164" s="4"/>
-      <c r="M164" s="4"/>
-      <c r="N164" s="4"/>
-      <c r="O164" s="4"/>
-      <c r="P164" s="4"/>
-      <c r="Q164" s="8"/>
-      <c r="R164" s="7"/>
-      <c r="S164" s="4"/>
-      <c r="T164" s="4"/>
-      <c r="U164" s="8"/>
-    </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A165" s="5"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="8"/>
-      <c r="K165" s="7"/>
-      <c r="L165" s="4"/>
-      <c r="M165" s="4"/>
-      <c r="N165" s="4"/>
-      <c r="O165" s="4"/>
-      <c r="P165" s="4"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="4"/>
-      <c r="T165" s="4"/>
-      <c r="U165" s="8"/>
-    </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A166" s="5"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-      <c r="I166" s="4"/>
-      <c r="J166" s="8"/>
-      <c r="K166" s="7"/>
-      <c r="L166" s="4"/>
-      <c r="M166" s="4"/>
-      <c r="N166" s="4"/>
-      <c r="O166" s="4"/>
-      <c r="P166" s="4"/>
-      <c r="Q166" s="8"/>
-      <c r="R166" s="7"/>
-      <c r="S166" s="4"/>
-      <c r="T166" s="4"/>
-      <c r="U166" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:E1"/>

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LVAROG~1\AppData\Roaming\MobaXterm\slash\RemoteFiles\66564_2_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F070DA52-7FA6-4AB4-B2FA-4EF19F6FCD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905757AE-40AB-42C4-A8DB-1A0F923B6E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info Sim" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="42">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -164,114 +164,6 @@
   <si>
     <t>0,7083;0,00;0,0972;0,1947</t>
   </si>
-  <si>
-    <t>output-7-0</t>
-  </si>
-  <si>
-    <t>output-7-1</t>
-  </si>
-  <si>
-    <t>output-7-2</t>
-  </si>
-  <si>
-    <t>output-7-3</t>
-  </si>
-  <si>
-    <t>output-7-4</t>
-  </si>
-  <si>
-    <t>output-7-5</t>
-  </si>
-  <si>
-    <t>output-7-6</t>
-  </si>
-  <si>
-    <t>output-7-7</t>
-  </si>
-  <si>
-    <t>output-7-8</t>
-  </si>
-  <si>
-    <t>output-7-9</t>
-  </si>
-  <si>
-    <t>output-7-10</t>
-  </si>
-  <si>
-    <t>output-7-11</t>
-  </si>
-  <si>
-    <t>output-33-0</t>
-  </si>
-  <si>
-    <t>output-91-0</t>
-  </si>
-  <si>
-    <t>output-81-0</t>
-  </si>
-  <si>
-    <t>output-81-1</t>
-  </si>
-  <si>
-    <t>output-81-2</t>
-  </si>
-  <si>
-    <t>output-101-0</t>
-  </si>
-  <si>
-    <t>output-111-0</t>
-  </si>
-  <si>
-    <t>output-111-1</t>
-  </si>
-  <si>
-    <t>output-111-2</t>
-  </si>
-  <si>
-    <t>output-111-3</t>
-  </si>
-  <si>
-    <t>output-111-4</t>
-  </si>
-  <si>
-    <t>output-111-5</t>
-  </si>
-  <si>
-    <t>output-111-6</t>
-  </si>
-  <si>
-    <t>output-111-7</t>
-  </si>
-  <si>
-    <t>output-111-8</t>
-  </si>
-  <si>
-    <t>output-121-0</t>
-  </si>
-  <si>
-    <t>output-121-1</t>
-  </si>
-  <si>
-    <t>output-121-2</t>
-  </si>
-  <si>
-    <t>output-121-3</t>
-  </si>
-  <si>
-    <t>output-121-4</t>
-  </si>
-  <si>
-    <t>output-121-5</t>
-  </si>
-  <si>
-    <t>output-121-6</t>
-  </si>
-  <si>
-    <t>output-121-7</t>
-  </si>
-  <si>
-    <t>output-121-8</t>
-  </si>
 </sst>
 </file>
 
@@ -327,7 +219,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,18 +241,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -677,9 +557,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -699,9 +576,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,34 +890,34 @@
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="36" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="35"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="34"/>
     </row>
     <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -4816,7 +4690,7 @@
         <v>3.7199999999999997E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="29">
         <v>2307</v>
       </c>
@@ -4881,7 +4755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="29">
         <v>2308</v>
       </c>
@@ -4946,7 +4820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="7"/>
       <c r="C67" s="4"/>
@@ -4969,7 +4843,7 @@
       <c r="T67" s="4"/>
       <c r="U67" s="8"/>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="18">
         <v>8101</v>
       </c>
@@ -5034,11 +4908,8 @@
       <c r="U68" s="8">
         <v>2</v>
       </c>
-      <c r="V68" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="18">
         <v>8102</v>
       </c>
@@ -5103,11 +4974,8 @@
       <c r="U69" s="8">
         <v>2</v>
       </c>
-      <c r="V69" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="18">
         <v>8103</v>
       </c>
@@ -5172,11 +5040,8 @@
       <c r="U70" s="8">
         <v>2</v>
       </c>
-      <c r="V70" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="19">
         <v>8104</v>
       </c>
@@ -5241,11 +5106,8 @@
       <c r="U71" s="8">
         <v>2</v>
       </c>
-      <c r="V71" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="19">
         <v>8105</v>
       </c>
@@ -5310,11 +5172,8 @@
       <c r="U72" s="8">
         <v>2</v>
       </c>
-      <c r="V72" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="19">
         <v>8106</v>
       </c>
@@ -5379,11 +5238,8 @@
       <c r="U73" s="8">
         <v>2</v>
       </c>
-      <c r="V73" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="19">
         <v>8107</v>
       </c>
@@ -5448,11 +5304,8 @@
       <c r="U74" s="8">
         <v>2</v>
       </c>
-      <c r="V74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>8108</v>
       </c>
@@ -5517,11 +5370,8 @@
       <c r="U75" s="8">
         <v>2</v>
       </c>
-      <c r="V75" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
         <v>8109</v>
       </c>
@@ -5586,11 +5436,8 @@
       <c r="U76" s="8">
         <v>2</v>
       </c>
-      <c r="V76" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
         <v>8110</v>
       </c>
@@ -5655,11 +5502,8 @@
       <c r="U77" s="8">
         <v>2</v>
       </c>
-      <c r="V77" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
         <v>8111</v>
       </c>
@@ -5724,11 +5568,8 @@
       <c r="U78" s="8">
         <v>2</v>
       </c>
-      <c r="V78" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
         <v>8112</v>
       </c>
@@ -5793,11 +5634,8 @@
       <c r="U79" s="8">
         <v>2</v>
       </c>
-      <c r="V79" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="19">
         <v>8113</v>
       </c>
@@ -5862,9 +5700,6 @@
       <c r="U80" s="8">
         <v>2</v>
       </c>
-      <c r="V80" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
@@ -5931,9 +5766,6 @@
       <c r="U81" s="8">
         <v>2</v>
       </c>
-      <c r="V81" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
@@ -5999,9 +5831,6 @@
       </c>
       <c r="U82" s="8">
         <v>2</v>
-      </c>
-      <c r="V82" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
@@ -6091,9 +5920,6 @@
       <c r="U84" s="22">
         <v>2</v>
       </c>
-      <c r="V84" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="32">
@@ -6702,9 +6528,6 @@
       </c>
       <c r="U94" s="8">
         <v>2</v>
-      </c>
-      <c r="V94" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
@@ -6796,7 +6619,7 @@
       <c r="T96" s="4"/>
       <c r="U96" s="8"/>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="19">
         <v>10101</v>
       </c>
@@ -6861,11 +6684,8 @@
       <c r="U97" s="8">
         <v>2</v>
       </c>
-      <c r="V97" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="7"/>
       <c r="C98" s="4"/>
@@ -6888,7 +6708,7 @@
       <c r="T98" s="4"/>
       <c r="U98" s="8"/>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="19">
         <v>11101</v>
       </c>
@@ -6953,11 +6773,8 @@
       <c r="U99" s="8">
         <v>2</v>
       </c>
-      <c r="V99" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="19">
         <v>11102</v>
       </c>
@@ -7022,11 +6839,8 @@
       <c r="U100" s="8">
         <v>2</v>
       </c>
-      <c r="V100" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="19">
         <v>11103</v>
       </c>
@@ -7091,11 +6905,8 @@
       <c r="U101" s="8">
         <v>2</v>
       </c>
-      <c r="V101" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="19">
         <v>11104</v>
       </c>
@@ -7160,11 +6971,8 @@
       <c r="U102" s="8">
         <v>2</v>
       </c>
-      <c r="V102" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="19">
         <v>11105</v>
       </c>
@@ -7229,11 +7037,8 @@
       <c r="U103" s="8">
         <v>2</v>
       </c>
-      <c r="V103" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="19">
         <v>11106</v>
       </c>
@@ -7298,11 +7103,8 @@
       <c r="U104" s="8">
         <v>2</v>
       </c>
-      <c r="V104" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="19">
         <v>11107</v>
       </c>
@@ -7367,11 +7169,8 @@
       <c r="U105" s="8">
         <v>2</v>
       </c>
-      <c r="V105" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="19">
         <v>11108</v>
       </c>
@@ -7436,12 +7235,9 @@
       <c r="U106" s="8">
         <v>2</v>
       </c>
-      <c r="V106" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A107" s="33">
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A107" s="19">
         <v>11109</v>
       </c>
       <c r="B107" s="14" t="s">
@@ -7505,11 +7301,8 @@
       <c r="U107" s="8">
         <v>2</v>
       </c>
-      <c r="V107" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="7"/>
       <c r="C108" s="4"/>
@@ -7532,8 +7325,8 @@
       <c r="T108" s="4"/>
       <c r="U108" s="8"/>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A109" s="33">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A109" s="19">
         <v>12101</v>
       </c>
       <c r="B109" s="14" t="s">
@@ -7597,12 +7390,9 @@
       <c r="U109" s="8">
         <v>2</v>
       </c>
-      <c r="V109" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A110" s="33">
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A110" s="19">
         <v>12102</v>
       </c>
       <c r="B110" s="14" t="s">
@@ -7666,12 +7456,9 @@
       <c r="U110" s="8">
         <v>2</v>
       </c>
-      <c r="V110" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A111" s="33">
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A111" s="19">
         <v>12103</v>
       </c>
       <c r="B111" s="14" t="s">
@@ -7735,12 +7522,9 @@
       <c r="U111" s="8">
         <v>2</v>
       </c>
-      <c r="V111" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A112" s="33">
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A112" s="19">
         <v>12104</v>
       </c>
       <c r="B112" s="14" t="s">
@@ -7804,12 +7588,9 @@
       <c r="U112" s="8">
         <v>2</v>
       </c>
-      <c r="V112" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A113" s="33">
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A113" s="19">
         <v>12105</v>
       </c>
       <c r="B113" s="14" t="s">
@@ -7873,12 +7654,9 @@
       <c r="U113" s="8">
         <v>2</v>
       </c>
-      <c r="V113" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A114" s="33">
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A114" s="19">
         <v>12106</v>
       </c>
       <c r="B114" s="14" t="s">
@@ -7942,12 +7720,9 @@
       <c r="U114" s="8">
         <v>2</v>
       </c>
-      <c r="V114" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A115" s="41">
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A115" s="19">
         <v>12107</v>
       </c>
       <c r="B115" s="14" t="s">
@@ -8011,12 +7786,9 @@
       <c r="U115" s="8">
         <v>2</v>
       </c>
-      <c r="V115" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A116" s="41">
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A116" s="19">
         <v>12108</v>
       </c>
       <c r="B116" s="14" t="s">
@@ -8080,12 +7852,9 @@
       <c r="U116" s="8">
         <v>2</v>
       </c>
-      <c r="V116" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A117" s="41">
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A117" s="19">
         <v>12109</v>
       </c>
       <c r="B117" s="14" t="s">
@@ -8149,11 +7918,8 @@
       <c r="U117" s="8">
         <v>2</v>
       </c>
-      <c r="V117" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="14"/>
       <c r="C120" s="4"/>
@@ -8176,7 +7942,7 @@
       <c r="T120" s="4"/>
       <c r="U120" s="8"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="7"/>
       <c r="C121" s="4"/>
@@ -8199,7 +7965,7 @@
       <c r="T121" s="4"/>
       <c r="U121" s="8"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="7"/>
       <c r="C122" s="4"/>
@@ -8222,7 +7988,7 @@
       <c r="T122" s="4"/>
       <c r="U122" s="8"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="7"/>
       <c r="C123" s="4"/>
@@ -8245,7 +8011,7 @@
       <c r="T123" s="4"/>
       <c r="U123" s="8"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
       <c r="B124" s="7"/>
       <c r="C124" s="4"/>
@@ -8268,7 +8034,7 @@
       <c r="T124" s="4"/>
       <c r="U124" s="8"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
       <c r="B125" s="7"/>
       <c r="C125" s="4"/>
@@ -8291,7 +8057,7 @@
       <c r="T125" s="4"/>
       <c r="U125" s="8"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="7"/>
       <c r="C126" s="4"/>
@@ -8314,7 +8080,7 @@
       <c r="T126" s="4"/>
       <c r="U126" s="8"/>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="7"/>
       <c r="C127" s="4"/>
@@ -8337,7 +8103,7 @@
       <c r="T127" s="4"/>
       <c r="U127" s="8"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="7"/>
       <c r="C128" s="4"/>
@@ -9134,7 +8900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2F00BA-95B2-42FB-9A66-5FDDA7DC61DE}">
-  <dimension ref="A1:V153"/>
+  <dimension ref="A1:U153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
@@ -9160,40 +8926,40 @@
     <col min="21" max="21" width="8.88671875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="37" t="s">
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="40"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="37" t="s">
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="39"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="39"/>
-    </row>
-    <row r="2" spans="1:22" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="38"/>
+    </row>
+    <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -9258,7 +9024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>12101</v>
       </c>
@@ -9323,11 +9089,8 @@
       <c r="U3" s="8">
         <v>2</v>
       </c>
-      <c r="V3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>12102</v>
       </c>
@@ -9392,11 +9155,8 @@
       <c r="U4" s="8">
         <v>2</v>
       </c>
-      <c r="V4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>12103</v>
       </c>
@@ -9461,11 +9221,8 @@
       <c r="U5" s="8">
         <v>2</v>
       </c>
-      <c r="V5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>12104</v>
       </c>
@@ -9530,11 +9287,8 @@
       <c r="U6" s="8">
         <v>2</v>
       </c>
-      <c r="V6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>12105</v>
       </c>
@@ -9599,11 +9353,8 @@
       <c r="U7" s="8">
         <v>2</v>
       </c>
-      <c r="V7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>12106</v>
       </c>
@@ -9668,11 +9419,8 @@
       <c r="U8" s="8">
         <v>2</v>
       </c>
-      <c r="V8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>12107</v>
       </c>
@@ -9737,11 +9485,8 @@
       <c r="U9" s="8">
         <v>2</v>
       </c>
-      <c r="V9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>12108</v>
       </c>
@@ -9806,11 +9551,8 @@
       <c r="U10" s="8">
         <v>2</v>
       </c>
-      <c r="V10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>12109</v>
       </c>
@@ -9875,11 +9617,8 @@
       <c r="U11" s="8">
         <v>2</v>
       </c>
-      <c r="V11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="14"/>
       <c r="C12" s="4"/>
@@ -9902,7 +9641,7 @@
       <c r="T12" s="4"/>
       <c r="U12" s="8"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="14"/>
       <c r="C13" s="4"/>
@@ -9925,7 +9664,7 @@
       <c r="T13" s="4"/>
       <c r="U13" s="8"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="14"/>
       <c r="C14" s="4"/>
@@ -9948,7 +9687,7 @@
       <c r="T14" s="4"/>
       <c r="U14" s="8"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="7"/>
       <c r="C15" s="4"/>
@@ -9971,7 +9710,7 @@
       <c r="T15" s="4"/>
       <c r="U15" s="8"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>

--- a/Droplet Evaporation.xlsx
+++ b/Droplet Evaporation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Códigos\DG_Droplet\DropletEvaporation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LVAROG~1\AppData\Roaming\MobaXterm\slash\RemoteFiles\264216_2_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905757AE-40AB-42C4-A8DB-1A0F923B6E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9D071D-D8F4-4524-A2FE-9EDF397000C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="87">
   <si>
     <t>MESH AND TIME CONFIGURATION</t>
   </si>
@@ -163,6 +163,141 @@
   </si>
   <si>
     <t>0,7083;0,00;0,0972;0,1947</t>
+  </si>
+  <si>
+    <t>output-7-0</t>
+  </si>
+  <si>
+    <t>output-7-1</t>
+  </si>
+  <si>
+    <t>output-7-2</t>
+  </si>
+  <si>
+    <t>output-7-3</t>
+  </si>
+  <si>
+    <t>output-7-4</t>
+  </si>
+  <si>
+    <t>output-7-5</t>
+  </si>
+  <si>
+    <t>output-7-6</t>
+  </si>
+  <si>
+    <t>output-7-7</t>
+  </si>
+  <si>
+    <t>output-7-8</t>
+  </si>
+  <si>
+    <t>output-7-9</t>
+  </si>
+  <si>
+    <t>output-7-10</t>
+  </si>
+  <si>
+    <t>output-7-11</t>
+  </si>
+  <si>
+    <t>output-33-0</t>
+  </si>
+  <si>
+    <t>output-91-0</t>
+  </si>
+  <si>
+    <t>output-81-0</t>
+  </si>
+  <si>
+    <t>output-81-1</t>
+  </si>
+  <si>
+    <t>output-81-2</t>
+  </si>
+  <si>
+    <t>output-101-0</t>
+  </si>
+  <si>
+    <t>output-111-0</t>
+  </si>
+  <si>
+    <t>output-111-1</t>
+  </si>
+  <si>
+    <t>output-111-2</t>
+  </si>
+  <si>
+    <t>output-111-3</t>
+  </si>
+  <si>
+    <t>output-111-4</t>
+  </si>
+  <si>
+    <t>output-111-5</t>
+  </si>
+  <si>
+    <t>output-111-6</t>
+  </si>
+  <si>
+    <t>output-111-7</t>
+  </si>
+  <si>
+    <t>output-111-8</t>
+  </si>
+  <si>
+    <t>output-121-0</t>
+  </si>
+  <si>
+    <t>output-121-1</t>
+  </si>
+  <si>
+    <t>output-121-2</t>
+  </si>
+  <si>
+    <t>output-121-3</t>
+  </si>
+  <si>
+    <t>output-121-4</t>
+  </si>
+  <si>
+    <t>output-121-5</t>
+  </si>
+  <si>
+    <t>output-121-6</t>
+  </si>
+  <si>
+    <t>output-121-7</t>
+  </si>
+  <si>
+    <t>output-121-8</t>
+  </si>
+  <si>
+    <t>output-131-0</t>
+  </si>
+  <si>
+    <t>output-131-1</t>
+  </si>
+  <si>
+    <t>output-131-2</t>
+  </si>
+  <si>
+    <t>output-131-3</t>
+  </si>
+  <si>
+    <t>output-131-4</t>
+  </si>
+  <si>
+    <t>output-131-5</t>
+  </si>
+  <si>
+    <t>output-131-6</t>
+  </si>
+  <si>
+    <t>output-131-7</t>
+  </si>
+  <si>
+    <t>output-131-8</t>
   </si>
 </sst>
 </file>
@@ -467,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -576,6 +711,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4690,7 +4828,7 @@
         <v>3.7199999999999997E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" s="29">
         <v>2307</v>
       </c>
@@ -4755,7 +4893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" s="29">
         <v>2308</v>
       </c>
@@ -4820,7 +4958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="7"/>
       <c r="C67" s="4"/>
@@ -4843,7 +4981,7 @@
       <c r="T67" s="4"/>
       <c r="U67" s="8"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="18">
         <v>8101</v>
       </c>
@@ -4908,8 +5046,11 @@
       <c r="U68" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V68" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="18">
         <v>8102</v>
       </c>
@@ -4974,8 +5115,11 @@
       <c r="U69" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="18">
         <v>8103</v>
       </c>
@@ -5040,8 +5184,11 @@
       <c r="U70" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V70" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="19">
         <v>8104</v>
       </c>
@@ -5106,8 +5253,11 @@
       <c r="U71" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V71" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="19">
         <v>8105</v>
       </c>
@@ -5172,8 +5322,11 @@
       <c r="U72" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V72" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="19">
         <v>8106</v>
       </c>
@@ -5238,8 +5391,11 @@
       <c r="U73" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V73" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="19">
         <v>8107</v>
       </c>
@@ -5304,8 +5460,11 @@
       <c r="U74" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>8108</v>
       </c>
@@ -5370,8 +5529,11 @@
       <c r="U75" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V75" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
         <v>8109</v>
       </c>
@@ -5436,8 +5598,11 @@
       <c r="U76" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V76" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
         <v>8110</v>
       </c>
@@ -5502,8 +5667,11 @@
       <c r="U77" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
         <v>8111</v>
       </c>
@@ -5568,8 +5736,11 @@
       <c r="U78" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V78" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
         <v>8112</v>
       </c>
@@ -5634,8 +5805,11 @@
       <c r="U79" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="19">
         <v>8113</v>
       </c>
@@ -5700,6 +5874,9 @@
       <c r="U80" s="8">
         <v>2</v>
       </c>
+      <c r="V80" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
@@ -5766,6 +5943,9 @@
       <c r="U81" s="8">
         <v>2</v>
       </c>
+      <c r="V81" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
@@ -5831,6 +6011,9 @@
       </c>
       <c r="U82" s="8">
         <v>2</v>
+      </c>
+      <c r="V82" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
@@ -5920,6 +6103,9 @@
       <c r="U84" s="22">
         <v>2</v>
       </c>
+      <c r="V84" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="32">
@@ -6528,6 +6714,9 @@
       </c>
       <c r="U94" s="8">
         <v>2</v>
+      </c>
+      <c r="V94" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
@@ -6619,7 +6808,7 @@
       <c r="T96" s="4"/>
       <c r="U96" s="8"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" s="19">
         <v>10101</v>
       </c>
@@ -6684,8 +6873,11 @@
       <c r="U97" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V97" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="7"/>
       <c r="C98" s="4"/>
@@ -6708,7 +6900,7 @@
       <c r="T98" s="4"/>
       <c r="U98" s="8"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="19">
         <v>11101</v>
       </c>
@@ -6725,7 +6917,7 @@
         <v>26</v>
       </c>
       <c r="F99" s="7">
-        <f t="shared" ref="F99:F117" si="7">(0.0001451)/2</f>
+        <f t="shared" ref="F99:F146" si="7">(0.0001451)/2</f>
         <v>7.2550000000000002E-5</v>
       </c>
       <c r="G99" s="4">
@@ -6773,8 +6965,11 @@
       <c r="U99" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V99" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="19">
         <v>11102</v>
       </c>
@@ -6839,8 +7034,11 @@
       <c r="U100" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V100" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" s="19">
         <v>11103</v>
       </c>
@@ -6905,8 +7103,11 @@
       <c r="U101" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V101" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" s="19">
         <v>11104</v>
       </c>
@@ -6971,8 +7172,11 @@
       <c r="U102" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V102" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="19">
         <v>11105</v>
       </c>
@@ -7037,8 +7241,11 @@
       <c r="U103" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V103" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="19">
         <v>11106</v>
       </c>
@@ -7103,8 +7310,11 @@
       <c r="U104" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V104" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" s="19">
         <v>11107</v>
       </c>
@@ -7169,8 +7379,11 @@
       <c r="U105" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V105" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A106" s="19">
         <v>11108</v>
       </c>
@@ -7235,8 +7448,11 @@
       <c r="U106" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V106" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" s="19">
         <v>11109</v>
       </c>
@@ -7301,8 +7517,11 @@
       <c r="U107" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V107" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="7"/>
       <c r="C108" s="4"/>
@@ -7325,7 +7544,7 @@
       <c r="T108" s="4"/>
       <c r="U108" s="8"/>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A109" s="19">
         <v>12101</v>
       </c>
@@ -7390,8 +7609,11 @@
       <c r="U109" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V109" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" s="19">
         <v>12102</v>
       </c>
@@ -7456,8 +7678,11 @@
       <c r="U110" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V110" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" s="19">
         <v>12103</v>
       </c>
@@ -7522,8 +7747,11 @@
       <c r="U111" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V111" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A112" s="19">
         <v>12104</v>
       </c>
@@ -7588,8 +7816,11 @@
       <c r="U112" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V112" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A113" s="19">
         <v>12105</v>
       </c>
@@ -7654,8 +7885,11 @@
       <c r="U113" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V113" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A114" s="19">
         <v>12106</v>
       </c>
@@ -7720,8 +7954,11 @@
       <c r="U114" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V114" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A115" s="19">
         <v>12107</v>
       </c>
@@ -7786,8 +8023,11 @@
       <c r="U115" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V115" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A116" s="19">
         <v>12108</v>
       </c>
@@ -7852,8 +8092,11 @@
       <c r="U116" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V116" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A117" s="19">
         <v>12109</v>
       </c>
@@ -7918,192 +8161,632 @@
       <c r="U117" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="14"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="15"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
-      <c r="J120" s="8"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="4"/>
-      <c r="M120" s="4"/>
-      <c r="N120" s="4"/>
-      <c r="O120" s="4"/>
-      <c r="P120" s="4"/>
-      <c r="Q120" s="30"/>
-      <c r="R120" s="7"/>
-      <c r="S120" s="4"/>
-      <c r="T120" s="4"/>
-      <c r="U120" s="8"/>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="4"/>
-      <c r="M121" s="4"/>
-      <c r="N121" s="4"/>
-      <c r="O121" s="4"/>
-      <c r="P121" s="4"/>
-      <c r="Q121" s="8"/>
-      <c r="R121" s="7"/>
-      <c r="S121" s="4"/>
-      <c r="T121" s="4"/>
-      <c r="U121" s="8"/>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A122" s="5"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="4"/>
-      <c r="M122" s="4"/>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-      <c r="P122" s="4"/>
-      <c r="Q122" s="8"/>
-      <c r="R122" s="7"/>
-      <c r="S122" s="4"/>
-      <c r="T122" s="4"/>
-      <c r="U122" s="8"/>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="4"/>
-      <c r="M123" s="4"/>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
-      <c r="P123" s="4"/>
-      <c r="Q123" s="8"/>
-      <c r="R123" s="7"/>
-      <c r="S123" s="4"/>
-      <c r="T123" s="4"/>
-      <c r="U123" s="8"/>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="4"/>
-      <c r="M124" s="4"/>
-      <c r="N124" s="4"/>
-      <c r="O124" s="4"/>
-      <c r="P124" s="4"/>
-      <c r="Q124" s="8"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="4"/>
-      <c r="T124" s="4"/>
-      <c r="U124" s="8"/>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A125" s="5"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-      <c r="J125" s="8"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="4"/>
-      <c r="M125" s="4"/>
-      <c r="N125" s="4"/>
-      <c r="O125" s="4"/>
-      <c r="P125" s="4"/>
-      <c r="Q125" s="8"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="4"/>
-      <c r="T125" s="4"/>
-      <c r="U125" s="8"/>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A126" s="5"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
-      <c r="J126" s="8"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="4"/>
-      <c r="M126" s="4"/>
-      <c r="N126" s="4"/>
-      <c r="O126" s="4"/>
-      <c r="P126" s="4"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="4"/>
-      <c r="T126" s="4"/>
-      <c r="U126" s="8"/>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="4"/>
-      <c r="M127" s="4"/>
-      <c r="N127" s="4"/>
-      <c r="O127" s="4"/>
-      <c r="P127" s="4"/>
-      <c r="Q127" s="8"/>
-      <c r="R127" s="7"/>
-      <c r="S127" s="4"/>
-      <c r="T127" s="4"/>
-      <c r="U127" s="8"/>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V117" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A119" s="19">
+        <v>13101</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F119" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G119" s="4">
+        <v>150</v>
+      </c>
+      <c r="H119" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I119" s="4">
+        <v>303</v>
+      </c>
+      <c r="J119" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K119" s="7">
+        <v>5</v>
+      </c>
+      <c r="L119" s="4">
+        <v>4</v>
+      </c>
+      <c r="M119" s="4">
+        <v>2</v>
+      </c>
+      <c r="N119" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O119" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P119" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q119" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R119" s="7">
+        <v>0</v>
+      </c>
+      <c r="S119" s="4">
+        <v>1</v>
+      </c>
+      <c r="T119" s="4">
+        <v>500</v>
+      </c>
+      <c r="U119" s="8">
+        <v>2</v>
+      </c>
+      <c r="V119" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A120" s="19">
+        <v>13102</v>
+      </c>
+      <c r="B120" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F120" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G120" s="4">
+        <v>150</v>
+      </c>
+      <c r="H120" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I120" s="4">
+        <v>303</v>
+      </c>
+      <c r="J120" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K120" s="7">
+        <v>10</v>
+      </c>
+      <c r="L120" s="4">
+        <v>2</v>
+      </c>
+      <c r="M120" s="4">
+        <v>2</v>
+      </c>
+      <c r="N120" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O120" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P120" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R120" s="7">
+        <v>0</v>
+      </c>
+      <c r="S120" s="4">
+        <v>1</v>
+      </c>
+      <c r="T120" s="4">
+        <v>500</v>
+      </c>
+      <c r="U120" s="8">
+        <v>2</v>
+      </c>
+      <c r="V120" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A121" s="19">
+        <v>13103</v>
+      </c>
+      <c r="B121" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F121" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G121" s="4">
+        <v>150</v>
+      </c>
+      <c r="H121" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I121" s="4">
+        <v>303</v>
+      </c>
+      <c r="J121" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K121" s="7">
+        <v>20</v>
+      </c>
+      <c r="L121" s="4">
+        <v>1</v>
+      </c>
+      <c r="M121" s="4">
+        <v>2</v>
+      </c>
+      <c r="N121" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O121" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P121" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R121" s="7">
+        <v>0</v>
+      </c>
+      <c r="S121" s="4">
+        <v>1</v>
+      </c>
+      <c r="T121" s="4">
+        <v>500</v>
+      </c>
+      <c r="U121" s="8">
+        <v>2</v>
+      </c>
+      <c r="V121" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A122" s="19">
+        <v>13104</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F122" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G122" s="4">
+        <v>150</v>
+      </c>
+      <c r="H122" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I122" s="4">
+        <v>303</v>
+      </c>
+      <c r="J122" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K122" s="7">
+        <v>5</v>
+      </c>
+      <c r="L122" s="4">
+        <v>4</v>
+      </c>
+      <c r="M122" s="4">
+        <v>3</v>
+      </c>
+      <c r="N122" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O122" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P122" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q122" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R122" s="7">
+        <v>0</v>
+      </c>
+      <c r="S122" s="4">
+        <v>1</v>
+      </c>
+      <c r="T122" s="4">
+        <v>500</v>
+      </c>
+      <c r="U122" s="8">
+        <v>2</v>
+      </c>
+      <c r="V122" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A123" s="19">
+        <v>13105</v>
+      </c>
+      <c r="B123" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F123" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G123" s="4">
+        <v>150</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I123" s="4">
+        <v>303</v>
+      </c>
+      <c r="J123" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K123" s="7">
+        <v>10</v>
+      </c>
+      <c r="L123" s="4">
+        <v>2</v>
+      </c>
+      <c r="M123" s="4">
+        <v>3</v>
+      </c>
+      <c r="N123" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O123" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P123" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q123" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R123" s="7">
+        <v>0</v>
+      </c>
+      <c r="S123" s="4">
+        <v>1</v>
+      </c>
+      <c r="T123" s="4">
+        <v>500</v>
+      </c>
+      <c r="U123" s="8">
+        <v>2</v>
+      </c>
+      <c r="V123" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A124" s="19">
+        <v>13106</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G124" s="4">
+        <v>150</v>
+      </c>
+      <c r="H124" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I124" s="4">
+        <v>303</v>
+      </c>
+      <c r="J124" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K124" s="7">
+        <v>20</v>
+      </c>
+      <c r="L124" s="4">
+        <v>1</v>
+      </c>
+      <c r="M124" s="4">
+        <v>3</v>
+      </c>
+      <c r="N124" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O124" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P124" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R124" s="7">
+        <v>0</v>
+      </c>
+      <c r="S124" s="4">
+        <v>1</v>
+      </c>
+      <c r="T124" s="4">
+        <v>500</v>
+      </c>
+      <c r="U124" s="8">
+        <v>2</v>
+      </c>
+      <c r="V124" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A125" s="19">
+        <v>13107</v>
+      </c>
+      <c r="B125" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F125" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G125" s="4">
+        <v>150</v>
+      </c>
+      <c r="H125" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I125" s="4">
+        <v>303</v>
+      </c>
+      <c r="J125" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K125" s="7">
+        <v>5</v>
+      </c>
+      <c r="L125" s="4">
+        <v>4</v>
+      </c>
+      <c r="M125" s="4">
+        <v>4</v>
+      </c>
+      <c r="N125" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O125" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P125" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q125" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R125" s="7">
+        <v>0</v>
+      </c>
+      <c r="S125" s="4">
+        <v>1</v>
+      </c>
+      <c r="T125" s="4">
+        <v>500</v>
+      </c>
+      <c r="U125" s="8">
+        <v>2</v>
+      </c>
+      <c r="V125" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A126" s="19">
+        <v>13108</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F126" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G126" s="4">
+        <v>150</v>
+      </c>
+      <c r="H126" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I126" s="4">
+        <v>303</v>
+      </c>
+      <c r="J126" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K126" s="7">
+        <v>10</v>
+      </c>
+      <c r="L126" s="4">
+        <v>2</v>
+      </c>
+      <c r="M126" s="4">
+        <v>4</v>
+      </c>
+      <c r="N126" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O126" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P126" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q126" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R126" s="7">
+        <v>0</v>
+      </c>
+      <c r="S126" s="4">
+        <v>1</v>
+      </c>
+      <c r="T126" s="4">
+        <v>500</v>
+      </c>
+      <c r="U126" s="8">
+        <v>2</v>
+      </c>
+      <c r="V126" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A127" s="19">
+        <v>13109</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F127" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G127" s="4">
+        <v>150</v>
+      </c>
+      <c r="H127" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I127" s="4">
+        <v>303</v>
+      </c>
+      <c r="J127" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K127" s="7">
+        <v>20</v>
+      </c>
+      <c r="L127" s="4">
+        <v>1</v>
+      </c>
+      <c r="M127" s="4">
+        <v>4</v>
+      </c>
+      <c r="N127" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O127" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P127" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q127" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R127" s="7">
+        <v>0</v>
+      </c>
+      <c r="S127" s="4">
+        <v>1</v>
+      </c>
+      <c r="T127" s="4">
+        <v>500</v>
+      </c>
+      <c r="U127" s="8">
+        <v>2</v>
+      </c>
+      <c r="V127" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="7"/>
       <c r="C128" s="4"/>
@@ -8126,421 +8809,1249 @@
       <c r="T128" s="4"/>
       <c r="U128" s="8"/>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A129" s="5"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="8"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="4"/>
-      <c r="M129" s="4"/>
-      <c r="N129" s="4"/>
-      <c r="O129" s="4"/>
-      <c r="P129" s="4"/>
-      <c r="Q129" s="8"/>
-      <c r="R129" s="7"/>
-      <c r="S129" s="4"/>
-      <c r="T129" s="4"/>
-      <c r="U129" s="8"/>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A130" s="5"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="4"/>
-      <c r="M130" s="4"/>
-      <c r="N130" s="4"/>
-      <c r="O130" s="4"/>
-      <c r="P130" s="4"/>
-      <c r="Q130" s="8"/>
-      <c r="R130" s="7"/>
-      <c r="S130" s="4"/>
-      <c r="T130" s="4"/>
-      <c r="U130" s="8"/>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="4"/>
-      <c r="M131" s="4"/>
-      <c r="N131" s="4"/>
-      <c r="O131" s="4"/>
-      <c r="P131" s="4"/>
-      <c r="Q131" s="8"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="4"/>
-      <c r="T131" s="4"/>
-      <c r="U131" s="8"/>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="8"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="4"/>
-      <c r="M132" s="4"/>
-      <c r="N132" s="4"/>
-      <c r="O132" s="4"/>
-      <c r="P132" s="4"/>
-      <c r="Q132" s="8"/>
-      <c r="R132" s="7"/>
-      <c r="S132" s="4"/>
-      <c r="T132" s="4"/>
-      <c r="U132" s="8"/>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A133" s="5"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="8"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="4"/>
-      <c r="M133" s="4"/>
-      <c r="N133" s="4"/>
-      <c r="O133" s="4"/>
-      <c r="P133" s="4"/>
-      <c r="Q133" s="8"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="4"/>
-      <c r="T133" s="4"/>
-      <c r="U133" s="8"/>
-    </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A134" s="5"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="8"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="4"/>
-      <c r="M134" s="4"/>
-      <c r="N134" s="4"/>
-      <c r="O134" s="4"/>
-      <c r="P134" s="4"/>
-      <c r="Q134" s="8"/>
-      <c r="R134" s="7"/>
-      <c r="S134" s="4"/>
-      <c r="T134" s="4"/>
-      <c r="U134" s="8"/>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="4"/>
-      <c r="M135" s="4"/>
-      <c r="N135" s="4"/>
-      <c r="O135" s="4"/>
-      <c r="P135" s="4"/>
-      <c r="Q135" s="8"/>
-      <c r="R135" s="7"/>
-      <c r="S135" s="4"/>
-      <c r="T135" s="4"/>
-      <c r="U135" s="8"/>
-    </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="4"/>
-      <c r="M136" s="4"/>
-      <c r="N136" s="4"/>
-      <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="4"/>
-      <c r="T136" s="4"/>
-      <c r="U136" s="8"/>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A137" s="5"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="4"/>
-      <c r="M137" s="4"/>
-      <c r="N137" s="4"/>
-      <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="8"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="4"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="8"/>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A138" s="5"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="4"/>
-      <c r="M138" s="4"/>
-      <c r="N138" s="4"/>
-      <c r="O138" s="4"/>
-      <c r="P138" s="4"/>
-      <c r="Q138" s="8"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="4"/>
-      <c r="T138" s="4"/>
-      <c r="U138" s="8"/>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="4"/>
-      <c r="M139" s="4"/>
-      <c r="N139" s="4"/>
-      <c r="O139" s="4"/>
-      <c r="P139" s="4"/>
-      <c r="Q139" s="8"/>
-      <c r="R139" s="7"/>
-      <c r="S139" s="4"/>
-      <c r="T139" s="4"/>
-      <c r="U139" s="8"/>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="8"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="4"/>
-      <c r="M140" s="4"/>
-      <c r="N140" s="4"/>
-      <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
-      <c r="Q140" s="8"/>
-      <c r="R140" s="7"/>
-      <c r="S140" s="4"/>
-      <c r="T140" s="4"/>
-      <c r="U140" s="8"/>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A141" s="5"/>
-      <c r="B141" s="7"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="7"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="8"/>
-      <c r="K141" s="7"/>
-      <c r="L141" s="4"/>
-      <c r="M141" s="4"/>
-      <c r="N141" s="4"/>
-      <c r="O141" s="4"/>
-      <c r="P141" s="4"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="4"/>
-      <c r="T141" s="4"/>
-      <c r="U141" s="8"/>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A142" s="5"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="8"/>
-      <c r="K142" s="7"/>
-      <c r="L142" s="4"/>
-      <c r="M142" s="4"/>
-      <c r="N142" s="4"/>
-      <c r="O142" s="4"/>
-      <c r="P142" s="4"/>
-      <c r="Q142" s="8"/>
-      <c r="R142" s="7"/>
-      <c r="S142" s="4"/>
-      <c r="T142" s="4"/>
-      <c r="U142" s="8"/>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
-      <c r="B143" s="7"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="7"/>
-      <c r="L143" s="4"/>
-      <c r="M143" s="4"/>
-      <c r="N143" s="4"/>
-      <c r="O143" s="4"/>
-      <c r="P143" s="4"/>
-      <c r="Q143" s="8"/>
-      <c r="R143" s="7"/>
-      <c r="S143" s="4"/>
-      <c r="T143" s="4"/>
-      <c r="U143" s="8"/>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="8"/>
-      <c r="K144" s="7"/>
-      <c r="L144" s="4"/>
-      <c r="M144" s="4"/>
-      <c r="N144" s="4"/>
-      <c r="O144" s="4"/>
-      <c r="P144" s="4"/>
-      <c r="Q144" s="8"/>
-      <c r="R144" s="7"/>
-      <c r="S144" s="4"/>
-      <c r="T144" s="4"/>
-      <c r="U144" s="8"/>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A145" s="5"/>
-      <c r="B145" s="7"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="7"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="8"/>
-      <c r="K145" s="7"/>
-      <c r="L145" s="4"/>
-      <c r="M145" s="4"/>
-      <c r="N145" s="4"/>
-      <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
-      <c r="Q145" s="8"/>
-      <c r="R145" s="7"/>
-      <c r="S145" s="4"/>
-      <c r="T145" s="4"/>
-      <c r="U145" s="8"/>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A146" s="5"/>
-      <c r="B146" s="7"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="8"/>
-      <c r="K146" s="7"/>
-      <c r="L146" s="4"/>
-      <c r="M146" s="4"/>
-      <c r="N146" s="4"/>
-      <c r="O146" s="4"/>
-      <c r="P146" s="4"/>
-      <c r="Q146" s="8"/>
-      <c r="R146" s="7"/>
-      <c r="S146" s="4"/>
-      <c r="T146" s="4"/>
-      <c r="U146" s="8"/>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A129" s="40">
+        <v>14101</v>
+      </c>
+      <c r="B129" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F129" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G129" s="4">
+        <v>150</v>
+      </c>
+      <c r="H129" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I129" s="4">
+        <v>303</v>
+      </c>
+      <c r="J129" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K129" s="7">
+        <v>5</v>
+      </c>
+      <c r="L129" s="4">
+        <v>4</v>
+      </c>
+      <c r="M129" s="4">
+        <v>2</v>
+      </c>
+      <c r="N129" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O129" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P129" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q129" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R129" s="7">
+        <v>0</v>
+      </c>
+      <c r="S129" s="4">
+        <v>1</v>
+      </c>
+      <c r="T129" s="4">
+        <v>500</v>
+      </c>
+      <c r="U129" s="8">
+        <v>2</v>
+      </c>
+      <c r="V129" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A130" s="40">
+        <v>14102</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F130" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G130" s="4">
+        <v>150</v>
+      </c>
+      <c r="H130" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I130" s="4">
+        <v>303</v>
+      </c>
+      <c r="J130" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K130" s="7">
+        <v>10</v>
+      </c>
+      <c r="L130" s="4">
+        <v>2</v>
+      </c>
+      <c r="M130" s="4">
+        <v>2</v>
+      </c>
+      <c r="N130" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O130" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P130" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q130" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R130" s="7">
+        <v>0</v>
+      </c>
+      <c r="S130" s="4">
+        <v>1</v>
+      </c>
+      <c r="T130" s="4">
+        <v>500</v>
+      </c>
+      <c r="U130" s="8">
+        <v>2</v>
+      </c>
+      <c r="V130" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A131" s="40">
+        <v>14103</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F131" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G131" s="4">
+        <v>150</v>
+      </c>
+      <c r="H131" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I131" s="4">
+        <v>303</v>
+      </c>
+      <c r="J131" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K131" s="7">
+        <v>20</v>
+      </c>
+      <c r="L131" s="4">
+        <v>1</v>
+      </c>
+      <c r="M131" s="4">
+        <v>2</v>
+      </c>
+      <c r="N131" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O131" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P131" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R131" s="7">
+        <v>0</v>
+      </c>
+      <c r="S131" s="4">
+        <v>1</v>
+      </c>
+      <c r="T131" s="4">
+        <v>500</v>
+      </c>
+      <c r="U131" s="8">
+        <v>2</v>
+      </c>
+      <c r="V131" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A132" s="40">
+        <v>14104</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F132" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G132" s="4">
+        <v>150</v>
+      </c>
+      <c r="H132" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I132" s="4">
+        <v>303</v>
+      </c>
+      <c r="J132" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K132" s="7">
+        <v>5</v>
+      </c>
+      <c r="L132" s="4">
+        <v>4</v>
+      </c>
+      <c r="M132" s="4">
+        <v>3</v>
+      </c>
+      <c r="N132" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O132" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P132" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q132" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R132" s="7">
+        <v>0</v>
+      </c>
+      <c r="S132" s="4">
+        <v>1</v>
+      </c>
+      <c r="T132" s="4">
+        <v>500</v>
+      </c>
+      <c r="U132" s="8">
+        <v>2</v>
+      </c>
+      <c r="V132" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A133" s="40">
+        <v>14105</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F133" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G133" s="4">
+        <v>150</v>
+      </c>
+      <c r="H133" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I133" s="4">
+        <v>303</v>
+      </c>
+      <c r="J133" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K133" s="7">
+        <v>10</v>
+      </c>
+      <c r="L133" s="4">
+        <v>2</v>
+      </c>
+      <c r="M133" s="4">
+        <v>3</v>
+      </c>
+      <c r="N133" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O133" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P133" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q133" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R133" s="7">
+        <v>0</v>
+      </c>
+      <c r="S133" s="4">
+        <v>1</v>
+      </c>
+      <c r="T133" s="4">
+        <v>500</v>
+      </c>
+      <c r="U133" s="8">
+        <v>2</v>
+      </c>
+      <c r="V133" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A134" s="40">
+        <v>14106</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F134" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G134" s="4">
+        <v>150</v>
+      </c>
+      <c r="H134" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I134" s="4">
+        <v>303</v>
+      </c>
+      <c r="J134" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K134" s="7">
+        <v>20</v>
+      </c>
+      <c r="L134" s="4">
+        <v>1</v>
+      </c>
+      <c r="M134" s="4">
+        <v>3</v>
+      </c>
+      <c r="N134" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O134" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P134" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q134" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R134" s="7">
+        <v>0</v>
+      </c>
+      <c r="S134" s="4">
+        <v>1</v>
+      </c>
+      <c r="T134" s="4">
+        <v>500</v>
+      </c>
+      <c r="U134" s="8">
+        <v>2</v>
+      </c>
+      <c r="V134" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A135" s="40">
+        <v>14107</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F135" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G135" s="4">
+        <v>150</v>
+      </c>
+      <c r="H135" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I135" s="4">
+        <v>303</v>
+      </c>
+      <c r="J135" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K135" s="7">
+        <v>5</v>
+      </c>
+      <c r="L135" s="4">
+        <v>4</v>
+      </c>
+      <c r="M135" s="4">
+        <v>4</v>
+      </c>
+      <c r="N135" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O135" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P135" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q135" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R135" s="7">
+        <v>0</v>
+      </c>
+      <c r="S135" s="4">
+        <v>1</v>
+      </c>
+      <c r="T135" s="4">
+        <v>500</v>
+      </c>
+      <c r="U135" s="8">
+        <v>2</v>
+      </c>
+      <c r="V135" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A136" s="40">
+        <v>14108</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F136" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G136" s="4">
+        <v>150</v>
+      </c>
+      <c r="H136" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I136" s="4">
+        <v>303</v>
+      </c>
+      <c r="J136" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K136" s="7">
+        <v>10</v>
+      </c>
+      <c r="L136" s="4">
+        <v>2</v>
+      </c>
+      <c r="M136" s="4">
+        <v>4</v>
+      </c>
+      <c r="N136" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O136" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P136" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q136" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R136" s="7">
+        <v>0</v>
+      </c>
+      <c r="S136" s="4">
+        <v>1</v>
+      </c>
+      <c r="T136" s="4">
+        <v>500</v>
+      </c>
+      <c r="U136" s="8">
+        <v>2</v>
+      </c>
+      <c r="V136" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A137" s="40">
+        <v>14109</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D137" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F137" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G137" s="4">
+        <v>150</v>
+      </c>
+      <c r="H137" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I137" s="4">
+        <v>303</v>
+      </c>
+      <c r="J137" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K137" s="7">
+        <v>20</v>
+      </c>
+      <c r="L137" s="4">
+        <v>1</v>
+      </c>
+      <c r="M137" s="4">
+        <v>4</v>
+      </c>
+      <c r="N137" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O137" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="P137" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R137" s="7">
+        <v>0</v>
+      </c>
+      <c r="S137" s="4">
+        <v>1</v>
+      </c>
+      <c r="T137" s="4">
+        <v>500</v>
+      </c>
+      <c r="U137" s="8">
+        <v>2</v>
+      </c>
+      <c r="V137" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A138" s="40">
+        <v>14110</v>
+      </c>
+      <c r="B138" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F138" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G138" s="4">
+        <v>150</v>
+      </c>
+      <c r="H138" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I138" s="4">
+        <v>303</v>
+      </c>
+      <c r="J138" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K138" s="7">
+        <v>5</v>
+      </c>
+      <c r="L138" s="4">
+        <v>4</v>
+      </c>
+      <c r="M138" s="4">
+        <v>2</v>
+      </c>
+      <c r="N138" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O138" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P138" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q138" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R138" s="7">
+        <v>0</v>
+      </c>
+      <c r="S138" s="4">
+        <v>1</v>
+      </c>
+      <c r="T138" s="4">
+        <v>500</v>
+      </c>
+      <c r="U138" s="8">
+        <v>2</v>
+      </c>
+      <c r="V138" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A139" s="40">
+        <v>14111</v>
+      </c>
+      <c r="B139" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D139" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F139" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G139" s="4">
+        <v>150</v>
+      </c>
+      <c r="H139" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I139" s="4">
+        <v>303</v>
+      </c>
+      <c r="J139" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K139" s="7">
+        <v>10</v>
+      </c>
+      <c r="L139" s="4">
+        <v>2</v>
+      </c>
+      <c r="M139" s="4">
+        <v>2</v>
+      </c>
+      <c r="N139" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O139" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P139" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q139" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R139" s="7">
+        <v>0</v>
+      </c>
+      <c r="S139" s="4">
+        <v>1</v>
+      </c>
+      <c r="T139" s="4">
+        <v>500</v>
+      </c>
+      <c r="U139" s="8">
+        <v>2</v>
+      </c>
+      <c r="V139" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A140" s="40">
+        <v>14112</v>
+      </c>
+      <c r="B140" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F140" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G140" s="4">
+        <v>150</v>
+      </c>
+      <c r="H140" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I140" s="4">
+        <v>303</v>
+      </c>
+      <c r="J140" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K140" s="7">
+        <v>20</v>
+      </c>
+      <c r="L140" s="4">
+        <v>1</v>
+      </c>
+      <c r="M140" s="4">
+        <v>2</v>
+      </c>
+      <c r="N140" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O140" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P140" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q140" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R140" s="7">
+        <v>0</v>
+      </c>
+      <c r="S140" s="4">
+        <v>1</v>
+      </c>
+      <c r="T140" s="4">
+        <v>500</v>
+      </c>
+      <c r="U140" s="8">
+        <v>2</v>
+      </c>
+      <c r="V140" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A141" s="40">
+        <v>14113</v>
+      </c>
+      <c r="B141" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F141" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G141" s="4">
+        <v>150</v>
+      </c>
+      <c r="H141" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I141" s="4">
+        <v>303</v>
+      </c>
+      <c r="J141" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K141" s="7">
+        <v>5</v>
+      </c>
+      <c r="L141" s="4">
+        <v>4</v>
+      </c>
+      <c r="M141" s="4">
+        <v>3</v>
+      </c>
+      <c r="N141" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O141" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P141" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q141" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R141" s="7">
+        <v>0</v>
+      </c>
+      <c r="S141" s="4">
+        <v>1</v>
+      </c>
+      <c r="T141" s="4">
+        <v>500</v>
+      </c>
+      <c r="U141" s="8">
+        <v>2</v>
+      </c>
+      <c r="V141" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A142" s="40">
+        <v>14114</v>
+      </c>
+      <c r="B142" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F142" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G142" s="4">
+        <v>150</v>
+      </c>
+      <c r="H142" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I142" s="4">
+        <v>303</v>
+      </c>
+      <c r="J142" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K142" s="7">
+        <v>10</v>
+      </c>
+      <c r="L142" s="4">
+        <v>2</v>
+      </c>
+      <c r="M142" s="4">
+        <v>3</v>
+      </c>
+      <c r="N142" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O142" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P142" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q142" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R142" s="7">
+        <v>0</v>
+      </c>
+      <c r="S142" s="4">
+        <v>1</v>
+      </c>
+      <c r="T142" s="4">
+        <v>500</v>
+      </c>
+      <c r="U142" s="8">
+        <v>2</v>
+      </c>
+      <c r="V142" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A143" s="40">
+        <v>14115</v>
+      </c>
+      <c r="B143" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F143" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G143" s="4">
+        <v>150</v>
+      </c>
+      <c r="H143" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I143" s="4">
+        <v>303</v>
+      </c>
+      <c r="J143" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K143" s="7">
+        <v>20</v>
+      </c>
+      <c r="L143" s="4">
+        <v>1</v>
+      </c>
+      <c r="M143" s="4">
+        <v>3</v>
+      </c>
+      <c r="N143" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O143" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P143" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q143" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R143" s="7">
+        <v>0</v>
+      </c>
+      <c r="S143" s="4">
+        <v>1</v>
+      </c>
+      <c r="T143" s="4">
+        <v>500</v>
+      </c>
+      <c r="U143" s="8">
+        <v>2</v>
+      </c>
+      <c r="V143" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A144" s="40">
+        <v>14116</v>
+      </c>
+      <c r="B144" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F144" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G144" s="4">
+        <v>150</v>
+      </c>
+      <c r="H144" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I144" s="4">
+        <v>303</v>
+      </c>
+      <c r="J144" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K144" s="7">
+        <v>5</v>
+      </c>
+      <c r="L144" s="4">
+        <v>4</v>
+      </c>
+      <c r="M144" s="4">
+        <v>4</v>
+      </c>
+      <c r="N144" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O144" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P144" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q144" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R144" s="7">
+        <v>0</v>
+      </c>
+      <c r="S144" s="4">
+        <v>1</v>
+      </c>
+      <c r="T144" s="4">
+        <v>500</v>
+      </c>
+      <c r="U144" s="8">
+        <v>2</v>
+      </c>
+      <c r="V144" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A145" s="40">
+        <v>14117</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F145" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G145" s="4">
+        <v>150</v>
+      </c>
+      <c r="H145" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I145" s="4">
+        <v>303</v>
+      </c>
+      <c r="J145" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K145" s="7">
+        <v>10</v>
+      </c>
+      <c r="L145" s="4">
+        <v>2</v>
+      </c>
+      <c r="M145" s="4">
+        <v>4</v>
+      </c>
+      <c r="N145" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O145" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P145" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q145" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R145" s="7">
+        <v>0</v>
+      </c>
+      <c r="S145" s="4">
+        <v>1</v>
+      </c>
+      <c r="T145" s="4">
+        <v>500</v>
+      </c>
+      <c r="U145" s="8">
+        <v>2</v>
+      </c>
+      <c r="V145" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A146" s="40">
+        <v>14118</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F146" s="7">
+        <f t="shared" si="7"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G146" s="4">
+        <v>150</v>
+      </c>
+      <c r="H146" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I146" s="4">
+        <v>303</v>
+      </c>
+      <c r="J146" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K146" s="7">
+        <v>20</v>
+      </c>
+      <c r="L146" s="4">
+        <v>1</v>
+      </c>
+      <c r="M146" s="4">
+        <v>4</v>
+      </c>
+      <c r="N146" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O146" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P146" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q146" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R146" s="7">
+        <v>0</v>
+      </c>
+      <c r="S146" s="4">
+        <v>1</v>
+      </c>
+      <c r="T146" s="4">
+        <v>500</v>
+      </c>
+      <c r="U146" s="8">
+        <v>2</v>
+      </c>
+      <c r="V146" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="7"/>
       <c r="C147" s="4"/>
@@ -8563,7 +10074,7 @@
       <c r="T147" s="4"/>
       <c r="U147" s="8"/>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="7"/>
       <c r="C148" s="4"/>
@@ -8586,7 +10097,7 @@
       <c r="T148" s="4"/>
       <c r="U148" s="8"/>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="7"/>
       <c r="C149" s="4"/>
@@ -8609,7 +10120,7 @@
       <c r="T149" s="4"/>
       <c r="U149" s="8"/>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="7"/>
       <c r="C150" s="4"/>
@@ -8632,7 +10143,7 @@
       <c r="T150" s="4"/>
       <c r="U150" s="8"/>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="7"/>
       <c r="C151" s="4"/>
@@ -8655,7 +10166,7 @@
       <c r="T151" s="4"/>
       <c r="U151" s="8"/>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="7"/>
       <c r="C152" s="4"/>
@@ -8678,7 +10189,7 @@
       <c r="T152" s="4"/>
       <c r="U152" s="8"/>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="7"/>
       <c r="C153" s="4"/>
@@ -8701,7 +10212,7 @@
       <c r="T153" s="4"/>
       <c r="U153" s="8"/>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="7"/>
       <c r="C154" s="4"/>
@@ -8724,7 +10235,7 @@
       <c r="T154" s="4"/>
       <c r="U154" s="8"/>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="7"/>
       <c r="C155" s="4"/>
@@ -8747,7 +10258,7 @@
       <c r="T155" s="4"/>
       <c r="U155" s="8"/>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="7"/>
       <c r="C156" s="4"/>
@@ -8770,7 +10281,7 @@
       <c r="T156" s="4"/>
       <c r="U156" s="8"/>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="7"/>
       <c r="C157" s="4"/>
@@ -8793,7 +10304,7 @@
       <c r="T157" s="4"/>
       <c r="U157" s="8"/>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="7"/>
       <c r="C158" s="4"/>
@@ -8816,7 +10327,7 @@
       <c r="T158" s="4"/>
       <c r="U158" s="8"/>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="7"/>
       <c r="C159" s="4"/>
@@ -8839,7 +10350,7 @@
       <c r="T159" s="4"/>
       <c r="U159" s="8"/>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="7"/>
       <c r="C160" s="4"/>
@@ -8900,7 +10411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2F00BA-95B2-42FB-9A66-5FDDA7DC61DE}">
-  <dimension ref="A1:U153"/>
+  <dimension ref="A1:V153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="6" bestFit="1" customWidth="1"/>
@@ -8926,7 +10437,7 @@
     <col min="21" max="21" width="8.88671875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
@@ -8959,7 +10470,7 @@
       <c r="T1" s="37"/>
       <c r="U1" s="38"/>
     </row>
-    <row r="2" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -9024,9 +10535,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>12101</v>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="40">
+        <v>14101</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>27</v>
@@ -9041,7 +10552,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="7">
-        <f t="shared" ref="F3:F11" si="0">(0.0001451)/2</f>
+        <f t="shared" ref="F3:F20" si="0">(0.0001451)/2</f>
         <v>7.2550000000000002E-5</v>
       </c>
       <c r="G3" s="4">
@@ -9057,7 +10568,7 @@
         <v>1730</v>
       </c>
       <c r="K3" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3" s="4">
         <v>4</v>
@@ -9069,7 +10580,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O3" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P3" s="4">
         <v>1</v>
@@ -9089,10 +10600,13 @@
       <c r="U3" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>12102</v>
+      <c r="V3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="40">
+        <v>14102</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>27</v>
@@ -9123,7 +10637,7 @@
         <v>1730</v>
       </c>
       <c r="K4" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L4" s="4">
         <v>2</v>
@@ -9135,7 +10649,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O4" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P4" s="4">
         <v>1</v>
@@ -9155,10 +10669,13 @@
       <c r="U4" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>12103</v>
+      <c r="V4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="40">
+        <v>14103</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -9189,7 +10706,7 @@
         <v>1730</v>
       </c>
       <c r="K5" s="7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L5" s="4">
         <v>1</v>
@@ -9201,7 +10718,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O5" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P5" s="4">
         <v>1</v>
@@ -9221,10 +10738,13 @@
       <c r="U5" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>12104</v>
+      <c r="V5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="40">
+        <v>14104</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>27</v>
@@ -9255,7 +10775,7 @@
         <v>1730</v>
       </c>
       <c r="K6" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4">
         <v>4</v>
@@ -9267,7 +10787,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O6" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P6" s="4">
         <v>1</v>
@@ -9287,10 +10807,13 @@
       <c r="U6" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>12105</v>
+      <c r="V6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="40">
+        <v>14105</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>27</v>
@@ -9321,7 +10844,7 @@
         <v>1730</v>
       </c>
       <c r="K7" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" s="4">
         <v>2</v>
@@ -9333,7 +10856,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O7" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P7" s="4">
         <v>1</v>
@@ -9353,10 +10876,13 @@
       <c r="U7" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>12106</v>
+      <c r="V7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="40">
+        <v>14106</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>27</v>
@@ -9387,7 +10913,7 @@
         <v>1730</v>
       </c>
       <c r="K8" s="7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L8" s="4">
         <v>1</v>
@@ -9399,7 +10925,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O8" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P8" s="4">
         <v>1</v>
@@ -9419,10 +10945,13 @@
       <c r="U8" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>12107</v>
+      <c r="V8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="40">
+        <v>14107</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>27</v>
@@ -9453,7 +10982,7 @@
         <v>1730</v>
       </c>
       <c r="K9" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" s="4">
         <v>4</v>
@@ -9465,7 +10994,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O9" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P9" s="4">
         <v>1</v>
@@ -9485,10 +11014,13 @@
       <c r="U9" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
-        <v>12108</v>
+      <c r="V9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="40">
+        <v>14108</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>27</v>
@@ -9519,7 +11051,7 @@
         <v>1730</v>
       </c>
       <c r="K10" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L10" s="4">
         <v>2</v>
@@ -9531,7 +11063,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O10" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P10" s="4">
         <v>1</v>
@@ -9551,10 +11083,13 @@
       <c r="U10" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
-        <v>12109</v>
+      <c r="V10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="40">
+        <v>14109</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>27</v>
@@ -9585,7 +11120,7 @@
         <v>1730</v>
       </c>
       <c r="K11" s="7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L11" s="4">
         <v>1</v>
@@ -9597,7 +11132,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O11" s="4">
-        <v>4.0416000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P11" s="4">
         <v>1</v>
@@ -9617,215 +11152,632 @@
       <c r="U11" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="8"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="8"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="8"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="8"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="8"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="8"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="8"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="8"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="8"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="40">
+        <v>14110</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>150</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="4">
+        <v>303</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K12" s="7">
+        <v>5</v>
+      </c>
+      <c r="L12" s="4">
+        <v>4</v>
+      </c>
+      <c r="M12" s="4">
+        <v>2</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O12" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4">
+        <v>1</v>
+      </c>
+      <c r="T12" s="4">
+        <v>500</v>
+      </c>
+      <c r="U12" s="8">
+        <v>2</v>
+      </c>
+      <c r="V12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="40">
+        <v>14111</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G13" s="4">
+        <v>150</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I13" s="4">
+        <v>303</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K13" s="7">
+        <v>10</v>
+      </c>
+      <c r="L13" s="4">
+        <v>2</v>
+      </c>
+      <c r="M13" s="4">
+        <v>2</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O13" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P13" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4">
+        <v>500</v>
+      </c>
+      <c r="U13" s="8">
+        <v>2</v>
+      </c>
+      <c r="V13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="40">
+        <v>14112</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G14" s="4">
+        <v>150</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I14" s="4">
+        <v>303</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K14" s="7">
+        <v>20</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4">
+        <v>2</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O14" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
+        <v>1</v>
+      </c>
+      <c r="T14" s="4">
+        <v>500</v>
+      </c>
+      <c r="U14" s="8">
+        <v>2</v>
+      </c>
+      <c r="V14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="40">
+        <v>14113</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G15" s="4">
+        <v>150</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I15" s="4">
+        <v>303</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K15" s="7">
+        <v>5</v>
+      </c>
+      <c r="L15" s="4">
+        <v>4</v>
+      </c>
+      <c r="M15" s="4">
+        <v>3</v>
+      </c>
+      <c r="N15" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O15" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>1</v>
+      </c>
+      <c r="T15" s="4">
+        <v>500</v>
+      </c>
+      <c r="U15" s="8">
+        <v>2</v>
+      </c>
+      <c r="V15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="40">
+        <v>14114</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>150</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I16" s="4">
+        <v>303</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K16" s="7">
+        <v>10</v>
+      </c>
+      <c r="L16" s="4">
+        <v>2</v>
+      </c>
+      <c r="M16" s="4">
+        <v>3</v>
+      </c>
+      <c r="N16" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O16" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>1</v>
+      </c>
+      <c r="T16" s="4">
+        <v>500</v>
+      </c>
+      <c r="U16" s="8">
+        <v>2</v>
+      </c>
+      <c r="V16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="40">
+        <v>14115</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G17" s="4">
+        <v>150</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I17" s="4">
+        <v>303</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K17" s="7">
+        <v>20</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>3</v>
+      </c>
+      <c r="N17" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O17" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>1</v>
+      </c>
+      <c r="T17" s="4">
+        <v>500</v>
+      </c>
+      <c r="U17" s="8">
+        <v>2</v>
+      </c>
+      <c r="V17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="40">
+        <v>14116</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>150</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I18" s="4">
+        <v>303</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K18" s="7">
+        <v>5</v>
+      </c>
+      <c r="L18" s="4">
+        <v>4</v>
+      </c>
+      <c r="M18" s="4">
+        <v>4</v>
+      </c>
+      <c r="N18" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O18" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <v>1</v>
+      </c>
+      <c r="T18" s="4">
+        <v>500</v>
+      </c>
+      <c r="U18" s="8">
+        <v>2</v>
+      </c>
+      <c r="V18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="40">
+        <v>14117</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G19" s="4">
+        <v>150</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I19" s="4">
+        <v>303</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K19" s="7">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4">
+        <v>2</v>
+      </c>
+      <c r="M19" s="4">
+        <v>4</v>
+      </c>
+      <c r="N19" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O19" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P19" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>1</v>
+      </c>
+      <c r="T19" s="4">
+        <v>500</v>
+      </c>
+      <c r="U19" s="8">
+        <v>2</v>
+      </c>
+      <c r="V19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="40">
+        <v>14118</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2550000000000002E-5</v>
+      </c>
+      <c r="G20" s="4">
+        <v>150</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I20" s="4">
+        <v>303</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1730</v>
+      </c>
+      <c r="K20" s="7">
+        <v>20</v>
+      </c>
+      <c r="L20" s="4">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4">
+        <v>4</v>
+      </c>
+      <c r="N20" s="4">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O20" s="4">
+        <v>4.0416000000000001E-2</v>
+      </c>
+      <c r="P20" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="30">
+        <v>1E-8</v>
+      </c>
+      <c r="R20" s="7">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4">
+        <v>1</v>
+      </c>
+      <c r="T20" s="4">
+        <v>500</v>
+      </c>
+      <c r="U20" s="8">
+        <v>2</v>
+      </c>
+      <c r="V20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="7"/>
       <c r="C21" s="4"/>
@@ -9848,7 +11800,7 @@
       <c r="T21" s="4"/>
       <c r="U21" s="8"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="7"/>
       <c r="C22" s="4"/>
@@ -9871,7 +11823,7 @@
       <c r="T22" s="4"/>
       <c r="U22" s="8"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="7"/>
       <c r="C23" s="4"/>
@@ -9894,7 +11846,7 @@
       <c r="T23" s="4"/>
       <c r="U23" s="8"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
@@ -9917,7 +11869,7 @@
       <c r="T24" s="4"/>
       <c r="U24" s="8"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
@@ -9940,7 +11892,7 @@
       <c r="T25" s="4"/>
       <c r="U25" s="8"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="7"/>
       <c r="C26" s="4"/>
@@ -9963,7 +11915,7 @@
       <c r="T26" s="4"/>
       <c r="U26" s="8"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="7"/>
       <c r="C27" s="4"/>
@@ -9986,7 +11938,7 @@
       <c r="T27" s="4"/>
       <c r="U27" s="8"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="7"/>
       <c r="C28" s="4"/>
@@ -10009,7 +11961,7 @@
       <c r="T28" s="4"/>
       <c r="U28" s="8"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
@@ -10032,7 +11984,7 @@
       <c r="T29" s="4"/>
       <c r="U29" s="8"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
@@ -10055,7 +12007,7 @@
       <c r="T30" s="4"/>
       <c r="U30" s="8"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="7"/>
       <c r="C31" s="4"/>
@@ -10078,7 +12030,7 @@
       <c r="T31" s="4"/>
       <c r="U31" s="8"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="7"/>
       <c r="C32" s="4"/>
@@ -12893,5 +14845,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>